--- a/Excel/Diy优胜/第一届.xlsx
+++ b/Excel/Diy优胜/第一届.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318D2293-FA86-416C-99B7-AB794E5BF818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F641A862-39B2-44FC-8295-F4EC8BA88BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1659,10 +1659,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>Target.MainSkill.SkillData.PowerType == PowerRecoverTypeEnum.攻击</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>被动</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -1672,6 +1668,10 @@
   </si>
   <si>
     <t>眩晕</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target.MainSkill.SkillData.PowerType == 1</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -6984,20 +6984,23 @@
         <v>447</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>449</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>450</v>
       </c>
       <c r="P6"/>
       <c r="AC6">
         <v>1</v>
       </c>
       <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AF6">
         <v>1</v>
       </c>
       <c r="AJ6" s="2"/>
@@ -7013,9 +7016,6 @@
       </c>
       <c r="BB6">
         <v>99</v>
-      </c>
-      <c r="BQ6">
-        <v>0.1</v>
       </c>
       <c r="BZ6" s="2"/>
       <c r="CE6" s="2"/>
@@ -7023,7 +7023,7 @@
       <c r="CJ6" s="2"/>
       <c r="CK6" s="2"/>
       <c r="CL6" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="CP6">
         <v>5</v>

--- a/Excel/Diy优胜/第一届.xlsx
+++ b/Excel/Diy优胜/第一届.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F641A862-39B2-44FC-8295-F4EC8BA88BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D0BB17-0FC2-499A-9CDA-02E06D56811F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -105,7 +105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AZ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="BB1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -132,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BP1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="BR1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -156,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CR1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="CT1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="480">
   <si>
     <t>Id</t>
   </si>
@@ -680,9 +680,6 @@
   </si>
   <si>
     <t>Hip</t>
-  </si>
-  <si>
-    <t>先锋</t>
   </si>
   <si>
     <t>half_skadi</t>
@@ -1671,7 +1668,120 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>Target.MainSkill.SkillData.PowerType == 1</t>
+    <t>优先Buff</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderBuff</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义优先级</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrderExpression</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙普攻</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>塑灵术士式索敌</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>干员</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0#0,-1#1,-1#2,-1#1,0#2,0#3,0#0,1#1,1#2,1</t>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>跟随攻击</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>史都华德弹道</t>
+  </si>
+  <si>
+    <t>Muzzle</t>
+  </si>
+  <si>
+    <t>时蒙天赋一标记</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>叠层转化</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通Buff</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>部署流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>部署干员</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"UnitId":"流涟","TargetPos":"useSelfTargetPos","SetMod":"Add","UseMod":"UserDirection","UserName":"时蒙"}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"ExTarget":"流涟"}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target.MainSkill != null AND Target.MainSkill.SkillData.PowerType == 1</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>术士</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"BuffId":"生成流涟","MaxLevel":2,"LastTime":9999}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙普攻,部署流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Idle_1</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target.UnitData.Name != \"流涟\"</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -2252,10 +2362,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -2862,14 +2972,14 @@
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>125</v>
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -2911,19 +3021,22 @@
         <v>1</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AH5" s="2" t="s">
         <v>126</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="AK5">
         <v>0</v>
       </c>
+      <c r="AM5">
+        <v>1</v>
+      </c>
       <c r="AN5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5">
         <v>2</v>
@@ -2935,44 +3048,44 @@
         <v>0.25</v>
       </c>
       <c r="BB5" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="BD5" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="BE5" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="BD5" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="BE5" s="2" t="s">
+      <c r="BF5" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="BF5" s="2" t="s">
+      <c r="BG5" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="BG5" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="BH5">
         <v>6</v>
       </c>
       <c r="BI5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="BJ5" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="BK5" s="19"/>
       <c r="BM5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BN5" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="BN5" s="2" t="s">
+      <c r="BP5" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="BP5" s="2" t="s">
+      <c r="BQ5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BR5" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="BQ5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BR5" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="BS5">
         <v>1</v>
@@ -2980,17 +3093,20 @@
     </row>
     <row r="6" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>458</v>
       </c>
       <c r="E6" s="17"/>
       <c r="F6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>90</v>
@@ -3026,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AK6">
         <v>0</v>
@@ -3050,10 +3166,28 @@
         <v>0.25</v>
       </c>
       <c r="BB6" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BD6" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
+      </c>
+      <c r="BM6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BN6" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="BP6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BQ6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BR6" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="BS6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:71" x14ac:dyDescent="0.25">
@@ -5890,7 +6024,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DH842"/>
+  <dimension ref="A1:DJ842"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -5930,375 +6064,381 @@
     <col min="38" max="39" width="8.33203125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
     <col min="41" max="41" width="13.25" customWidth="1"/>
-    <col min="42" max="43" width="11.83203125" customWidth="1"/>
-    <col min="44" max="44" width="18.4140625" customWidth="1"/>
-    <col min="45" max="45" width="12.25" customWidth="1"/>
-    <col min="46" max="46" width="11.9140625" customWidth="1"/>
-    <col min="47" max="47" width="19.58203125" customWidth="1"/>
-    <col min="48" max="48" width="12.6640625" customWidth="1"/>
-    <col min="50" max="50" width="7" customWidth="1"/>
-    <col min="51" max="51" width="11.75" customWidth="1"/>
-    <col min="52" max="52" width="19.75" customWidth="1"/>
-    <col min="53" max="53" width="5.08203125" customWidth="1"/>
-    <col min="54" max="54" width="8.5" customWidth="1"/>
-    <col min="55" max="55" width="13.5" customWidth="1"/>
-    <col min="56" max="56" width="14.6640625" customWidth="1"/>
-    <col min="57" max="57" width="10.1640625" customWidth="1"/>
-    <col min="58" max="58" width="8.25" customWidth="1"/>
-    <col min="59" max="65" width="8.33203125" customWidth="1"/>
-    <col min="66" max="68" width="11.25" customWidth="1"/>
-    <col min="69" max="69" width="6.58203125" customWidth="1"/>
-    <col min="70" max="71" width="8" customWidth="1"/>
-    <col min="72" max="72" width="7.33203125" style="6" customWidth="1"/>
-    <col min="73" max="74" width="8.5" style="6" customWidth="1"/>
-    <col min="75" max="76" width="7.83203125" style="6" customWidth="1"/>
-    <col min="77" max="77" width="22.1640625" style="6" customWidth="1"/>
-    <col min="78" max="78" width="13.5" customWidth="1"/>
-    <col min="79" max="79" width="21.1640625" customWidth="1"/>
-    <col min="80" max="80" width="15.75" customWidth="1"/>
-    <col min="81" max="81" width="15.58203125" customWidth="1"/>
-    <col min="82" max="82" width="12.83203125" customWidth="1"/>
-    <col min="83" max="83" width="16.1640625" customWidth="1"/>
-    <col min="85" max="85" width="16" customWidth="1"/>
-    <col min="86" max="87" width="12.83203125" customWidth="1"/>
-    <col min="88" max="88" width="23.58203125" customWidth="1"/>
-    <col min="89" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="17.08203125" customWidth="1"/>
-    <col min="97" max="97" width="14" customWidth="1"/>
-    <col min="98" max="98" width="8" customWidth="1"/>
-    <col min="100" max="100" width="11.08203125" customWidth="1"/>
-    <col min="101" max="101" width="13.75" customWidth="1"/>
-    <col min="108" max="108" width="15.5" customWidth="1"/>
-    <col min="112" max="112" width="9" hidden="1" customWidth="1"/>
+    <col min="42" max="45" width="11.83203125" customWidth="1"/>
+    <col min="46" max="46" width="18.4140625" customWidth="1"/>
+    <col min="47" max="47" width="12.25" customWidth="1"/>
+    <col min="48" max="48" width="11.9140625" customWidth="1"/>
+    <col min="49" max="49" width="19.58203125" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" customWidth="1"/>
+    <col min="52" max="52" width="7" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="19.75" customWidth="1"/>
+    <col min="55" max="55" width="5.08203125" customWidth="1"/>
+    <col min="56" max="56" width="8.5" customWidth="1"/>
+    <col min="57" max="57" width="13.5" customWidth="1"/>
+    <col min="58" max="58" width="14.6640625" customWidth="1"/>
+    <col min="59" max="59" width="10.1640625" customWidth="1"/>
+    <col min="60" max="60" width="8.25" customWidth="1"/>
+    <col min="61" max="67" width="8.33203125" customWidth="1"/>
+    <col min="68" max="70" width="11.25" customWidth="1"/>
+    <col min="71" max="71" width="6.58203125" customWidth="1"/>
+    <col min="72" max="73" width="8" customWidth="1"/>
+    <col min="74" max="74" width="7.33203125" style="6" customWidth="1"/>
+    <col min="75" max="76" width="8.5" style="6" customWidth="1"/>
+    <col min="77" max="78" width="7.83203125" style="6" customWidth="1"/>
+    <col min="79" max="79" width="22.1640625" style="6" customWidth="1"/>
+    <col min="80" max="80" width="13.5" customWidth="1"/>
+    <col min="81" max="81" width="21.1640625" customWidth="1"/>
+    <col min="82" max="82" width="15.75" customWidth="1"/>
+    <col min="83" max="83" width="15.58203125" customWidth="1"/>
+    <col min="84" max="84" width="12.83203125" customWidth="1"/>
+    <col min="85" max="85" width="16.1640625" customWidth="1"/>
+    <col min="87" max="87" width="16" customWidth="1"/>
+    <col min="88" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="23.58203125" customWidth="1"/>
+    <col min="91" max="91" width="12.83203125" customWidth="1"/>
+    <col min="92" max="92" width="17.08203125" customWidth="1"/>
+    <col min="99" max="99" width="14" customWidth="1"/>
+    <col min="100" max="100" width="8" customWidth="1"/>
+    <col min="102" max="102" width="11.08203125" customWidth="1"/>
+    <col min="103" max="103" width="13.75" customWidth="1"/>
+    <col min="110" max="110" width="15.5" customWidth="1"/>
+    <col min="114" max="114" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:111" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" t="s">
         <v>137</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>138</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>139</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>140</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" t="s">
         <v>142</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>143</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="V1" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="U1" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" t="s">
         <v>157</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>158</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" t="s">
         <v>160</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>161</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>162</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>163</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>164</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>165</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>166</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>167</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>168</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>169</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>170</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>171</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>172</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>173</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>174</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>175</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="AT1" t="s">
         <v>176</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AU1" t="s">
         <v>177</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AV1" t="s">
         <v>178</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AW1" t="s">
         <v>179</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AX1" t="s">
         <v>180</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AY1" t="s">
         <v>181</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AZ1" t="s">
         <v>182</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BA1" t="s">
         <v>183</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BC1" t="s">
         <v>185</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BD1" t="s">
         <v>186</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BE1" t="s">
         <v>187</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BF1" t="s">
         <v>188</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BG1" t="s">
         <v>189</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BH1" t="s">
         <v>190</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BJ1" t="s">
+        <v>190</v>
+      </c>
+      <c r="BK1" t="s">
         <v>191</v>
       </c>
-      <c r="BH1" t="s">
-        <v>191</v>
-      </c>
-      <c r="BI1" t="s">
+      <c r="BL1" t="s">
         <v>192</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BM1" t="s">
         <v>193</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BN1" t="s">
         <v>194</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BO1" t="s">
         <v>195</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BP1" t="s">
         <v>196</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BQ1" t="s">
         <v>197</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BR1" t="s">
         <v>198</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BS1" t="s">
         <v>199</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BT1" t="s">
         <v>200</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BU1" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BV1" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BW1" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="BU1" s="6" t="s">
+      <c r="BX1" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BY1" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="BZ1" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="CA1" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="BY1" s="6" t="s">
+      <c r="CB1" t="s">
         <v>208</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CC1" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="CA1" s="6" t="s">
+      <c r="CD1" t="s">
         <v>210</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CE1" t="s">
         <v>211</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CF1" t="s">
         <v>212</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CG1" t="s">
         <v>213</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CH1" t="s">
         <v>214</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CI1" t="s">
         <v>215</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CJ1" t="s">
         <v>216</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CK1" t="s">
         <v>217</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CL1" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CM1" t="s">
         <v>219</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CN1" t="s">
         <v>220</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CO1" t="s">
         <v>221</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CP1" t="s">
         <v>222</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CQ1" t="s">
         <v>223</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CR1" t="s">
+        <v>200</v>
+      </c>
+      <c r="CS1" t="s">
         <v>224</v>
       </c>
-      <c r="CP1" t="s">
-        <v>201</v>
-      </c>
-      <c r="CQ1" t="s">
+      <c r="CT1" t="s">
         <v>225</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CU1" t="s">
         <v>226</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CV1" t="s">
         <v>227</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CW1" t="s">
         <v>228</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CX1" t="s">
         <v>229</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CY1" t="s">
         <v>230</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CZ1" t="s">
+        <v>229</v>
+      </c>
+      <c r="DA1" t="s">
         <v>231</v>
       </c>
-      <c r="CX1" t="s">
-        <v>230</v>
-      </c>
-      <c r="CY1" t="s">
+      <c r="DB1" t="s">
         <v>232</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DC1" t="s">
         <v>233</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DD1" t="s">
         <v>234</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DE1" t="s">
         <v>235</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DF1" t="s">
         <v>236</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DG1" t="s">
         <v>237</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DH1" t="s">
         <v>238</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DI1" t="s">
         <v>239</v>
       </c>
-      <c r="DG1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="2" spans="1:111" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6309,328 +6449,334 @@
         <v>76</v>
       </c>
       <c r="E2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F2" t="s">
         <v>241</v>
-      </c>
-      <c r="F2" t="s">
-        <v>242</v>
       </c>
       <c r="G2" t="s">
         <v>52</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I2" t="s">
         <v>243</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>244</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="Y2" t="s">
         <v>259</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>260</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AB2" t="s">
         <v>262</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>263</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>264</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>265</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>266</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>267</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>268</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>269</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>270</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>271</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>272</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>273</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>274</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>275</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>276</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>277</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="AT2" t="s">
         <v>278</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AU2" t="s">
         <v>279</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AV2" t="s">
         <v>280</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AW2" t="s">
         <v>281</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AX2" t="s">
         <v>282</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AY2" t="s">
         <v>283</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AZ2" t="s">
         <v>284</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BA2" t="s">
         <v>285</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BB2" t="s">
         <v>286</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BC2" t="s">
         <v>287</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BD2" t="s">
         <v>288</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BE2" t="s">
         <v>289</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BF2" t="s">
         <v>290</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BG2" t="s">
         <v>291</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BH2" t="s">
         <v>292</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BI2" t="s">
         <v>293</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BJ2" t="s">
         <v>294</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BK2" t="s">
         <v>295</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BL2" t="s">
         <v>296</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BM2" t="s">
         <v>297</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BN2" t="s">
         <v>298</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BO2" t="s">
+        <v>78</v>
+      </c>
+      <c r="BP2" t="s">
         <v>299</v>
       </c>
-      <c r="BM2" t="s">
-        <v>78</v>
-      </c>
-      <c r="BN2" t="s">
+      <c r="BQ2" t="s">
         <v>300</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BR2" t="s">
         <v>301</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BS2" t="s">
         <v>302</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BT2" t="s">
         <v>303</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BU2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="BV2" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="BS2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="BT2" s="6" t="s">
+      <c r="BW2" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="BU2" s="6" t="s">
+      <c r="BX2" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="BV2" s="6" t="s">
+      <c r="BY2" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="BW2" s="6" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="CA2" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="CB2" t="s">
         <v>310</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CC2" t="s">
         <v>311</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CD2" t="s">
         <v>312</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CE2" t="s">
         <v>313</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CF2" t="s">
         <v>314</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CG2" t="s">
         <v>315</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CH2" t="s">
         <v>316</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CI2" t="s">
         <v>317</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CJ2" t="s">
         <v>318</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CK2" t="s">
         <v>319</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CM2" t="s">
         <v>321</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CN2" t="s">
         <v>322</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CO2" t="s">
         <v>323</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CP2" t="s">
         <v>324</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CQ2" t="s">
         <v>325</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CR2" t="s">
         <v>326</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CS2" t="s">
         <v>327</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CT2" t="s">
         <v>328</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CU2" t="s">
         <v>329</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CV2" t="s">
         <v>330</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CW2" t="s">
         <v>331</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CX2" t="s">
         <v>332</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CY2" t="s">
         <v>333</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CZ2" t="s">
         <v>334</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="DA2" t="s">
         <v>335</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="DB2" t="s">
         <v>336</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DC2" t="s">
         <v>337</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DD2" t="s">
         <v>338</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DE2" t="s">
         <v>339</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DF2" t="s">
         <v>340</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DG2" t="s">
         <v>341</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DH2" t="s">
         <v>342</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DI2" t="s">
         <v>343</v>
       </c>
-      <c r="DG2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="3" spans="1:111" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6656,13 +6802,13 @@
         <v>115</v>
       </c>
       <c r="J3" t="s">
+        <v>344</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>346</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>347</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>117</v>
@@ -6725,7 +6871,7 @@
         <v>115</v>
       </c>
       <c r="AG3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AH3" t="s">
         <v>115</v>
@@ -6749,184 +6895,184 @@
         <v>115</v>
       </c>
       <c r="AO3" t="s">
+        <v>348</v>
+      </c>
+      <c r="AP3" t="s">
         <v>349</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>350</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" t="s">
-        <v>351</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>115</v>
+      <c r="AR3" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>452</v>
       </c>
       <c r="AT3" t="s">
-        <v>116</v>
+        <v>350</v>
       </c>
       <c r="AU3" t="s">
         <v>115</v>
       </c>
       <c r="AV3" t="s">
-        <v>352</v>
+        <v>116</v>
       </c>
       <c r="AW3" t="s">
         <v>115</v>
       </c>
       <c r="AX3" t="s">
-        <v>116</v>
+        <v>351</v>
       </c>
       <c r="AY3" t="s">
         <v>115</v>
       </c>
       <c r="AZ3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BA3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BB3" t="s">
         <v>117</v>
       </c>
       <c r="BC3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BD3" t="s">
         <v>117</v>
       </c>
-      <c r="BD3" t="s">
+      <c r="BE3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BF3" t="s">
         <v>116</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>115</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>351</v>
       </c>
       <c r="BG3" t="s">
         <v>115</v>
       </c>
       <c r="BH3" t="s">
-        <v>116</v>
+        <v>350</v>
       </c>
       <c r="BI3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BJ3" t="s">
         <v>116</v>
       </c>
       <c r="BK3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BM3" t="s">
         <v>117</v>
       </c>
-      <c r="BL3" t="s">
+      <c r="BN3" t="s">
         <v>117</v>
       </c>
-      <c r="BM3" t="s">
+      <c r="BO3" t="s">
         <v>118</v>
       </c>
-      <c r="BN3" t="s">
+      <c r="BP3" t="s">
         <v>118</v>
       </c>
-      <c r="BO3" t="s">
+      <c r="BQ3" t="s">
+        <v>352</v>
+      </c>
+      <c r="BR3" t="s">
         <v>353</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="BS3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BV3" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="BW3" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="BX3" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="BY3" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="BQ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>116</v>
-      </c>
-      <c r="BS3" s="2" t="s">
+      <c r="BZ3" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="BT3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="BU3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW3" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="BX3" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="BY3" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>356</v>
+      <c r="CA3" s="6" t="s">
+        <v>354</v>
       </c>
       <c r="CB3" t="s">
         <v>123</v>
       </c>
       <c r="CC3" t="s">
-        <v>123</v>
+        <v>355</v>
       </c>
       <c r="CD3" t="s">
         <v>123</v>
       </c>
       <c r="CE3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>356</v>
+      </c>
+      <c r="CH3" t="s">
         <v>357</v>
       </c>
-      <c r="CF3" t="s">
+      <c r="CI3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" t="s">
         <v>358</v>
       </c>
-      <c r="CG3" t="s">
-        <v>2</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>359</v>
-      </c>
-      <c r="CI3" t="s">
-        <v>359</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
+      <c r="CK3" t="s">
+        <v>358</v>
+      </c>
+      <c r="CL3" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="CK3" t="s">
+      <c r="CM3" t="s">
         <v>119</v>
       </c>
-      <c r="CL3" t="s">
+      <c r="CN3" t="s">
         <v>119</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>122</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>122</v>
       </c>
       <c r="CO3" t="s">
         <v>122</v>
       </c>
       <c r="CP3" t="s">
-        <v>356</v>
+        <v>122</v>
       </c>
       <c r="CQ3" t="s">
         <v>122</v>
       </c>
       <c r="CR3" t="s">
+        <v>355</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CT3" t="s">
         <v>115</v>
       </c>
-      <c r="CS3" t="s">
+      <c r="CU3" t="s">
         <v>124</v>
       </c>
-      <c r="CT3" t="s">
-        <v>360</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>361</v>
-      </c>
       <c r="CV3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="CW3" t="s">
         <v>360</v>
@@ -6935,19 +7081,19 @@
         <v>360</v>
       </c>
       <c r="CY3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="CZ3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="DA3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="DB3" t="s">
-        <v>115</v>
+        <v>359</v>
       </c>
       <c r="DC3" t="s">
-        <v>115</v>
+        <v>359</v>
       </c>
       <c r="DD3" t="s">
         <v>115</v>
@@ -6961,37 +7107,43 @@
       <c r="DG3" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="4" spans="1:111" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="DH3" t="s">
+        <v>115</v>
+      </c>
+      <c r="DI3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:113" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="5" spans="1:111" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="BM5" s="2"/>
-      <c r="CS5" s="2"/>
-    </row>
-    <row r="6" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="BO5" s="2"/>
+      <c r="CU5" s="2"/>
+    </row>
+    <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>447</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>451</v>
+        <v>473</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>448</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>449</v>
       </c>
       <c r="P6"/>
       <c r="AC6">
@@ -7005,84 +7157,162 @@
       </c>
       <c r="AJ6" s="2"/>
       <c r="AO6" s="2"/>
-      <c r="AT6">
+      <c r="AV6">
         <v>20</v>
       </c>
-      <c r="AX6">
+      <c r="AZ6">
         <v>0</v>
       </c>
-      <c r="AZ6">
+      <c r="BB6">
         <v>2</v>
       </c>
-      <c r="BB6">
+      <c r="BD6">
         <v>99</v>
       </c>
-      <c r="BZ6" s="2"/>
-      <c r="CE6" s="2"/>
-      <c r="CF6" s="2"/>
-      <c r="CJ6" s="2"/>
-      <c r="CK6" s="2"/>
-      <c r="CL6" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="CP6">
+      <c r="CB6" s="2"/>
+      <c r="CG6" s="2"/>
+      <c r="CH6" s="2"/>
+      <c r="CL6" s="2"/>
+      <c r="CM6" s="2"/>
+      <c r="CN6" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="CR6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="C7" s="2"/>
+    <row r="7" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>456</v>
+      </c>
       <c r="J7" s="2"/>
+      <c r="K7" s="5" t="s">
+        <v>457</v>
+      </c>
       <c r="O7"/>
+      <c r="AC7">
+        <v>2</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
       <c r="AO7" s="2"/>
-      <c r="BZ7" s="2"/>
-      <c r="CE7" s="2"/>
-    </row>
-    <row r="8" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="AT7" t="s">
+        <v>459</v>
+      </c>
+      <c r="AX7" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="AZ7">
+        <v>1</v>
+      </c>
+      <c r="BD7">
+        <v>1</v>
+      </c>
+      <c r="CB7" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="CG7" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="CH7" t="s">
+        <v>462</v>
+      </c>
+      <c r="CI7" t="s">
+        <v>463</v>
+      </c>
+      <c r="CN7" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="CR7">
+        <v>9999</v>
+      </c>
+      <c r="CU7" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="8" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="AC8">
+        <v>2</v>
+      </c>
+      <c r="AD8">
+        <v>2</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
       <c r="AG8" s="2"/>
+      <c r="AH8" s="2">
+        <v>1</v>
+      </c>
       <c r="AO8" s="2"/>
-      <c r="AV8" s="2"/>
-      <c r="CE8" s="2"/>
-      <c r="CJ8" s="2"/>
+      <c r="AX8" s="2"/>
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="CG8" s="2"/>
       <c r="CL8" s="2"/>
-      <c r="CM8" s="2"/>
-    </row>
-    <row r="9" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="CN8" s="2"/>
+      <c r="CO8" s="2"/>
+      <c r="CU8" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="C9" s="2"/>
       <c r="AG9" s="2"/>
       <c r="AO9" s="2"/>
-      <c r="AV9" s="2"/>
-      <c r="CE9" s="2"/>
-      <c r="CJ9" s="2"/>
+      <c r="AX9" s="2"/>
+      <c r="CG9" s="2"/>
       <c r="CL9" s="2"/>
-      <c r="CM9" s="2"/>
-    </row>
-    <row r="10" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="CN9" s="2"/>
+      <c r="CO9" s="2"/>
+    </row>
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="C10" s="2"/>
       <c r="AG10" s="2"/>
       <c r="AO10" s="2"/>
-      <c r="AV10" s="2"/>
-      <c r="CE10" s="2"/>
-      <c r="CJ10" s="2"/>
+      <c r="AX10" s="2"/>
+      <c r="CG10" s="2"/>
       <c r="CL10" s="2"/>
-      <c r="CM10" s="2"/>
-    </row>
-    <row r="11" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="CN10" s="2"/>
+      <c r="CO10" s="2"/>
+    </row>
+    <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="C11" s="2"/>
       <c r="AG11" s="2"/>
       <c r="AJ11" s="2"/>
       <c r="AO11" s="2"/>
-      <c r="BT11"/>
-      <c r="CJ11" s="5"/>
-      <c r="CL11" s="2"/>
-      <c r="CM11" s="2"/>
-    </row>
-    <row r="12" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="BV11"/>
+      <c r="CL11" s="5"/>
+      <c r="CN11" s="2"/>
+      <c r="CO11" s="2"/>
+    </row>
+    <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
@@ -7097,15 +7327,15 @@
       <c r="V12" s="7"/>
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
-      <c r="BT12" s="10"/>
-      <c r="BU12" s="10"/>
       <c r="BV12" s="10"/>
       <c r="BW12" s="10"/>
       <c r="BX12" s="10"/>
       <c r="BY12" s="10"/>
-      <c r="CJ12" s="7"/>
-    </row>
-    <row r="13" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="BZ12" s="10"/>
+      <c r="CA12" s="10"/>
+      <c r="CL12" s="7"/>
+    </row>
+    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
@@ -7120,15 +7350,15 @@
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-      <c r="BT13" s="10"/>
-      <c r="BU13" s="10"/>
       <c r="BV13" s="10"/>
       <c r="BW13" s="10"/>
       <c r="BX13" s="10"/>
       <c r="BY13" s="10"/>
-      <c r="CJ13" s="7"/>
-    </row>
-    <row r="14" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="BZ13" s="10"/>
+      <c r="CA13" s="10"/>
+      <c r="CL13" s="7"/>
+    </row>
+    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
@@ -7143,15 +7373,15 @@
       <c r="V14" s="7"/>
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
-      <c r="BT14"/>
-      <c r="BU14" s="10"/>
-      <c r="BV14" s="10"/>
+      <c r="BV14"/>
       <c r="BW14" s="10"/>
       <c r="BX14" s="10"/>
       <c r="BY14" s="10"/>
-      <c r="CJ14" s="7"/>
-    </row>
-    <row r="15" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="BZ14" s="10"/>
+      <c r="CA14" s="10"/>
+      <c r="CL14" s="7"/>
+    </row>
+    <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
@@ -7166,16 +7396,16 @@
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
-      <c r="BT15" s="10"/>
-      <c r="BU15" s="10"/>
       <c r="BV15" s="10"/>
       <c r="BW15" s="10"/>
       <c r="BX15" s="10"/>
       <c r="BY15" s="10"/>
-      <c r="CJ15" s="7"/>
-      <c r="CS15" s="2"/>
-    </row>
-    <row r="16" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="BZ15" s="10"/>
+      <c r="CA15" s="10"/>
+      <c r="CL15" s="7"/>
+      <c r="CU15" s="2"/>
+    </row>
+    <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
@@ -7190,15 +7420,15 @@
       <c r="V16" s="7"/>
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
-      <c r="BT16"/>
-      <c r="BU16" s="10"/>
-      <c r="BV16" s="10"/>
+      <c r="BV16"/>
       <c r="BW16" s="10"/>
       <c r="BX16" s="10"/>
       <c r="BY16" s="10"/>
-      <c r="CJ16" s="7"/>
-    </row>
-    <row r="17" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ16" s="10"/>
+      <c r="CA16" s="10"/>
+      <c r="CL16" s="7"/>
+    </row>
+    <row r="17" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
@@ -7213,15 +7443,15 @@
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
-      <c r="BT17" s="10"/>
-      <c r="BU17" s="10"/>
       <c r="BV17" s="10"/>
       <c r="BW17" s="10"/>
       <c r="BX17" s="10"/>
       <c r="BY17" s="10"/>
-      <c r="CJ17" s="7"/>
-    </row>
-    <row r="18" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ17" s="10"/>
+      <c r="CA17" s="10"/>
+      <c r="CL17" s="7"/>
+    </row>
+    <row r="18" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
@@ -7236,15 +7466,15 @@
       <c r="V18" s="7"/>
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
-      <c r="BT18" s="10"/>
-      <c r="BU18" s="10"/>
       <c r="BV18" s="10"/>
       <c r="BW18" s="10"/>
       <c r="BX18" s="10"/>
       <c r="BY18" s="10"/>
-      <c r="CJ18" s="7"/>
-    </row>
-    <row r="19" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ18" s="10"/>
+      <c r="CA18" s="10"/>
+      <c r="CL18" s="7"/>
+    </row>
+    <row r="19" spans="1:99" x14ac:dyDescent="0.25">
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
@@ -7261,14 +7491,14 @@
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
       <c r="Y19" s="8"/>
-      <c r="BT19" s="11"/>
-      <c r="BU19" s="11"/>
       <c r="BV19" s="11"/>
       <c r="BW19" s="11"/>
       <c r="BX19" s="11"/>
       <c r="BY19" s="11"/>
-    </row>
-    <row r="20" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ19" s="11"/>
+      <c r="CA19" s="11"/>
+    </row>
+    <row r="20" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
@@ -7283,15 +7513,15 @@
       <c r="V20" s="7"/>
       <c r="W20" s="7"/>
       <c r="X20" s="7"/>
-      <c r="BT20"/>
-      <c r="BU20" s="10"/>
-      <c r="BV20" s="10"/>
+      <c r="BV20"/>
       <c r="BW20" s="10"/>
       <c r="BX20" s="10"/>
       <c r="BY20" s="10"/>
-      <c r="CJ20" s="7"/>
-    </row>
-    <row r="21" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ20" s="10"/>
+      <c r="CA20" s="10"/>
+      <c r="CL20" s="7"/>
+    </row>
+    <row r="21" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
@@ -7306,15 +7536,15 @@
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
-      <c r="BT21"/>
-      <c r="BU21" s="10"/>
-      <c r="BV21" s="10"/>
+      <c r="BV21"/>
       <c r="BW21" s="10"/>
       <c r="BX21" s="10"/>
       <c r="BY21" s="10"/>
-      <c r="CJ21" s="7"/>
-    </row>
-    <row r="22" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ21" s="10"/>
+      <c r="CA21" s="10"/>
+      <c r="CL21" s="7"/>
+    </row>
+    <row r="22" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
@@ -7329,15 +7559,15 @@
       <c r="V22" s="7"/>
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
-      <c r="BT22" s="10"/>
-      <c r="BU22" s="10"/>
       <c r="BV22" s="10"/>
       <c r="BW22" s="10"/>
       <c r="BX22" s="10"/>
       <c r="BY22" s="10"/>
-      <c r="CJ22" s="7"/>
-    </row>
-    <row r="23" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ22" s="10"/>
+      <c r="CA22" s="10"/>
+      <c r="CL22" s="7"/>
+    </row>
+    <row r="23" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K23" s="7"/>
       <c r="L23" s="8"/>
       <c r="M23"/>
@@ -7353,15 +7583,15 @@
       <c r="W23" s="8"/>
       <c r="X23" s="8"/>
       <c r="Y23" s="8"/>
-      <c r="BT23" s="11"/>
-      <c r="BU23" s="11"/>
       <c r="BV23" s="11"/>
       <c r="BW23" s="11"/>
       <c r="BX23" s="11"/>
       <c r="BY23" s="11"/>
-      <c r="CJ23" s="7"/>
-    </row>
-    <row r="24" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ23" s="11"/>
+      <c r="CA23" s="11"/>
+      <c r="CL23" s="7"/>
+    </row>
+    <row r="24" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7"/>
@@ -7376,15 +7606,15 @@
       <c r="V24" s="7"/>
       <c r="W24" s="7"/>
       <c r="X24" s="7"/>
-      <c r="BT24"/>
-      <c r="BU24" s="10"/>
-      <c r="BV24" s="10"/>
+      <c r="BV24"/>
       <c r="BW24" s="10"/>
       <c r="BX24" s="10"/>
       <c r="BY24" s="10"/>
-      <c r="CJ24" s="7"/>
-    </row>
-    <row r="25" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ24" s="10"/>
+      <c r="CA24" s="10"/>
+      <c r="CL24" s="7"/>
+    </row>
+    <row r="25" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
@@ -7399,35 +7629,35 @@
       <c r="V25" s="7"/>
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
-      <c r="BT25"/>
-      <c r="BU25" s="10"/>
-      <c r="BV25" s="10"/>
+      <c r="BV25"/>
       <c r="BW25" s="10"/>
       <c r="BX25" s="10"/>
       <c r="BY25" s="10"/>
-      <c r="CJ25" s="7"/>
-    </row>
-    <row r="27" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BZ25" s="10"/>
+      <c r="CA25" s="10"/>
+      <c r="CL25" s="7"/>
+    </row>
+    <row r="27" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="AR27" s="2"/>
-      <c r="BT27"/>
-      <c r="CJ27" s="5"/>
-      <c r="CS27" s="2"/>
-    </row>
-    <row r="28" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="AT27" s="2"/>
+      <c r="BV27"/>
+      <c r="CL27" s="5"/>
+      <c r="CU27" s="2"/>
+    </row>
+    <row r="28" spans="1:99" x14ac:dyDescent="0.25">
       <c r="J28" s="2"/>
       <c r="O28"/>
       <c r="AO28" s="2"/>
-      <c r="CS28" s="2"/>
-    </row>
-    <row r="29" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="CU28" s="2"/>
+    </row>
+    <row r="29" spans="1:99" x14ac:dyDescent="0.25">
       <c r="P29"/>
     </row>
-    <row r="30" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="CJ30" s="5"/>
-    </row>
-    <row r="31" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CL30" s="5"/>
+    </row>
+    <row r="31" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
       <c r="M31"/>
@@ -7442,15 +7672,15 @@
       <c r="V31" s="9"/>
       <c r="W31" s="9"/>
       <c r="X31"/>
-      <c r="BS31" s="12"/>
-      <c r="BT31" s="12"/>
       <c r="BU31" s="12"/>
       <c r="BV31" s="12"/>
       <c r="BW31" s="12"/>
       <c r="BX31" s="12"/>
-      <c r="BY31"/>
-    </row>
-    <row r="32" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BY31" s="12"/>
+      <c r="BZ31" s="12"/>
+      <c r="CA31"/>
+    </row>
+    <row r="32" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
       <c r="M32"/>
@@ -7465,1583 +7695,1583 @@
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
       <c r="X32"/>
-      <c r="BS32" s="12"/>
-      <c r="BT32" s="12"/>
       <c r="BU32" s="12"/>
       <c r="BV32" s="12"/>
       <c r="BW32" s="12"/>
       <c r="BX32" s="12"/>
-      <c r="BY32"/>
-      <c r="CL32" s="3"/>
-    </row>
-    <row r="33" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="AW33" s="5"/>
-      <c r="BT33"/>
-      <c r="BU33"/>
+      <c r="BY32" s="12"/>
+      <c r="BZ32" s="12"/>
+      <c r="CA32"/>
+      <c r="CN32" s="3"/>
+    </row>
+    <row r="33" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="AY33" s="5"/>
       <c r="BV33"/>
       <c r="BW33"/>
       <c r="BX33"/>
       <c r="BY33"/>
-      <c r="BZ33" s="5"/>
-      <c r="CA33" s="5"/>
+      <c r="BZ33"/>
+      <c r="CA33"/>
       <c r="CB33" s="5"/>
       <c r="CC33" s="5"/>
       <c r="CD33" s="5"/>
+      <c r="CE33" s="5"/>
       <c r="CF33" s="5"/>
-      <c r="CG33" s="5"/>
       <c r="CH33" s="5"/>
       <c r="CI33" s="5"/>
       <c r="CJ33" s="5"/>
       <c r="CK33" s="5"/>
-    </row>
-    <row r="34" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="CL33" s="5"/>
+      <c r="CM33" s="5"/>
+    </row>
+    <row r="34" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M34"/>
       <c r="N34"/>
       <c r="P34" s="3"/>
       <c r="R34" s="3"/>
       <c r="S34"/>
       <c r="X34"/>
-      <c r="BT34"/>
-      <c r="BZ34" s="6"/>
-    </row>
-    <row r="35" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="BT35"/>
-    </row>
-    <row r="36" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="BV34"/>
+      <c r="CB34" s="6"/>
+    </row>
+    <row r="35" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="BV35"/>
+    </row>
+    <row r="36" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M36"/>
       <c r="O36"/>
-      <c r="BM36" s="2"/>
-      <c r="BN36" s="2"/>
-      <c r="CL36" s="3"/>
-    </row>
-    <row r="37" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="BO36" s="2"/>
+      <c r="BP36" s="2"/>
+      <c r="CN36" s="3"/>
+    </row>
+    <row r="37" spans="1:92" x14ac:dyDescent="0.25">
       <c r="J37" s="5"/>
       <c r="M37"/>
       <c r="O37" s="3"/>
       <c r="P37"/>
       <c r="Q37"/>
-      <c r="CL37" s="2"/>
-    </row>
-    <row r="38" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="CN37" s="2"/>
+    </row>
+    <row r="38" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M38"/>
-      <c r="BZ38" s="13"/>
-    </row>
-    <row r="39" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="CB38" s="13"/>
+    </row>
+    <row r="39" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M39"/>
       <c r="O39" s="3"/>
       <c r="P39"/>
       <c r="Q39"/>
     </row>
-    <row r="40" spans="1:90" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="M40"/>
       <c r="O40" s="3"/>
       <c r="P40"/>
       <c r="Q40"/>
-      <c r="CL40" s="3"/>
-    </row>
-    <row r="41" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="CN40" s="3"/>
+    </row>
+    <row r="41" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M41"/>
-      <c r="AW41" s="5"/>
-      <c r="BT41"/>
-      <c r="BU41"/>
+      <c r="AY41" s="5"/>
       <c r="BV41"/>
       <c r="BW41"/>
       <c r="BX41"/>
       <c r="BY41"/>
-      <c r="BZ41" s="5"/>
-      <c r="CA41" s="5"/>
+      <c r="BZ41"/>
+      <c r="CA41"/>
       <c r="CB41" s="5"/>
       <c r="CC41" s="5"/>
       <c r="CD41" s="5"/>
+      <c r="CE41" s="5"/>
       <c r="CF41" s="5"/>
-      <c r="CG41" s="5"/>
       <c r="CH41" s="5"/>
       <c r="CI41" s="5"/>
-      <c r="CL41" s="3"/>
-    </row>
-    <row r="42" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="CJ41" s="5"/>
+      <c r="CK41" s="5"/>
+      <c r="CN41" s="3"/>
+    </row>
+    <row r="42" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M42"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
     </row>
-    <row r="43" spans="1:90" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M43"/>
       <c r="N43"/>
-      <c r="BT43"/>
-      <c r="CG43" s="5"/>
-      <c r="CH43" s="5"/>
-    </row>
-    <row r="44" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="BV43"/>
+      <c r="CI43" s="5"/>
+      <c r="CJ43" s="5"/>
+    </row>
+    <row r="44" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M44"/>
       <c r="N44"/>
-      <c r="BT44"/>
-      <c r="CH44" s="5"/>
-    </row>
-    <row r="45" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="BV44"/>
+      <c r="CJ44" s="5"/>
+    </row>
+    <row r="45" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M45"/>
       <c r="O45" s="3"/>
       <c r="AG45" s="2"/>
       <c r="AO45" s="2"/>
-      <c r="BM45" s="2"/>
-      <c r="BN45" s="2"/>
-      <c r="CE45" s="2"/>
-      <c r="CK45" s="2"/>
-    </row>
-    <row r="46" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="BO45" s="2"/>
+      <c r="BP45" s="2"/>
+      <c r="CG45" s="2"/>
+      <c r="CM45" s="2"/>
+    </row>
+    <row r="46" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="M46"/>
       <c r="O46" s="3"/>
       <c r="AG46" s="2"/>
       <c r="AO46" s="2"/>
-      <c r="CE46" s="2"/>
-    </row>
-    <row r="47" spans="1:90" x14ac:dyDescent="0.25">
-      <c r="BS47" s="6"/>
-      <c r="BY47"/>
-    </row>
-    <row r="48" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="CG46" s="2"/>
+    </row>
+    <row r="47" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="BU47" s="6"/>
+      <c r="CA47"/>
+    </row>
+    <row r="48" spans="1:92" x14ac:dyDescent="0.25">
       <c r="E48" s="2"/>
       <c r="O48"/>
       <c r="W48"/>
       <c r="X48"/>
-      <c r="BM48" s="2"/>
-      <c r="BN48" s="2"/>
-      <c r="CL48" s="3"/>
-    </row>
-    <row r="49" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="BO48" s="2"/>
+      <c r="BP48" s="2"/>
+      <c r="CN48" s="3"/>
+    </row>
+    <row r="49" spans="1:99" x14ac:dyDescent="0.25">
       <c r="M49"/>
       <c r="O49" s="3"/>
       <c r="P49"/>
       <c r="Q49"/>
-      <c r="CL49" s="3"/>
-    </row>
-    <row r="50" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="CN49" s="3"/>
+    </row>
+    <row r="50" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="M50"/>
       <c r="O50" s="3"/>
       <c r="P50"/>
       <c r="Q50"/>
-      <c r="CL50" s="3"/>
-    </row>
-    <row r="51" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="CN50" s="3"/>
+    </row>
+    <row r="51" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="O51" s="3"/>
     </row>
-    <row r="52" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
-      <c r="CJ52" s="5"/>
-    </row>
-    <row r="53" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="CJ53" s="5"/>
-    </row>
-    <row r="54" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="CL52" s="5"/>
+    </row>
+    <row r="53" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CL53" s="5"/>
+    </row>
+    <row r="54" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="C54" s="2"/>
       <c r="J54" s="2"/>
       <c r="AJ54" s="2"/>
-      <c r="CJ54" s="5"/>
-      <c r="CS54" s="2"/>
-    </row>
-    <row r="55" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="CJ55" s="5"/>
-    </row>
-    <row r="56" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="CL54" s="5"/>
+      <c r="CU54" s="2"/>
+    </row>
+    <row r="55" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CL55" s="5"/>
+    </row>
+    <row r="56" spans="1:99" x14ac:dyDescent="0.25">
       <c r="O56"/>
       <c r="W56"/>
       <c r="X56"/>
-      <c r="CL56" s="3"/>
-    </row>
-    <row r="57" spans="1:97" x14ac:dyDescent="0.25">
+      <c r="CN56" s="3"/>
+    </row>
+    <row r="57" spans="1:99" x14ac:dyDescent="0.25">
       <c r="O57" s="3"/>
       <c r="X57"/>
     </row>
-    <row r="58" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:99" x14ac:dyDescent="0.25">
       <c r="O58" s="3"/>
       <c r="P58"/>
       <c r="Q58"/>
       <c r="X58"/>
     </row>
-    <row r="59" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:99" x14ac:dyDescent="0.25">
       <c r="O59" s="3"/>
       <c r="X59"/>
     </row>
-    <row r="62" spans="1:97" x14ac:dyDescent="0.25">
-      <c r="CK62" s="3"/>
-      <c r="CL62" s="3"/>
-    </row>
-    <row r="64" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CM62" s="3"/>
+      <c r="CN62" s="3"/>
+    </row>
+    <row r="64" spans="1:99" x14ac:dyDescent="0.25">
       <c r="M64"/>
       <c r="N64"/>
-      <c r="BT64"/>
-      <c r="BZ64" s="14"/>
-      <c r="CG64" s="5"/>
-      <c r="CH64" s="5"/>
-    </row>
-    <row r="65" spans="13:89" x14ac:dyDescent="0.25">
+      <c r="BV64"/>
+      <c r="CB64" s="14"/>
+      <c r="CI64" s="5"/>
+      <c r="CJ64" s="5"/>
+    </row>
+    <row r="65" spans="13:91" x14ac:dyDescent="0.25">
       <c r="M65"/>
       <c r="N65"/>
-      <c r="BT65"/>
-      <c r="BZ65" s="14"/>
-      <c r="CH65" s="5"/>
-    </row>
-    <row r="66" spans="13:89" x14ac:dyDescent="0.25">
+      <c r="BV65"/>
+      <c r="CB65" s="14"/>
+      <c r="CJ65" s="5"/>
+    </row>
+    <row r="66" spans="13:91" x14ac:dyDescent="0.25">
       <c r="O66"/>
       <c r="X66"/>
-      <c r="CK66" s="3"/>
-    </row>
-    <row r="69" spans="13:89" x14ac:dyDescent="0.25">
-      <c r="CJ69" s="5"/>
-    </row>
-    <row r="70" spans="13:89" x14ac:dyDescent="0.25">
-      <c r="CJ70" s="5"/>
-    </row>
-    <row r="76" spans="13:89" x14ac:dyDescent="0.25">
-      <c r="CJ76" s="5"/>
-    </row>
-    <row r="77" spans="13:89" x14ac:dyDescent="0.25">
-      <c r="CJ77" s="5"/>
-    </row>
-    <row r="79" spans="13:89" x14ac:dyDescent="0.25">
-      <c r="CJ79" s="5"/>
-    </row>
-    <row r="80" spans="13:89" x14ac:dyDescent="0.25">
-      <c r="CJ80" s="5"/>
-    </row>
-    <row r="81" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ81" s="5"/>
-    </row>
-    <row r="82" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ82" s="5"/>
-    </row>
-    <row r="83" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT83"/>
-    </row>
-    <row r="84" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT84"/>
-    </row>
-    <row r="85" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT85"/>
-      <c r="CJ85" s="5"/>
-    </row>
-    <row r="86" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ86" s="5"/>
-    </row>
-    <row r="87" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ87" s="5"/>
-    </row>
-    <row r="88" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT88"/>
-    </row>
-    <row r="89" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ89" s="5"/>
-    </row>
-    <row r="93" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT93"/>
-    </row>
-    <row r="94" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ94" s="5"/>
-    </row>
-    <row r="102" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ102" s="5"/>
-    </row>
-    <row r="103" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ103" s="5"/>
-    </row>
-    <row r="104" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT104"/>
-    </row>
-    <row r="109" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT109"/>
-    </row>
-    <row r="110" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT110"/>
-      <c r="CJ110" s="5"/>
-    </row>
-    <row r="111" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ111" s="5"/>
-    </row>
-    <row r="112" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ112" s="5"/>
-    </row>
-    <row r="113" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ113" s="5"/>
-    </row>
-    <row r="114" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ114" s="5"/>
-    </row>
-    <row r="115" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT115"/>
-    </row>
-    <row r="116" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ116" s="5"/>
-    </row>
-    <row r="117" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ117" s="5"/>
-    </row>
-    <row r="118" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ118" s="5"/>
-    </row>
-    <row r="119" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ119" s="5"/>
-    </row>
-    <row r="120" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT120"/>
-    </row>
-    <row r="121" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ121" s="5"/>
-    </row>
-    <row r="122" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ122" s="5"/>
-    </row>
-    <row r="123" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ123" s="5"/>
-    </row>
-    <row r="124" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ124" s="5"/>
-    </row>
-    <row r="127" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ127" s="5"/>
-    </row>
-    <row r="128" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ128" s="5"/>
-    </row>
-    <row r="129" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ129" s="5"/>
-    </row>
-    <row r="130" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ130" s="5"/>
-    </row>
-    <row r="131" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ131" s="5"/>
-    </row>
-    <row r="133" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT133"/>
-    </row>
-    <row r="134" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ134" s="5"/>
-    </row>
-    <row r="135" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ135" s="5"/>
-    </row>
-    <row r="136" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ136" s="5"/>
-    </row>
-    <row r="137" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ137" s="5"/>
-    </row>
-    <row r="141" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ141" s="5"/>
-    </row>
-    <row r="143" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT143"/>
-    </row>
-    <row r="144" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT144"/>
-      <c r="CJ144" s="5"/>
-    </row>
-    <row r="145" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ145" s="5"/>
-    </row>
-    <row r="146" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ146" s="5"/>
-    </row>
-    <row r="147" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ147" s="5"/>
-    </row>
-    <row r="148" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ148" s="5"/>
-    </row>
-    <row r="150" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT150"/>
-    </row>
-    <row r="151" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ151" s="5"/>
-    </row>
-    <row r="152" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ152" s="5"/>
-    </row>
-    <row r="154" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ154" s="5"/>
-    </row>
-    <row r="155" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ155" s="5"/>
-    </row>
-    <row r="157" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT157"/>
-    </row>
-    <row r="158" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ158" s="5"/>
-    </row>
-    <row r="161" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ161" s="5"/>
-    </row>
-    <row r="162" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ162" s="5"/>
-    </row>
-    <row r="165" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ165" s="5"/>
-    </row>
-    <row r="167" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ167" s="5"/>
-    </row>
-    <row r="169" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT169"/>
-    </row>
-    <row r="170" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ170" s="5"/>
-    </row>
-    <row r="171" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ171" s="5"/>
-    </row>
-    <row r="173" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ173" s="5"/>
-    </row>
-    <row r="174" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ174" s="5"/>
-    </row>
-    <row r="175" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ175" s="5"/>
-    </row>
-    <row r="180" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ180" s="5"/>
-    </row>
-    <row r="181" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ181" s="5"/>
-    </row>
-    <row r="184" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ184" s="5"/>
-    </row>
-    <row r="185" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ185" s="5"/>
-    </row>
-    <row r="189" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ189" s="5"/>
-    </row>
-    <row r="193" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ193" s="5"/>
-    </row>
-    <row r="195" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ195" s="5"/>
-    </row>
-    <row r="196" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ196" s="5"/>
-    </row>
-    <row r="198" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ198" s="5"/>
-    </row>
-    <row r="199" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ199" s="5"/>
-    </row>
-    <row r="201" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT201"/>
-    </row>
-    <row r="202" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT202"/>
-      <c r="CJ202" s="5"/>
-    </row>
-    <row r="203" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ203" s="5"/>
-    </row>
-    <row r="205" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ205" s="5"/>
-    </row>
-    <row r="214" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT214"/>
-    </row>
-    <row r="215" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT215"/>
-      <c r="CJ215" s="5"/>
-    </row>
-    <row r="216" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ216" s="5"/>
-    </row>
-    <row r="217" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ217" s="5"/>
-    </row>
-    <row r="218" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT218"/>
-    </row>
-    <row r="219" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT219"/>
-      <c r="CJ219" s="5"/>
-    </row>
-    <row r="220" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ220" s="5"/>
-    </row>
-    <row r="222" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT222"/>
-    </row>
-    <row r="223" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT223"/>
-      <c r="CJ223" s="5"/>
-    </row>
-    <row r="224" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ224" s="5"/>
-    </row>
-    <row r="226" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT226"/>
-    </row>
-    <row r="227" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ227" s="5"/>
-    </row>
-    <row r="230" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ230" s="5"/>
-    </row>
-    <row r="234" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ234" s="5"/>
-    </row>
-    <row r="236" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT236"/>
-    </row>
-    <row r="237" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ237" s="5"/>
-    </row>
-    <row r="244" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT244"/>
-    </row>
-    <row r="245" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ245" s="5"/>
-    </row>
-    <row r="246" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ246" s="5"/>
-    </row>
-    <row r="248" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT248"/>
-    </row>
-    <row r="249" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT249"/>
-      <c r="CJ249" s="5"/>
-    </row>
-    <row r="250" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ250" s="5"/>
-    </row>
-    <row r="256" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT256"/>
-    </row>
-    <row r="257" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT257"/>
-      <c r="CJ257" s="5"/>
-    </row>
-    <row r="258" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT258"/>
-      <c r="CJ258" s="5"/>
-    </row>
-    <row r="259" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ259" s="5"/>
-    </row>
-    <row r="264" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT264"/>
-    </row>
-    <row r="265" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT265"/>
-    </row>
-    <row r="269" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT269"/>
-    </row>
-    <row r="270" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ270" s="5"/>
-    </row>
-    <row r="271" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT271"/>
-    </row>
-    <row r="272" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ272" s="5"/>
-    </row>
-    <row r="282" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT282"/>
-    </row>
-    <row r="283" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ283" s="5"/>
-    </row>
-    <row r="285" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT285"/>
-    </row>
-    <row r="286" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ286" s="5"/>
-    </row>
-    <row r="294" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT294"/>
-    </row>
-    <row r="295" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ295" s="5"/>
-    </row>
-    <row r="299" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT299"/>
-    </row>
-    <row r="300" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ300" s="5"/>
-    </row>
-    <row r="302" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT302"/>
-    </row>
-    <row r="303" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ303" s="5"/>
-    </row>
-    <row r="319" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT319"/>
-    </row>
-    <row r="320" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT320"/>
-      <c r="CJ320" s="5"/>
-    </row>
-    <row r="321" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT321"/>
-      <c r="CJ321" s="5"/>
-    </row>
-    <row r="322" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT322"/>
-      <c r="CJ322" s="5"/>
-    </row>
-    <row r="323" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT323"/>
-    </row>
-    <row r="325" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT325"/>
-    </row>
-    <row r="326" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT326"/>
-      <c r="CJ326" s="5"/>
-    </row>
-    <row r="327" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT327"/>
-      <c r="CJ327" s="5"/>
-    </row>
-    <row r="328" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ328" s="5"/>
-    </row>
-    <row r="332" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT332"/>
-    </row>
-    <row r="333" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ333" s="5"/>
-    </row>
-    <row r="335" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT335"/>
-    </row>
-    <row r="336" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT336"/>
-      <c r="CJ336" s="5"/>
-    </row>
-    <row r="337" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT337"/>
-      <c r="CJ337" s="5"/>
-    </row>
-    <row r="338" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ338" s="5"/>
-    </row>
-    <row r="354" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT354"/>
-    </row>
-    <row r="355" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ355" s="5"/>
-    </row>
-    <row r="363" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ363" s="5"/>
-    </row>
-    <row r="364" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ364" s="5"/>
-    </row>
-    <row r="365" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ365" s="5"/>
-    </row>
-    <row r="366" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ366" s="5"/>
-    </row>
-    <row r="367" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ367" s="5"/>
-    </row>
-    <row r="369" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT369"/>
-    </row>
-    <row r="370" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ370" s="5"/>
-    </row>
-    <row r="371" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT371"/>
-    </row>
-    <row r="372" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT372"/>
-      <c r="CJ372" s="5"/>
-    </row>
-    <row r="373" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ373" s="5"/>
-    </row>
-    <row r="375" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT375"/>
-    </row>
-    <row r="376" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT376"/>
-      <c r="CJ376" s="5"/>
-    </row>
-    <row r="377" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT377"/>
-      <c r="CJ377" s="5"/>
-    </row>
-    <row r="378" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ378" s="5"/>
-    </row>
-    <row r="380" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ380" s="5"/>
-    </row>
-    <row r="382" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ382" s="5"/>
-    </row>
-    <row r="384" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ384" s="5"/>
-    </row>
-    <row r="387" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ387" s="5"/>
-    </row>
-    <row r="388" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ388" s="5"/>
-    </row>
-    <row r="389" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ389" s="5"/>
-    </row>
-    <row r="390" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ390" s="5"/>
-    </row>
-    <row r="391" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ391" s="5"/>
-    </row>
-    <row r="392" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ392" s="5"/>
-    </row>
-    <row r="393" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT393"/>
-    </row>
-    <row r="394" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT394"/>
-      <c r="CJ394" s="5"/>
-    </row>
-    <row r="395" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT395"/>
-      <c r="CJ395" s="5"/>
-    </row>
-    <row r="396" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ396" s="5"/>
-    </row>
-    <row r="397" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ397" s="5"/>
-    </row>
-    <row r="398" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ398" s="5"/>
-    </row>
-    <row r="399" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ399" s="5"/>
-    </row>
-    <row r="401" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ401" s="5"/>
-    </row>
-    <row r="402" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ402" s="5"/>
-    </row>
-    <row r="403" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT403"/>
-    </row>
-    <row r="404" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT404"/>
-      <c r="CJ404" s="5"/>
-    </row>
-    <row r="405" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT405"/>
-      <c r="CJ405" s="5"/>
-    </row>
-    <row r="406" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ406" s="5"/>
-    </row>
-    <row r="407" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ407" s="5"/>
-    </row>
-    <row r="409" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ409" s="5"/>
-    </row>
-    <row r="410" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ410" s="5"/>
-    </row>
-    <row r="411" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT411"/>
-      <c r="CJ411" s="5"/>
-    </row>
-    <row r="412" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT412"/>
-      <c r="CJ412" s="5"/>
-    </row>
-    <row r="413" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ413" s="5"/>
-    </row>
-    <row r="414" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ414" s="5"/>
-    </row>
-    <row r="415" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ415" s="5"/>
-    </row>
-    <row r="417" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT417"/>
-      <c r="CJ417" s="5"/>
-    </row>
-    <row r="418" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ418" s="5"/>
-    </row>
-    <row r="419" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ419" s="5"/>
-    </row>
-    <row r="421" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT421"/>
-      <c r="CJ421" s="5"/>
-    </row>
-    <row r="422" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT422"/>
-      <c r="CJ422" s="5"/>
-    </row>
-    <row r="423" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ423" s="5"/>
-    </row>
-    <row r="425" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ425" s="5"/>
-    </row>
-    <row r="427" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ427" s="5"/>
-    </row>
-    <row r="430" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ430" s="5"/>
-    </row>
-    <row r="431" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ431" s="5"/>
-    </row>
-    <row r="435" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT435"/>
-    </row>
-    <row r="436" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT436"/>
-      <c r="CJ436" s="5"/>
-    </row>
-    <row r="437" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT437"/>
-      <c r="CJ437" s="5"/>
-    </row>
-    <row r="438" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ438" s="5"/>
-    </row>
-    <row r="439" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ439" s="5"/>
-    </row>
-    <row r="440" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT440"/>
-    </row>
-    <row r="441" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ441" s="5"/>
-    </row>
-    <row r="443" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ443" s="5"/>
-    </row>
-    <row r="444" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ444" s="5"/>
-    </row>
-    <row r="446" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ446" s="5"/>
-    </row>
-    <row r="447" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ447" s="5"/>
-    </row>
-    <row r="448" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ448" s="5"/>
-    </row>
-    <row r="449" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ449" s="5"/>
-    </row>
-    <row r="450" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ450" s="5"/>
-    </row>
-    <row r="451" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ451" s="5"/>
-    </row>
-    <row r="452" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ452" s="5"/>
-    </row>
-    <row r="454" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT454"/>
-    </row>
-    <row r="455" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ455" s="5"/>
-    </row>
-    <row r="456" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ456" s="5"/>
-    </row>
-    <row r="489" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS489" s="15"/>
-      <c r="BT489" s="16"/>
-    </row>
-    <row r="490" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CM66" s="3"/>
+    </row>
+    <row r="69" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL69" s="5"/>
+    </row>
+    <row r="70" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL70" s="5"/>
+    </row>
+    <row r="76" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL76" s="5"/>
+    </row>
+    <row r="77" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL77" s="5"/>
+    </row>
+    <row r="79" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL79" s="5"/>
+    </row>
+    <row r="80" spans="13:91" x14ac:dyDescent="0.25">
+      <c r="CL80" s="5"/>
+    </row>
+    <row r="81" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL81" s="5"/>
+    </row>
+    <row r="82" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL82" s="5"/>
+    </row>
+    <row r="83" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV83"/>
+    </row>
+    <row r="84" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV84"/>
+    </row>
+    <row r="85" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV85"/>
+      <c r="CL85" s="5"/>
+    </row>
+    <row r="86" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL86" s="5"/>
+    </row>
+    <row r="87" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL87" s="5"/>
+    </row>
+    <row r="88" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV88"/>
+    </row>
+    <row r="89" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL89" s="5"/>
+    </row>
+    <row r="93" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV93"/>
+    </row>
+    <row r="94" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL94" s="5"/>
+    </row>
+    <row r="102" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL102" s="5"/>
+    </row>
+    <row r="103" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL103" s="5"/>
+    </row>
+    <row r="104" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV104"/>
+    </row>
+    <row r="109" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV109"/>
+    </row>
+    <row r="110" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV110"/>
+      <c r="CL110" s="5"/>
+    </row>
+    <row r="111" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL111" s="5"/>
+    </row>
+    <row r="112" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL112" s="5"/>
+    </row>
+    <row r="113" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL113" s="5"/>
+    </row>
+    <row r="114" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL114" s="5"/>
+    </row>
+    <row r="115" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV115"/>
+    </row>
+    <row r="116" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL116" s="5"/>
+    </row>
+    <row r="117" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL117" s="5"/>
+    </row>
+    <row r="118" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL118" s="5"/>
+    </row>
+    <row r="119" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL119" s="5"/>
+    </row>
+    <row r="120" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV120"/>
+    </row>
+    <row r="121" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL121" s="5"/>
+    </row>
+    <row r="122" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL122" s="5"/>
+    </row>
+    <row r="123" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL123" s="5"/>
+    </row>
+    <row r="124" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL124" s="5"/>
+    </row>
+    <row r="127" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL127" s="5"/>
+    </row>
+    <row r="128" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL128" s="5"/>
+    </row>
+    <row r="129" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL129" s="5"/>
+    </row>
+    <row r="130" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL130" s="5"/>
+    </row>
+    <row r="131" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL131" s="5"/>
+    </row>
+    <row r="133" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV133"/>
+    </row>
+    <row r="134" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL134" s="5"/>
+    </row>
+    <row r="135" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL135" s="5"/>
+    </row>
+    <row r="136" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL136" s="5"/>
+    </row>
+    <row r="137" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL137" s="5"/>
+    </row>
+    <row r="141" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL141" s="5"/>
+    </row>
+    <row r="143" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV143"/>
+    </row>
+    <row r="144" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV144"/>
+      <c r="CL144" s="5"/>
+    </row>
+    <row r="145" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL145" s="5"/>
+    </row>
+    <row r="146" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL146" s="5"/>
+    </row>
+    <row r="147" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL147" s="5"/>
+    </row>
+    <row r="148" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL148" s="5"/>
+    </row>
+    <row r="150" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV150"/>
+    </row>
+    <row r="151" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL151" s="5"/>
+    </row>
+    <row r="152" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL152" s="5"/>
+    </row>
+    <row r="154" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL154" s="5"/>
+    </row>
+    <row r="155" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL155" s="5"/>
+    </row>
+    <row r="157" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV157"/>
+    </row>
+    <row r="158" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL158" s="5"/>
+    </row>
+    <row r="161" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL161" s="5"/>
+    </row>
+    <row r="162" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL162" s="5"/>
+    </row>
+    <row r="165" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL165" s="5"/>
+    </row>
+    <row r="167" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL167" s="5"/>
+    </row>
+    <row r="169" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV169"/>
+    </row>
+    <row r="170" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL170" s="5"/>
+    </row>
+    <row r="171" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL171" s="5"/>
+    </row>
+    <row r="173" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL173" s="5"/>
+    </row>
+    <row r="174" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL174" s="5"/>
+    </row>
+    <row r="175" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL175" s="5"/>
+    </row>
+    <row r="180" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL180" s="5"/>
+    </row>
+    <row r="181" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL181" s="5"/>
+    </row>
+    <row r="184" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL184" s="5"/>
+    </row>
+    <row r="185" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL185" s="5"/>
+    </row>
+    <row r="189" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL189" s="5"/>
+    </row>
+    <row r="193" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL193" s="5"/>
+    </row>
+    <row r="195" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL195" s="5"/>
+    </row>
+    <row r="196" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL196" s="5"/>
+    </row>
+    <row r="198" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL198" s="5"/>
+    </row>
+    <row r="199" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL199" s="5"/>
+    </row>
+    <row r="201" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV201"/>
+    </row>
+    <row r="202" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV202"/>
+      <c r="CL202" s="5"/>
+    </row>
+    <row r="203" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL203" s="5"/>
+    </row>
+    <row r="205" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL205" s="5"/>
+    </row>
+    <row r="214" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV214"/>
+    </row>
+    <row r="215" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV215"/>
+      <c r="CL215" s="5"/>
+    </row>
+    <row r="216" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL216" s="5"/>
+    </row>
+    <row r="217" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL217" s="5"/>
+    </row>
+    <row r="218" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV218"/>
+    </row>
+    <row r="219" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV219"/>
+      <c r="CL219" s="5"/>
+    </row>
+    <row r="220" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL220" s="5"/>
+    </row>
+    <row r="222" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV222"/>
+    </row>
+    <row r="223" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV223"/>
+      <c r="CL223" s="5"/>
+    </row>
+    <row r="224" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL224" s="5"/>
+    </row>
+    <row r="226" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV226"/>
+    </row>
+    <row r="227" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL227" s="5"/>
+    </row>
+    <row r="230" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL230" s="5"/>
+    </row>
+    <row r="234" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL234" s="5"/>
+    </row>
+    <row r="236" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV236"/>
+    </row>
+    <row r="237" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL237" s="5"/>
+    </row>
+    <row r="244" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV244"/>
+    </row>
+    <row r="245" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL245" s="5"/>
+    </row>
+    <row r="246" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL246" s="5"/>
+    </row>
+    <row r="248" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV248"/>
+    </row>
+    <row r="249" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV249"/>
+      <c r="CL249" s="5"/>
+    </row>
+    <row r="250" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL250" s="5"/>
+    </row>
+    <row r="256" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV256"/>
+    </row>
+    <row r="257" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV257"/>
+      <c r="CL257" s="5"/>
+    </row>
+    <row r="258" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV258"/>
+      <c r="CL258" s="5"/>
+    </row>
+    <row r="259" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL259" s="5"/>
+    </row>
+    <row r="264" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV264"/>
+    </row>
+    <row r="265" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV265"/>
+    </row>
+    <row r="269" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV269"/>
+    </row>
+    <row r="270" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL270" s="5"/>
+    </row>
+    <row r="271" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV271"/>
+    </row>
+    <row r="272" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL272" s="5"/>
+    </row>
+    <row r="282" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV282"/>
+    </row>
+    <row r="283" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL283" s="5"/>
+    </row>
+    <row r="285" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV285"/>
+    </row>
+    <row r="286" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL286" s="5"/>
+    </row>
+    <row r="294" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV294"/>
+    </row>
+    <row r="295" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL295" s="5"/>
+    </row>
+    <row r="299" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV299"/>
+    </row>
+    <row r="300" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL300" s="5"/>
+    </row>
+    <row r="302" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV302"/>
+    </row>
+    <row r="303" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL303" s="5"/>
+    </row>
+    <row r="319" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV319"/>
+    </row>
+    <row r="320" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV320"/>
+      <c r="CL320" s="5"/>
+    </row>
+    <row r="321" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV321"/>
+      <c r="CL321" s="5"/>
+    </row>
+    <row r="322" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV322"/>
+      <c r="CL322" s="5"/>
+    </row>
+    <row r="323" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV323"/>
+    </row>
+    <row r="325" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV325"/>
+    </row>
+    <row r="326" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV326"/>
+      <c r="CL326" s="5"/>
+    </row>
+    <row r="327" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV327"/>
+      <c r="CL327" s="5"/>
+    </row>
+    <row r="328" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL328" s="5"/>
+    </row>
+    <row r="332" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV332"/>
+    </row>
+    <row r="333" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL333" s="5"/>
+    </row>
+    <row r="335" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV335"/>
+    </row>
+    <row r="336" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV336"/>
+      <c r="CL336" s="5"/>
+    </row>
+    <row r="337" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV337"/>
+      <c r="CL337" s="5"/>
+    </row>
+    <row r="338" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL338" s="5"/>
+    </row>
+    <row r="354" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV354"/>
+    </row>
+    <row r="355" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL355" s="5"/>
+    </row>
+    <row r="363" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL363" s="5"/>
+    </row>
+    <row r="364" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL364" s="5"/>
+    </row>
+    <row r="365" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL365" s="5"/>
+    </row>
+    <row r="366" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL366" s="5"/>
+    </row>
+    <row r="367" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL367" s="5"/>
+    </row>
+    <row r="369" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV369"/>
+    </row>
+    <row r="370" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL370" s="5"/>
+    </row>
+    <row r="371" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV371"/>
+    </row>
+    <row r="372" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV372"/>
+      <c r="CL372" s="5"/>
+    </row>
+    <row r="373" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL373" s="5"/>
+    </row>
+    <row r="375" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV375"/>
+    </row>
+    <row r="376" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV376"/>
+      <c r="CL376" s="5"/>
+    </row>
+    <row r="377" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV377"/>
+      <c r="CL377" s="5"/>
+    </row>
+    <row r="378" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL378" s="5"/>
+    </row>
+    <row r="380" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL380" s="5"/>
+    </row>
+    <row r="382" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL382" s="5"/>
+    </row>
+    <row r="384" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL384" s="5"/>
+    </row>
+    <row r="387" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL387" s="5"/>
+    </row>
+    <row r="388" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL388" s="5"/>
+    </row>
+    <row r="389" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL389" s="5"/>
+    </row>
+    <row r="390" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL390" s="5"/>
+    </row>
+    <row r="391" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL391" s="5"/>
+    </row>
+    <row r="392" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL392" s="5"/>
+    </row>
+    <row r="393" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV393"/>
+    </row>
+    <row r="394" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV394"/>
+      <c r="CL394" s="5"/>
+    </row>
+    <row r="395" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV395"/>
+      <c r="CL395" s="5"/>
+    </row>
+    <row r="396" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL396" s="5"/>
+    </row>
+    <row r="397" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL397" s="5"/>
+    </row>
+    <row r="398" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL398" s="5"/>
+    </row>
+    <row r="399" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL399" s="5"/>
+    </row>
+    <row r="401" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL401" s="5"/>
+    </row>
+    <row r="402" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL402" s="5"/>
+    </row>
+    <row r="403" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV403"/>
+    </row>
+    <row r="404" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV404"/>
+      <c r="CL404" s="5"/>
+    </row>
+    <row r="405" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV405"/>
+      <c r="CL405" s="5"/>
+    </row>
+    <row r="406" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL406" s="5"/>
+    </row>
+    <row r="407" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL407" s="5"/>
+    </row>
+    <row r="409" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL409" s="5"/>
+    </row>
+    <row r="410" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL410" s="5"/>
+    </row>
+    <row r="411" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV411"/>
+      <c r="CL411" s="5"/>
+    </row>
+    <row r="412" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV412"/>
+      <c r="CL412" s="5"/>
+    </row>
+    <row r="413" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL413" s="5"/>
+    </row>
+    <row r="414" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL414" s="5"/>
+    </row>
+    <row r="415" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL415" s="5"/>
+    </row>
+    <row r="417" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV417"/>
+      <c r="CL417" s="5"/>
+    </row>
+    <row r="418" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL418" s="5"/>
+    </row>
+    <row r="419" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL419" s="5"/>
+    </row>
+    <row r="421" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV421"/>
+      <c r="CL421" s="5"/>
+    </row>
+    <row r="422" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV422"/>
+      <c r="CL422" s="5"/>
+    </row>
+    <row r="423" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL423" s="5"/>
+    </row>
+    <row r="425" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL425" s="5"/>
+    </row>
+    <row r="427" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL427" s="5"/>
+    </row>
+    <row r="430" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL430" s="5"/>
+    </row>
+    <row r="431" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL431" s="5"/>
+    </row>
+    <row r="435" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV435"/>
+    </row>
+    <row r="436" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV436"/>
+      <c r="CL436" s="5"/>
+    </row>
+    <row r="437" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV437"/>
+      <c r="CL437" s="5"/>
+    </row>
+    <row r="438" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL438" s="5"/>
+    </row>
+    <row r="439" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL439" s="5"/>
+    </row>
+    <row r="440" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV440"/>
+    </row>
+    <row r="441" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL441" s="5"/>
+    </row>
+    <row r="443" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL443" s="5"/>
+    </row>
+    <row r="444" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL444" s="5"/>
+    </row>
+    <row r="446" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL446" s="5"/>
+    </row>
+    <row r="447" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL447" s="5"/>
+    </row>
+    <row r="448" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL448" s="5"/>
+    </row>
+    <row r="449" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL449" s="5"/>
+    </row>
+    <row r="450" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL450" s="5"/>
+    </row>
+    <row r="451" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL451" s="5"/>
+    </row>
+    <row r="452" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL452" s="5"/>
+    </row>
+    <row r="454" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV454"/>
+    </row>
+    <row r="455" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL455" s="5"/>
+    </row>
+    <row r="456" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL456" s="5"/>
+    </row>
+    <row r="489" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU489" s="15"/>
+      <c r="BV489" s="16"/>
+    </row>
+    <row r="490" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H490" s="15"/>
-      <c r="CJ490" s="15"/>
-    </row>
-    <row r="496" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT496"/>
-    </row>
-    <row r="497" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT497"/>
-      <c r="CJ497" s="5"/>
-    </row>
-    <row r="498" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT498"/>
-      <c r="CJ498" s="5"/>
-    </row>
-    <row r="499" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ499" s="5"/>
-    </row>
-    <row r="516" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT516"/>
-    </row>
-    <row r="517" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ517" s="5"/>
-    </row>
-    <row r="549" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT549"/>
-    </row>
-    <row r="550" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT550"/>
-      <c r="CJ550" s="5"/>
-    </row>
-    <row r="551" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ551" s="5"/>
-    </row>
-    <row r="567" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT567"/>
-    </row>
-    <row r="568" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ568" s="5"/>
-    </row>
-    <row r="574" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT574"/>
-    </row>
-    <row r="575" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT575"/>
-      <c r="CJ575" s="5"/>
-    </row>
-    <row r="576" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ576" s="5"/>
-    </row>
-    <row r="581" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT581"/>
-    </row>
-    <row r="582" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT582"/>
-      <c r="CJ582" s="5"/>
-    </row>
-    <row r="583" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT583"/>
-      <c r="CJ583" s="5"/>
-    </row>
-    <row r="584" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT584"/>
-      <c r="CJ584" s="5"/>
-    </row>
-    <row r="585" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT585"/>
-      <c r="CJ585" s="5"/>
-    </row>
-    <row r="586" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT586"/>
-      <c r="CJ586" s="5"/>
-    </row>
-    <row r="587" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT587"/>
-      <c r="CJ587" s="5"/>
-    </row>
-    <row r="588" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT588"/>
-      <c r="CJ588" s="5"/>
-    </row>
-    <row r="589" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT589"/>
-      <c r="CJ589" s="5"/>
-    </row>
-    <row r="590" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT590"/>
-      <c r="CJ590" s="5"/>
-    </row>
-    <row r="591" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT591"/>
-      <c r="CJ591" s="5"/>
-    </row>
-    <row r="592" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT592"/>
-      <c r="CJ592" s="5"/>
-    </row>
-    <row r="593" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT593"/>
-      <c r="CJ593" s="5"/>
-    </row>
-    <row r="594" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT594"/>
-      <c r="CJ594" s="5"/>
-    </row>
-    <row r="595" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT595"/>
-      <c r="CJ595" s="5"/>
-    </row>
-    <row r="596" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT596"/>
-      <c r="CJ596" s="5"/>
-    </row>
-    <row r="597" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ597" s="5"/>
-    </row>
-    <row r="601" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT601"/>
-    </row>
-    <row r="602" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT602"/>
-      <c r="CJ602" s="5"/>
-    </row>
-    <row r="603" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ603" s="5"/>
-    </row>
-    <row r="604" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT604"/>
-    </row>
-    <row r="605" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ605" s="5"/>
-    </row>
-    <row r="608" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT608"/>
-    </row>
-    <row r="609" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT609"/>
-      <c r="CJ609" s="5"/>
-    </row>
-    <row r="610" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ610" s="5"/>
-    </row>
-    <row r="641" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT641"/>
-    </row>
-    <row r="642" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT642"/>
-      <c r="CJ642" s="5"/>
-    </row>
-    <row r="643" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT643"/>
-      <c r="CJ643" s="5"/>
-    </row>
-    <row r="644" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT644"/>
-      <c r="CJ644" s="5"/>
-    </row>
-    <row r="645" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT645"/>
-      <c r="CJ645" s="5"/>
-    </row>
-    <row r="646" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT646"/>
-      <c r="CJ646" s="5"/>
-    </row>
-    <row r="647" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT647"/>
-      <c r="CJ647" s="5"/>
-    </row>
-    <row r="648" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT648"/>
-      <c r="CJ648" s="5"/>
-    </row>
-    <row r="649" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ649" s="5"/>
-    </row>
-    <row r="651" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT651"/>
-    </row>
-    <row r="652" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ652" s="5"/>
-    </row>
-    <row r="656" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT656"/>
-    </row>
-    <row r="657" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ657" s="5"/>
-    </row>
-    <row r="660" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT660"/>
-    </row>
-    <row r="661" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT661"/>
-      <c r="CJ661" s="5"/>
-    </row>
-    <row r="662" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT662"/>
-      <c r="CJ662" s="5"/>
-    </row>
-    <row r="663" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT663"/>
-      <c r="CJ663" s="5"/>
-    </row>
-    <row r="664" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ664" s="5"/>
-    </row>
-    <row r="671" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT671"/>
-    </row>
-    <row r="672" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ672" s="5"/>
-    </row>
-    <row r="675" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT675"/>
-    </row>
-    <row r="676" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT676"/>
-      <c r="CJ676" s="5"/>
-    </row>
-    <row r="677" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT677"/>
-      <c r="CJ677" s="5"/>
-    </row>
-    <row r="678" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT678"/>
-      <c r="CJ678" s="5"/>
-    </row>
-    <row r="679" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ679" s="5"/>
-    </row>
-    <row r="681" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT681"/>
-    </row>
-    <row r="682" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT682"/>
-      <c r="CJ682" s="5"/>
-    </row>
-    <row r="683" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ683" s="5"/>
-    </row>
-    <row r="684" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ684">
+      <c r="CL490" s="15"/>
+    </row>
+    <row r="496" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV496"/>
+    </row>
+    <row r="497" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV497"/>
+      <c r="CL497" s="5"/>
+    </row>
+    <row r="498" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV498"/>
+      <c r="CL498" s="5"/>
+    </row>
+    <row r="499" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL499" s="5"/>
+    </row>
+    <row r="516" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV516"/>
+    </row>
+    <row r="517" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL517" s="5"/>
+    </row>
+    <row r="549" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV549"/>
+    </row>
+    <row r="550" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV550"/>
+      <c r="CL550" s="5"/>
+    </row>
+    <row r="551" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL551" s="5"/>
+    </row>
+    <row r="567" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV567"/>
+    </row>
+    <row r="568" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL568" s="5"/>
+    </row>
+    <row r="574" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV574"/>
+    </row>
+    <row r="575" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV575"/>
+      <c r="CL575" s="5"/>
+    </row>
+    <row r="576" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL576" s="5"/>
+    </row>
+    <row r="581" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV581"/>
+    </row>
+    <row r="582" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV582"/>
+      <c r="CL582" s="5"/>
+    </row>
+    <row r="583" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV583"/>
+      <c r="CL583" s="5"/>
+    </row>
+    <row r="584" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV584"/>
+      <c r="CL584" s="5"/>
+    </row>
+    <row r="585" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV585"/>
+      <c r="CL585" s="5"/>
+    </row>
+    <row r="586" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV586"/>
+      <c r="CL586" s="5"/>
+    </row>
+    <row r="587" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV587"/>
+      <c r="CL587" s="5"/>
+    </row>
+    <row r="588" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV588"/>
+      <c r="CL588" s="5"/>
+    </row>
+    <row r="589" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV589"/>
+      <c r="CL589" s="5"/>
+    </row>
+    <row r="590" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV590"/>
+      <c r="CL590" s="5"/>
+    </row>
+    <row r="591" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV591"/>
+      <c r="CL591" s="5"/>
+    </row>
+    <row r="592" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV592"/>
+      <c r="CL592" s="5"/>
+    </row>
+    <row r="593" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV593"/>
+      <c r="CL593" s="5"/>
+    </row>
+    <row r="594" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV594"/>
+      <c r="CL594" s="5"/>
+    </row>
+    <row r="595" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV595"/>
+      <c r="CL595" s="5"/>
+    </row>
+    <row r="596" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV596"/>
+      <c r="CL596" s="5"/>
+    </row>
+    <row r="597" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL597" s="5"/>
+    </row>
+    <row r="601" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV601"/>
+    </row>
+    <row r="602" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV602"/>
+      <c r="CL602" s="5"/>
+    </row>
+    <row r="603" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL603" s="5"/>
+    </row>
+    <row r="604" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV604"/>
+    </row>
+    <row r="605" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL605" s="5"/>
+    </row>
+    <row r="608" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV608"/>
+    </row>
+    <row r="609" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV609"/>
+      <c r="CL609" s="5"/>
+    </row>
+    <row r="610" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL610" s="5"/>
+    </row>
+    <row r="641" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV641"/>
+    </row>
+    <row r="642" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV642"/>
+      <c r="CL642" s="5"/>
+    </row>
+    <row r="643" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV643"/>
+      <c r="CL643" s="5"/>
+    </row>
+    <row r="644" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV644"/>
+      <c r="CL644" s="5"/>
+    </row>
+    <row r="645" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV645"/>
+      <c r="CL645" s="5"/>
+    </row>
+    <row r="646" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV646"/>
+      <c r="CL646" s="5"/>
+    </row>
+    <row r="647" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV647"/>
+      <c r="CL647" s="5"/>
+    </row>
+    <row r="648" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV648"/>
+      <c r="CL648" s="5"/>
+    </row>
+    <row r="649" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL649" s="5"/>
+    </row>
+    <row r="651" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV651"/>
+    </row>
+    <row r="652" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL652" s="5"/>
+    </row>
+    <row r="656" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV656"/>
+    </row>
+    <row r="657" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL657" s="5"/>
+    </row>
+    <row r="660" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV660"/>
+    </row>
+    <row r="661" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV661"/>
+      <c r="CL661" s="5"/>
+    </row>
+    <row r="662" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV662"/>
+      <c r="CL662" s="5"/>
+    </row>
+    <row r="663" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV663"/>
+      <c r="CL663" s="5"/>
+    </row>
+    <row r="664" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL664" s="5"/>
+    </row>
+    <row r="671" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV671"/>
+    </row>
+    <row r="672" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL672" s="5"/>
+    </row>
+    <row r="675" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV675"/>
+    </row>
+    <row r="676" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV676"/>
+      <c r="CL676" s="5"/>
+    </row>
+    <row r="677" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV677"/>
+      <c r="CL677" s="5"/>
+    </row>
+    <row r="678" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV678"/>
+      <c r="CL678" s="5"/>
+    </row>
+    <row r="679" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL679" s="5"/>
+    </row>
+    <row r="681" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV681"/>
+    </row>
+    <row r="682" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV682"/>
+      <c r="CL682" s="5"/>
+    </row>
+    <row r="683" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL683" s="5"/>
+    </row>
+    <row r="684" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL684">
         <v>0.15</v>
       </c>
     </row>
-    <row r="686" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ686">
+    <row r="686" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL686">
         <v>0.2</v>
       </c>
     </row>
-    <row r="687" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ687">
+    <row r="687" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL687">
         <v>0.1</v>
       </c>
     </row>
-    <row r="689" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ689">
+    <row r="689" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL689">
         <v>0.2</v>
       </c>
     </row>
-    <row r="696" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ696">
+    <row r="696" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL696">
         <v>1</v>
       </c>
     </row>
-    <row r="698" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ698">
+    <row r="698" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL698">
         <v>0.4</v>
       </c>
     </row>
-    <row r="699" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ699">
+    <row r="699" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL699">
         <v>0.6</v>
       </c>
     </row>
-    <row r="702" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ702">
+    <row r="702" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL702">
         <v>0.5</v>
       </c>
     </row>
-    <row r="703" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ703">
+    <row r="703" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL703">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="704" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ704">
+    <row r="704" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL704">
         <v>0.2</v>
       </c>
     </row>
-    <row r="707" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT707"/>
-    </row>
-    <row r="708" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT708"/>
-      <c r="CJ708" s="5"/>
-    </row>
-    <row r="709" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT709"/>
-      <c r="CJ709" s="5"/>
-    </row>
-    <row r="710" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT710"/>
-      <c r="CJ710" s="5"/>
-    </row>
-    <row r="711" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT711"/>
-      <c r="CJ711" s="5"/>
-    </row>
-    <row r="712" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT712"/>
-      <c r="CJ712" s="5"/>
-    </row>
-    <row r="713" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT713"/>
-      <c r="CJ713" s="5"/>
-    </row>
-    <row r="714" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT714"/>
-      <c r="CJ714" s="5"/>
-    </row>
-    <row r="715" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT715"/>
-      <c r="CJ715" s="5"/>
-    </row>
-    <row r="716" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ716" s="5"/>
-    </row>
-    <row r="717" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT717"/>
-    </row>
-    <row r="718" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ718" s="5"/>
-    </row>
-    <row r="727" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT727"/>
-    </row>
-    <row r="728" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT728"/>
-      <c r="CJ728" s="5"/>
-    </row>
-    <row r="729" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT729"/>
-      <c r="CJ729" s="5"/>
-    </row>
-    <row r="730" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT730"/>
-      <c r="CJ730" s="5"/>
-    </row>
-    <row r="731" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT731"/>
-      <c r="CJ731" s="5"/>
-    </row>
-    <row r="732" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT732"/>
-      <c r="CJ732" s="5"/>
-    </row>
-    <row r="733" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT733"/>
-      <c r="CJ733" s="5"/>
-    </row>
-    <row r="734" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT734"/>
-      <c r="CJ734" s="5"/>
-    </row>
-    <row r="735" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ735" s="5"/>
-    </row>
-    <row r="736" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT736"/>
-    </row>
-    <row r="737" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ737" s="5"/>
-    </row>
-    <row r="742" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT742"/>
-    </row>
-    <row r="743" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT743"/>
-      <c r="CJ743" s="5"/>
-    </row>
-    <row r="744" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ744" s="5"/>
-    </row>
-    <row r="745" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT745"/>
-    </row>
-    <row r="746" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT746"/>
-      <c r="CJ746" s="5"/>
-    </row>
-    <row r="747" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ747" s="5"/>
-    </row>
-    <row r="748" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT748"/>
-    </row>
-    <row r="749" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT749"/>
-      <c r="CJ749" s="5"/>
-    </row>
-    <row r="750" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT750"/>
-      <c r="CJ750" s="5"/>
-    </row>
-    <row r="751" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT751"/>
-      <c r="CJ751" s="5"/>
-    </row>
-    <row r="752" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ752" s="5"/>
-    </row>
-    <row r="756" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT756"/>
-    </row>
-    <row r="757" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT757"/>
-      <c r="CJ757" s="5"/>
-    </row>
-    <row r="758" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT758"/>
-      <c r="CJ758" s="5"/>
-    </row>
-    <row r="759" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ759" s="5"/>
-    </row>
-    <row r="760" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT760"/>
-    </row>
-    <row r="761" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ761" s="5"/>
-    </row>
-    <row r="762" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS762" s="15"/>
-      <c r="BT762" s="16"/>
-    </row>
-    <row r="763" spans="8:88" x14ac:dyDescent="0.25">
+    <row r="707" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV707"/>
+    </row>
+    <row r="708" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV708"/>
+      <c r="CL708" s="5"/>
+    </row>
+    <row r="709" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV709"/>
+      <c r="CL709" s="5"/>
+    </row>
+    <row r="710" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV710"/>
+      <c r="CL710" s="5"/>
+    </row>
+    <row r="711" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV711"/>
+      <c r="CL711" s="5"/>
+    </row>
+    <row r="712" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV712"/>
+      <c r="CL712" s="5"/>
+    </row>
+    <row r="713" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV713"/>
+      <c r="CL713" s="5"/>
+    </row>
+    <row r="714" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV714"/>
+      <c r="CL714" s="5"/>
+    </row>
+    <row r="715" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV715"/>
+      <c r="CL715" s="5"/>
+    </row>
+    <row r="716" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL716" s="5"/>
+    </row>
+    <row r="717" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV717"/>
+    </row>
+    <row r="718" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL718" s="5"/>
+    </row>
+    <row r="727" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV727"/>
+    </row>
+    <row r="728" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV728"/>
+      <c r="CL728" s="5"/>
+    </row>
+    <row r="729" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV729"/>
+      <c r="CL729" s="5"/>
+    </row>
+    <row r="730" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV730"/>
+      <c r="CL730" s="5"/>
+    </row>
+    <row r="731" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV731"/>
+      <c r="CL731" s="5"/>
+    </row>
+    <row r="732" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV732"/>
+      <c r="CL732" s="5"/>
+    </row>
+    <row r="733" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV733"/>
+      <c r="CL733" s="5"/>
+    </row>
+    <row r="734" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV734"/>
+      <c r="CL734" s="5"/>
+    </row>
+    <row r="735" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL735" s="5"/>
+    </row>
+    <row r="736" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV736"/>
+    </row>
+    <row r="737" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL737" s="5"/>
+    </row>
+    <row r="742" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV742"/>
+    </row>
+    <row r="743" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV743"/>
+      <c r="CL743" s="5"/>
+    </row>
+    <row r="744" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL744" s="5"/>
+    </row>
+    <row r="745" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV745"/>
+    </row>
+    <row r="746" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV746"/>
+      <c r="CL746" s="5"/>
+    </row>
+    <row r="747" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL747" s="5"/>
+    </row>
+    <row r="748" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV748"/>
+    </row>
+    <row r="749" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV749"/>
+      <c r="CL749" s="5"/>
+    </row>
+    <row r="750" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV750"/>
+      <c r="CL750" s="5"/>
+    </row>
+    <row r="751" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV751"/>
+      <c r="CL751" s="5"/>
+    </row>
+    <row r="752" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL752" s="5"/>
+    </row>
+    <row r="756" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV756"/>
+    </row>
+    <row r="757" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV757"/>
+      <c r="CL757" s="5"/>
+    </row>
+    <row r="758" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV758"/>
+      <c r="CL758" s="5"/>
+    </row>
+    <row r="759" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL759" s="5"/>
+    </row>
+    <row r="760" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV760"/>
+    </row>
+    <row r="761" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL761" s="5"/>
+    </row>
+    <row r="762" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU762" s="15"/>
+      <c r="BV762" s="16"/>
+    </row>
+    <row r="763" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H763" s="15"/>
-      <c r="CJ763" s="15"/>
-    </row>
-    <row r="780" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT780"/>
-    </row>
-    <row r="781" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT781"/>
-      <c r="CJ781" s="5"/>
-    </row>
-    <row r="782" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT782"/>
-      <c r="CJ782" s="5"/>
-    </row>
-    <row r="783" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT783"/>
-      <c r="CJ783" s="5"/>
-    </row>
-    <row r="784" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ784" s="5"/>
-    </row>
-    <row r="785" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT785"/>
-    </row>
-    <row r="786" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT786"/>
-      <c r="CJ786" s="5"/>
-    </row>
-    <row r="787" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS787" s="15"/>
-      <c r="BT787" s="16"/>
-      <c r="CJ787" s="5"/>
-    </row>
-    <row r="788" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CL763" s="15"/>
+    </row>
+    <row r="780" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV780"/>
+    </row>
+    <row r="781" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV781"/>
+      <c r="CL781" s="5"/>
+    </row>
+    <row r="782" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV782"/>
+      <c r="CL782" s="5"/>
+    </row>
+    <row r="783" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV783"/>
+      <c r="CL783" s="5"/>
+    </row>
+    <row r="784" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL784" s="5"/>
+    </row>
+    <row r="785" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV785"/>
+    </row>
+    <row r="786" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV786"/>
+      <c r="CL786" s="5"/>
+    </row>
+    <row r="787" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU787" s="15"/>
+      <c r="BV787" s="16"/>
+      <c r="CL787" s="5"/>
+    </row>
+    <row r="788" spans="8:90" x14ac:dyDescent="0.25">
       <c r="H788" s="15"/>
-      <c r="CJ788" s="15"/>
-    </row>
-    <row r="791" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT791"/>
-    </row>
-    <row r="792" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT792"/>
-      <c r="CJ792" s="5"/>
-    </row>
-    <row r="793" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT793"/>
-      <c r="CJ793" s="5"/>
-    </row>
-    <row r="794" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT794"/>
-      <c r="CJ794" s="5"/>
-    </row>
-    <row r="795" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT795"/>
-      <c r="CJ795" s="5"/>
-    </row>
-    <row r="796" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT796"/>
-      <c r="CJ796" s="5"/>
-    </row>
-    <row r="797" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT797"/>
-      <c r="CJ797" s="5"/>
-    </row>
-    <row r="798" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT798"/>
-      <c r="CJ798" s="5"/>
-    </row>
-    <row r="799" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ799" s="5"/>
-    </row>
-    <row r="801" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT801"/>
-    </row>
-    <row r="802" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT802"/>
-      <c r="CJ802" s="5"/>
-    </row>
-    <row r="803" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT803"/>
-      <c r="CJ803" s="5"/>
-    </row>
-    <row r="804" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT804"/>
-      <c r="CJ804" s="5"/>
-    </row>
-    <row r="805" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT805"/>
-      <c r="CJ805" s="5"/>
-    </row>
-    <row r="806" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT806"/>
-      <c r="CJ806" s="5"/>
-    </row>
-    <row r="807" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ807" s="5"/>
-    </row>
-    <row r="808" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT808"/>
-    </row>
-    <row r="809" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT809"/>
-      <c r="CJ809" s="5"/>
-    </row>
-    <row r="810" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT810"/>
-      <c r="CJ810" s="5"/>
-    </row>
-    <row r="811" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT811"/>
-      <c r="CJ811" s="5"/>
-    </row>
-    <row r="812" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT812"/>
-      <c r="CJ812" s="5"/>
-    </row>
-    <row r="813" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT813"/>
-      <c r="CJ813" s="5"/>
-    </row>
-    <row r="814" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT814"/>
-      <c r="CJ814" s="5"/>
-    </row>
-    <row r="815" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT815"/>
-      <c r="CJ815" s="5"/>
-    </row>
-    <row r="816" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT816"/>
-      <c r="CJ816" s="5"/>
-    </row>
-    <row r="817" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT817"/>
-      <c r="CJ817" s="5"/>
-    </row>
-    <row r="818" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT818"/>
-      <c r="CJ818" s="5"/>
-    </row>
-    <row r="819" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT819"/>
-      <c r="CJ819" s="5"/>
-    </row>
-    <row r="820" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT820"/>
-      <c r="CJ820" s="5"/>
-    </row>
-    <row r="821" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT821"/>
-      <c r="CJ821" s="5"/>
-    </row>
-    <row r="822" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT822"/>
-      <c r="CJ822" s="5"/>
-    </row>
-    <row r="823" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT823"/>
-      <c r="CJ823" s="5"/>
-    </row>
-    <row r="824" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT824"/>
-      <c r="CJ824" s="5"/>
-    </row>
-    <row r="825" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT825"/>
-      <c r="CJ825" s="5"/>
-    </row>
-    <row r="826" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT826"/>
-      <c r="CJ826" s="5"/>
-    </row>
-    <row r="827" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT827"/>
-      <c r="CJ827" s="5"/>
-    </row>
-    <row r="828" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT828"/>
-      <c r="CJ828" s="5"/>
-    </row>
-    <row r="829" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT829"/>
-      <c r="CJ829" s="5"/>
-    </row>
-    <row r="830" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT830"/>
-      <c r="CJ830" s="5"/>
-    </row>
-    <row r="831" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT831"/>
-      <c r="CJ831" s="5"/>
-    </row>
-    <row r="832" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT832"/>
-      <c r="CJ832" s="5"/>
-    </row>
-    <row r="833" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT833"/>
-      <c r="CJ833" s="5"/>
-    </row>
-    <row r="834" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT834"/>
-      <c r="CJ834" s="5"/>
-    </row>
-    <row r="835" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT835"/>
-      <c r="CJ835" s="5"/>
-    </row>
-    <row r="836" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT836"/>
-      <c r="CJ836" s="5"/>
-    </row>
-    <row r="837" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT837"/>
-      <c r="CJ837" s="5"/>
-    </row>
-    <row r="838" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ838" s="5"/>
-    </row>
-    <row r="839" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT839"/>
-    </row>
-    <row r="840" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT840"/>
-      <c r="CJ840" s="5"/>
-    </row>
-    <row r="841" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT841"/>
-      <c r="CJ841" s="5"/>
-    </row>
-    <row r="842" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ842" s="5"/>
+      <c r="CL788" s="15"/>
+    </row>
+    <row r="791" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV791"/>
+    </row>
+    <row r="792" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV792"/>
+      <c r="CL792" s="5"/>
+    </row>
+    <row r="793" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV793"/>
+      <c r="CL793" s="5"/>
+    </row>
+    <row r="794" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV794"/>
+      <c r="CL794" s="5"/>
+    </row>
+    <row r="795" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV795"/>
+      <c r="CL795" s="5"/>
+    </row>
+    <row r="796" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV796"/>
+      <c r="CL796" s="5"/>
+    </row>
+    <row r="797" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV797"/>
+      <c r="CL797" s="5"/>
+    </row>
+    <row r="798" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV798"/>
+      <c r="CL798" s="5"/>
+    </row>
+    <row r="799" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL799" s="5"/>
+    </row>
+    <row r="801" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV801"/>
+    </row>
+    <row r="802" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV802"/>
+      <c r="CL802" s="5"/>
+    </row>
+    <row r="803" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV803"/>
+      <c r="CL803" s="5"/>
+    </row>
+    <row r="804" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV804"/>
+      <c r="CL804" s="5"/>
+    </row>
+    <row r="805" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV805"/>
+      <c r="CL805" s="5"/>
+    </row>
+    <row r="806" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV806"/>
+      <c r="CL806" s="5"/>
+    </row>
+    <row r="807" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL807" s="5"/>
+    </row>
+    <row r="808" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV808"/>
+    </row>
+    <row r="809" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV809"/>
+      <c r="CL809" s="5"/>
+    </row>
+    <row r="810" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV810"/>
+      <c r="CL810" s="5"/>
+    </row>
+    <row r="811" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV811"/>
+      <c r="CL811" s="5"/>
+    </row>
+    <row r="812" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV812"/>
+      <c r="CL812" s="5"/>
+    </row>
+    <row r="813" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV813"/>
+      <c r="CL813" s="5"/>
+    </row>
+    <row r="814" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV814"/>
+      <c r="CL814" s="5"/>
+    </row>
+    <row r="815" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV815"/>
+      <c r="CL815" s="5"/>
+    </row>
+    <row r="816" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV816"/>
+      <c r="CL816" s="5"/>
+    </row>
+    <row r="817" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV817"/>
+      <c r="CL817" s="5"/>
+    </row>
+    <row r="818" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV818"/>
+      <c r="CL818" s="5"/>
+    </row>
+    <row r="819" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV819"/>
+      <c r="CL819" s="5"/>
+    </row>
+    <row r="820" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV820"/>
+      <c r="CL820" s="5"/>
+    </row>
+    <row r="821" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV821"/>
+      <c r="CL821" s="5"/>
+    </row>
+    <row r="822" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV822"/>
+      <c r="CL822" s="5"/>
+    </row>
+    <row r="823" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV823"/>
+      <c r="CL823" s="5"/>
+    </row>
+    <row r="824" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV824"/>
+      <c r="CL824" s="5"/>
+    </row>
+    <row r="825" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV825"/>
+      <c r="CL825" s="5"/>
+    </row>
+    <row r="826" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV826"/>
+      <c r="CL826" s="5"/>
+    </row>
+    <row r="827" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV827"/>
+      <c r="CL827" s="5"/>
+    </row>
+    <row r="828" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV828"/>
+      <c r="CL828" s="5"/>
+    </row>
+    <row r="829" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV829"/>
+      <c r="CL829" s="5"/>
+    </row>
+    <row r="830" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV830"/>
+      <c r="CL830" s="5"/>
+    </row>
+    <row r="831" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV831"/>
+      <c r="CL831" s="5"/>
+    </row>
+    <row r="832" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV832"/>
+      <c r="CL832" s="5"/>
+    </row>
+    <row r="833" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV833"/>
+      <c r="CL833" s="5"/>
+    </row>
+    <row r="834" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV834"/>
+      <c r="CL834" s="5"/>
+    </row>
+    <row r="835" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV835"/>
+      <c r="CL835" s="5"/>
+    </row>
+    <row r="836" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV836"/>
+      <c r="CL836" s="5"/>
+    </row>
+    <row r="837" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV837"/>
+      <c r="CL837" s="5"/>
+    </row>
+    <row r="838" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL838" s="5"/>
+    </row>
+    <row r="839" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV839"/>
+    </row>
+    <row r="840" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV840"/>
+      <c r="CL840" s="5"/>
+    </row>
+    <row r="841" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV841"/>
+      <c r="CL841" s="5"/>
+    </row>
+    <row r="842" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL842" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
@@ -9075,37 +9305,37 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F1" t="s">
         <v>363</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>364</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>365</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>366</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>367</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>368</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>369</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>370</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>371</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -9119,43 +9349,43 @@
         <v>76</v>
       </c>
       <c r="E2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F2" t="s">
         <v>374</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>375</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>376</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>377</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>378</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>379</v>
-      </c>
-      <c r="K2" t="s">
-        <v>380</v>
       </c>
       <c r="L2" t="s">
         <v>52</v>
       </c>
       <c r="M2" t="s">
+        <v>380</v>
+      </c>
+      <c r="N2" t="s">
         <v>381</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>382</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="Q2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -9184,13 +9414,13 @@
         <v>115</v>
       </c>
       <c r="J3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K3" t="s">
         <v>116</v>
       </c>
       <c r="L3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M3" t="s">
         <v>115</v>
@@ -9199,13 +9429,32 @@
         <v>115</v>
       </c>
       <c r="O3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P3" t="s">
         <v>115</v>
       </c>
       <c r="Q3" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9261,7 +9510,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9272,10 +9521,10 @@
         <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9286,7 +9535,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D3" t="s">
         <v>124</v>
@@ -9321,22 +9570,22 @@
         <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E2" t="s">
         <v>71</v>
       </c>
       <c r="F2" t="s">
+        <v>387</v>
+      </c>
+      <c r="G2" t="s">
         <v>388</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>389</v>
       </c>
-      <c r="H2" t="s">
-        <v>390</v>
-      </c>
       <c r="I2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -9402,34 +9651,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C1" t="s">
         <v>391</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>392</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>393</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>394</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>395</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>396</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>397</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>398</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>399</v>
-      </c>
-      <c r="L1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -9437,34 +9686,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C2" t="s">
         <v>401</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>402</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>403</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>404</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>405</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>406</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>407</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>408</v>
       </c>
-      <c r="J2" t="s">
-        <v>409</v>
-      </c>
       <c r="K2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L2" t="s">
         <v>96</v>
@@ -9481,7 +9730,7 @@
         <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -9535,28 +9784,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C2" t="s">
         <v>76</v>
       </c>
       <c r="D2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E2" t="s">
         <v>411</v>
-      </c>
-      <c r="E2" t="s">
-        <v>412</v>
       </c>
       <c r="F2" t="s">
         <v>78</v>
       </c>
       <c r="G2" t="s">
+        <v>412</v>
+      </c>
+      <c r="H2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I2" t="s">
         <v>413</v>
-      </c>
-      <c r="H2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I2" t="s">
-        <v>414</v>
       </c>
       <c r="J2" t="s">
         <v>53</v>
@@ -9585,7 +9834,7 @@
         <v>117</v>
       </c>
       <c r="H3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I3" t="s">
         <v>117</v>
@@ -9622,28 +9871,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -9651,28 +9900,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -9706,28 +9955,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Diy优胜/第一届.xlsx
+++ b/Excel/Diy优胜/第一届.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D0BB17-0FC2-499A-9CDA-02E06D56811F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21F3018-391F-4E4C-86AC-D8C22133837B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="493">
   <si>
     <t>Id</t>
   </si>
@@ -1781,8 +1781,57 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>Target.UnitData.Name != \"流涟\"</t>
+    <t>生成下级流涟</t>
     <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"UnitId":"流涟","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"UserDirection","UserName":"时蒙"}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅自己</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己入场</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟标记</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成流涟</t>
+  </si>
+  <si>
+    <t>流涟标记自身</t>
+  </si>
+  <si>
+    <t>流涟回复技力</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>对Buff回复技力</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟可生成标记</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"目标技能":"流涟可生成标记","技力":1,"提示":1,"无视阻回":1}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟标记自身</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟可生成标记</t>
   </si>
 </sst>
 </file>
@@ -2405,7 +2454,8 @@
     <col min="33" max="33" width="15.83203125" customWidth="1"/>
     <col min="34" max="34" width="13.83203125" customWidth="1"/>
     <col min="35" max="35" width="34.5" customWidth="1"/>
-    <col min="36" max="37" width="9.83203125" customWidth="1"/>
+    <col min="36" max="36" width="20.1640625" customWidth="1"/>
+    <col min="37" max="37" width="9.83203125" customWidth="1"/>
     <col min="43" max="43" width="12.5" customWidth="1"/>
     <col min="50" max="50" width="24.33203125" customWidth="1"/>
     <col min="52" max="52" width="17.75" customWidth="1"/>
@@ -3147,6 +3197,12 @@
       <c r="AH6" s="2" t="s">
         <v>440</v>
       </c>
+      <c r="AI6" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>492</v>
+      </c>
       <c r="AK6">
         <v>0</v>
       </c>
@@ -3161,6 +3217,9 @@
       </c>
       <c r="AP6">
         <v>0.5</v>
+      </c>
+      <c r="AV6" s="2" t="s">
+        <v>464</v>
       </c>
       <c r="AW6">
         <v>0.25</v>
@@ -7241,9 +7300,7 @@
       <c r="C8" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>479</v>
-      </c>
+      <c r="H8" s="2"/>
       <c r="K8" s="5" t="s">
         <v>447</v>
       </c>
@@ -7257,7 +7314,7 @@
         <v>2</v>
       </c>
       <c r="AD8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF8">
         <v>1</v>
@@ -7291,49 +7348,135 @@
       <c r="CO9" s="2"/>
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="K10" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC10">
+        <v>2</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
+      </c>
       <c r="AG10" s="2"/>
+      <c r="AH10" s="2">
+        <v>1</v>
+      </c>
       <c r="AO10" s="2"/>
       <c r="AX10" s="2"/>
+      <c r="BD10">
+        <v>1</v>
+      </c>
       <c r="CG10" s="2"/>
       <c r="CL10" s="2"/>
       <c r="CN10" s="2"/>
       <c r="CO10" s="2"/>
+      <c r="CU10" s="2" t="s">
+        <v>481</v>
+      </c>
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="AG11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="AC11">
+        <v>2</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>482</v>
+      </c>
       <c r="AJ11" s="2"/>
       <c r="AO11" s="2"/>
-      <c r="BV11"/>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>2</v>
+      </c>
+      <c r="BD11">
+        <v>1</v>
+      </c>
+      <c r="BT11">
+        <v>0.1</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11" s="6">
+        <v>3</v>
+      </c>
+      <c r="BX11" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY11" s="6" t="s">
+        <v>480</v>
+      </c>
       <c r="CL11" s="5"/>
-      <c r="CN11" s="2"/>
+      <c r="CN11" s="2" t="s">
+        <v>485</v>
+      </c>
       <c r="CO11" s="2"/>
+      <c r="CR11">
+        <v>9999</v>
+      </c>
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="BV12" s="10"/>
-      <c r="BW12" s="10"/>
-      <c r="BX12" s="10"/>
-      <c r="BY12" s="10"/>
-      <c r="BZ12" s="10"/>
-      <c r="CA12" s="10"/>
-      <c r="CL12" s="7"/>
+      <c r="A12" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AD12">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="AJ12" s="2"/>
+      <c r="AO12" s="2"/>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>2</v>
+      </c>
+      <c r="BD12">
+        <v>1</v>
+      </c>
+      <c r="BV12"/>
+      <c r="CL12" s="5"/>
+      <c r="CN12" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="CO12" s="2"/>
+      <c r="CR12">
+        <v>9999</v>
+      </c>
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="K13" s="7"/>
@@ -9457,8 +9600,13 @@
         <v>467</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="P6"/>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K9"/>
@@ -9497,7 +9645,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -9539,6 +9687,20 @@
       </c>
       <c r="D3" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>490</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Diy优胜/第一届.xlsx
+++ b/Excel/Diy优胜/第一届.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21F3018-391F-4E4C-86AC-D8C22133837B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802CC9DB-65F8-462A-93D4-900D8FF2A4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="494">
   <si>
     <t>Id</t>
   </si>
@@ -1815,30 +1815,33 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>对Buff回复技力</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>流涟可生成标记</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>{"目标技能":"流涟可生成标记","技力":1,"提示":1,"无视阻回":1}</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>流涟标记自身</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>流涟可生成标记</t>
+  </si>
+  <si>
+    <t>流涟回复技力</t>
+  </si>
+  <si>
+    <t>对buff回复技力</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"目标技能":"流涟可生成标记","技力":1,"提示":0,"无视阻回":1}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1979,6 +1982,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2017,7 +2027,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2082,6 +2092,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3198,10 +3211,10 @@
         <v>440</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="AJ6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AK6">
         <v>0</v>
@@ -6122,8 +6135,9 @@
     <col min="37" max="37" width="8.58203125" customWidth="1"/>
     <col min="38" max="39" width="8.33203125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
-    <col min="41" max="41" width="13.25" customWidth="1"/>
-    <col min="42" max="45" width="11.83203125" customWidth="1"/>
+    <col min="41" max="41" width="18" customWidth="1"/>
+    <col min="42" max="42" width="20.58203125" customWidth="1"/>
+    <col min="43" max="45" width="11.83203125" customWidth="1"/>
     <col min="46" max="46" width="18.4140625" customWidth="1"/>
     <col min="47" max="47" width="12.25" customWidth="1"/>
     <col min="48" max="48" width="11.9140625" customWidth="1"/>
@@ -7283,6 +7297,9 @@
       <c r="CI7" t="s">
         <v>463</v>
       </c>
+      <c r="CJ7" s="22" t="s">
+        <v>491</v>
+      </c>
       <c r="CN7" s="2" t="s">
         <v>464</v>
       </c>
@@ -7383,7 +7400,7 @@
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>445</v>
@@ -9694,13 +9711,13 @@
         <v>487</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>484</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Diy优胜/第一届.xlsx
+++ b/Excel/Diy优胜/第一届.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802CC9DB-65F8-462A-93D4-900D8FF2A4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD0DC7C-1995-44AD-8015-781A2459A876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="564">
   <si>
     <t>Id</t>
   </si>
@@ -1214,9 +1214,6 @@
   </si>
   <si>
     <t>StartPower</t>
-  </si>
-  <si>
-    <t>MaxPower</t>
   </si>
   <si>
     <t>PowerCount</t>
@@ -1749,10 +1746,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>{"UnitId":"流涟","TargetPos":"useSelfTargetPos","SetMod":"Add","UseMod":"UserDirection","UserName":"时蒙"}</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>{"ExTarget":"流涟"}</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -1789,10 +1782,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>{"UnitId":"流涟","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"UserDirection","UserName":"时蒙"}</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>仅自己</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -1808,9 +1797,6 @@
     <t>生成流涟</t>
   </si>
   <si>
-    <t>流涟标记自身</t>
-  </si>
-  <si>
     <t>流涟回复技力</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -1833,7 +1819,446 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>{"目标技能":"流涟可生成标记","技力":1,"提示":0,"无视阻回":1}</t>
+    <t>充能释放</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"流涟","召唤位置":"使用本技能索敌位置","部署模式":"追加","召唤物方向":"固定方向"}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"流涟","召唤位置":"使用自身位置","部署模式":"追加","召唤物方向":"固定方向"}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"目标技能":"流涟可生成标记","技力":1,"提示":0,"无视阻回":0}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值变化依表达式</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟提升受击次数</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">仅自己 </t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升流涟技力需求</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxPower</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Expression":"Buff.Unit.WeightBase = Buff.Skill.Unit.Weight + 1","Time":1}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己以外</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟迭代次数</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟迭代</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Expression":"Buff.Unit.MainSkill.MaxPowerBase = Buff.Unit.Weight * 3 + 3","Time":2}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>棘刺2</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙1</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"LifeTime":8,"InitRadius":0.8,"MaxRadius":2.4,"RadiusExponentRate":0.2,"Trigger":1,"MoveHeight":2,"TriggerTimes":-1,"TargetTeam":2,"MaxTargetCount":-1}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>雨至光生</t>
+  </si>
+  <si>
+    <r>
+      <t>场上的我方单位部署时在其所在位置生成一个逐渐扩大的幻境，对幻境范围内的目标每秒造成攻击力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>250%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的法术伤害，持续</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>秒</t>
+    </r>
+  </si>
+  <si>
+    <t>skill_icon_skchr_shimeng_1</t>
+  </si>
+  <si>
+    <t>Muzzle</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定间隔</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙1子弹</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>midn_attack_01_trail</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟普攻</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0#-1,-1#0,-1#1,-1#-1,0#1,0#-1,1#0,1#1,1</t>
+  </si>
+  <si>
+    <t>时蒙2</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>光色无暇</t>
+  </si>
+  <si>
+    <r>
+      <t>立即获得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>个可主动部署的流涟（最多持有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>个）；时蒙与流涟攻击造成攻击力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>250%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的群体法术伤害，范围内的我方单位和敌方单位生命值不会低于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，时蒙攻击目标数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>+4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，流涟阻挡数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>+2</t>
+    </r>
+  </si>
+  <si>
+    <t>skill_icon_skchr_shimeng_2</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟可生成标记,流涟标记自身,流涟提升受击次数,流涟迭代次数</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>手动</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙2启动</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙2普攻</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙2获取流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取单位</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Count":3,"UnitId":"流涟","MaxCount":5}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅召唤</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟2普攻</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙2影响流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟加阻挡</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值变化</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"t":["StopCountAdd"]}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙2启动,流涟加阻挡</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙3</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>往赴随化</t>
+  </si>
+  <si>
+    <t>skill_icon_skchr_shimeng_3</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙3影响流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐身</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"HideTime":9999}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟相互连接</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身距离升序</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0#0,-3#-1,-2#0,-2#1,-2#-2,-1#-1,-1#0,-1#1,-1#2,-1#-3,0#-2,0#-1,0#1,0#2,0#3,0#-2,1#-1,1#0,1#1,1#2,1#-1,2#0,2#1,2#0,3</t>
+  </si>
+  <si>
+    <t>受击</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟3子弹</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>大飞镖</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙3获取流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>减速</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙1,时蒙2,时蒙3</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_icon_sktok_mlyss_wtrman</t>
+  </si>
+  <si>
+    <t>被动：流涟会连接周围流涟（至多3个），流涟部署时会使时蒙攻击目标数+1、攻击速度+10持续16秒（可叠加，独立持续）\n主动：获得1个可主动部署的流涟（最多持有5个）</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>midn_skill_01_trail</t>
+  </si>
+  <si>
+    <t>{"LifeTime":0,"Radius":1.4,"Trigger":0.02,"MoveHeight":0,"TriggerTimes":1,"TargetTeam":2,"MaxTargetCount":6}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"LiftTime":0,"Radius":0.8,"Trigger":0.02,"MoveHeight":0.5,"TriggerTimes":1,"TargetTeam":2,"MaxTargetCount":-1}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>终点距离</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙2锁血</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙2普攻,时蒙2获取流涟,时蒙2影响流涟,时蒙2锁血</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>锁血</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"TriggerPoint":0.1,"CanRecover":1}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟2锁血</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟普攻,流涟2普攻,流涟2锁血,生成下级流涟,通用绝食,流涟相互连接</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙a流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>打数溢出转换</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -1841,7 +2266,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1989,6 +2414,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2027,7 +2458,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2093,6 +2524,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2424,10 +2858,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -3035,14 +3469,14 @@
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>125</v>
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3054,43 +3488,46 @@
         <v>90</v>
       </c>
       <c r="K5">
-        <v>10000</v>
+        <v>1920</v>
       </c>
       <c r="M5">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="O5">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="Q5">
         <v>20</v>
       </c>
       <c r="S5">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="U5">
         <v>0.5</v>
       </c>
       <c r="V5">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="Y5">
         <v>0.05</v>
       </c>
       <c r="Z5">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AC5">
         <v>1</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AH5" s="2" t="s">
         <v>126</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>549</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3102,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="AO5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP5">
         <v>0.5</v>
@@ -3111,10 +3548,10 @@
         <v>0.25</v>
       </c>
       <c r="BB5" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="BD5" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="BE5" s="2" t="s">
         <v>127</v>
@@ -3156,20 +3593,20 @@
     </row>
     <row r="6" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E6" s="17"/>
       <c r="F6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>90</v>
@@ -3201,20 +3638,26 @@
       <c r="Z6">
         <v>1.5</v>
       </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
       <c r="AC6">
         <v>0</v>
       </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
       <c r="AG6" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>489</v>
+        <v>561</v>
       </c>
       <c r="AJ6" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="AK6">
         <v>0</v>
@@ -3231,23 +3674,26 @@
       <c r="AP6">
         <v>0.5</v>
       </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
       <c r="AV6" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AW6">
         <v>0.25</v>
       </c>
       <c r="BB6" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="BD6" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="BM6" s="2" t="s">
         <v>132</v>
       </c>
       <c r="BN6" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="BP6" s="2" t="s">
         <v>134</v>
@@ -3256,7 +3702,7 @@
         <v>134</v>
       </c>
       <c r="BR6" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="BS6">
         <v>1</v>
@@ -6096,7 +6542,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DJ842"/>
+  <dimension ref="A1:DJ851"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -6152,7 +6598,9 @@
     <col min="58" max="58" width="14.6640625" customWidth="1"/>
     <col min="59" max="59" width="10.1640625" customWidth="1"/>
     <col min="60" max="60" width="8.25" customWidth="1"/>
-    <col min="61" max="67" width="8.33203125" customWidth="1"/>
+    <col min="61" max="61" width="8.33203125" customWidth="1"/>
+    <col min="62" max="62" width="10.1640625" customWidth="1"/>
+    <col min="63" max="67" width="8.33203125" customWidth="1"/>
     <col min="68" max="70" width="11.25" customWidth="1"/>
     <col min="71" max="71" width="6.58203125" customWidth="1"/>
     <col min="72" max="73" width="8" customWidth="1"/>
@@ -6304,10 +6752,10 @@
         <v>175</v>
       </c>
       <c r="AR1" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AS1" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AT1" t="s">
         <v>176</v>
@@ -6639,10 +7087,10 @@
         <v>277</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AT2" t="s">
         <v>278</v>
@@ -6732,121 +7180,121 @@
         <v>304</v>
       </c>
       <c r="BW2" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="BX2" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="BY2" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="BZ2" s="6" t="s">
+      <c r="CA2" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="CA2" s="6" t="s">
+      <c r="CB2" t="s">
         <v>309</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CC2" t="s">
         <v>310</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CD2" t="s">
         <v>311</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CE2" t="s">
         <v>312</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CF2" t="s">
         <v>313</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
         <v>314</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>315</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CI2" t="s">
         <v>316</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CJ2" t="s">
         <v>317</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CK2" t="s">
         <v>318</v>
       </c>
-      <c r="CK2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CM2" t="s">
         <v>320</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CN2" t="s">
         <v>321</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CO2" t="s">
         <v>322</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CP2" t="s">
         <v>323</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CQ2" t="s">
         <v>324</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CR2" t="s">
         <v>325</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CS2" t="s">
         <v>326</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CT2" t="s">
         <v>327</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CU2" t="s">
         <v>328</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CV2" t="s">
         <v>329</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CW2" t="s">
         <v>330</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CX2" t="s">
         <v>331</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CY2" t="s">
         <v>332</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CZ2" t="s">
         <v>333</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DA2" t="s">
         <v>334</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DB2" t="s">
         <v>335</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DC2" t="s">
         <v>336</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DD2" t="s">
         <v>337</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DE2" t="s">
         <v>338</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DF2" t="s">
         <v>339</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DG2" t="s">
         <v>340</v>
       </c>
-      <c r="DG2" t="s">
+      <c r="DH2" t="s">
         <v>341</v>
       </c>
-      <c r="DH2" t="s">
+      <c r="DI2" t="s">
         <v>342</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -6875,13 +7323,13 @@
         <v>115</v>
       </c>
       <c r="J3" t="s">
+        <v>343</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>346</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>117</v>
@@ -6944,7 +7392,7 @@
         <v>115</v>
       </c>
       <c r="AG3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AH3" t="s">
         <v>115</v>
@@ -6968,22 +7416,22 @@
         <v>115</v>
       </c>
       <c r="AO3" t="s">
+        <v>347</v>
+      </c>
+      <c r="AP3" t="s">
         <v>348</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>349</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AS3" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AT3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AU3" t="s">
         <v>115</v>
@@ -6995,7 +7443,7 @@
         <v>115</v>
       </c>
       <c r="AX3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AY3" t="s">
         <v>115</v>
@@ -7025,7 +7473,7 @@
         <v>115</v>
       </c>
       <c r="BH3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="BI3" t="s">
         <v>115</v>
@@ -7052,10 +7500,10 @@
         <v>118</v>
       </c>
       <c r="BQ3" t="s">
+        <v>351</v>
+      </c>
+      <c r="BR3" t="s">
         <v>352</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>353</v>
       </c>
       <c r="BS3" t="s">
         <v>116</v>
@@ -7076,19 +7524,19 @@
         <v>117</v>
       </c>
       <c r="BY3" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="BZ3" s="6" t="s">
         <v>115</v>
       </c>
       <c r="CA3" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="CB3" t="s">
         <v>123</v>
       </c>
       <c r="CC3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="CD3" t="s">
         <v>123</v>
@@ -7100,19 +7548,19 @@
         <v>123</v>
       </c>
       <c r="CG3" t="s">
+        <v>355</v>
+      </c>
+      <c r="CH3" t="s">
         <v>356</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>357</v>
       </c>
       <c r="CI3" t="s">
         <v>2</v>
       </c>
       <c r="CJ3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="CK3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="CL3" s="2" t="s">
         <v>124</v>
@@ -7133,7 +7581,7 @@
         <v>122</v>
       </c>
       <c r="CR3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="CS3" t="s">
         <v>122</v>
@@ -7145,28 +7593,28 @@
         <v>124</v>
       </c>
       <c r="CV3" t="s">
+        <v>358</v>
+      </c>
+      <c r="CW3" t="s">
         <v>359</v>
       </c>
-      <c r="CW3" t="s">
-        <v>360</v>
-      </c>
       <c r="CX3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="CY3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="CZ3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="DA3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="DB3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="DC3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="DD3" t="s">
         <v>115</v>
@@ -7189,7 +7637,7 @@
     </row>
     <row r="4" spans="1:113" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:113" x14ac:dyDescent="0.25">
@@ -7200,23 +7648,23 @@
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>446</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>447</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>448</v>
       </c>
       <c r="P6"/>
       <c r="AC6">
@@ -7232,12 +7680,6 @@
       <c r="AO6" s="2"/>
       <c r="AV6">
         <v>20</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>2</v>
       </c>
       <c r="BD6">
         <v>99</v>
@@ -7248,7 +7690,7 @@
       <c r="CL6" s="2"/>
       <c r="CM6" s="2"/>
       <c r="CN6" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="CR6">
         <v>5</v>
@@ -7256,28 +7698,33 @@
     </row>
     <row r="7" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O7"/>
+      <c r="P7" s="2" t="s">
+        <v>523</v>
+      </c>
       <c r="AC7">
         <v>2</v>
       </c>
       <c r="AD7">
         <v>1</v>
       </c>
-      <c r="AO7" s="2"/>
+      <c r="AO7" s="2" t="s">
+        <v>555</v>
+      </c>
       <c r="AT7" t="s">
+        <v>458</v>
+      </c>
+      <c r="AX7" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="AX7" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="AZ7">
         <v>1</v>
@@ -7285,128 +7732,154 @@
       <c r="BD7">
         <v>1</v>
       </c>
+      <c r="BP7" s="2" t="s">
+        <v>562</v>
+      </c>
       <c r="CB7" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="CG7" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="CH7" t="s">
         <v>461</v>
       </c>
-      <c r="CH7" t="s">
+      <c r="CI7" t="s">
         <v>462</v>
       </c>
-      <c r="CI7" t="s">
+      <c r="CJ7" s="22"/>
+      <c r="CN7" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="CJ7" s="22" t="s">
-        <v>491</v>
-      </c>
-      <c r="CN7" s="2" t="s">
-        <v>464</v>
       </c>
       <c r="CR7">
         <v>9999</v>
       </c>
-      <c r="CU7" s="2" t="s">
-        <v>472</v>
-      </c>
+      <c r="CU7" s="2"/>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>468</v>
+        <v>562</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="H8" s="2"/>
+        <v>563</v>
+      </c>
+      <c r="J8" s="2"/>
       <c r="K8" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>466</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="O8"/>
+      <c r="P8" s="2"/>
       <c r="AC8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD8">
         <v>1</v>
       </c>
-      <c r="AF8">
+      <c r="AJ8" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="AV8">
+        <v>20</v>
+      </c>
+      <c r="AX8" s="2"/>
+      <c r="CB8" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="CG8" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="CH8" t="s">
+        <v>461</v>
+      </c>
+      <c r="CI8" t="s">
+        <v>462</v>
+      </c>
+      <c r="CJ8" s="22" t="s">
+        <v>487</v>
+      </c>
+      <c r="CN8" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="CR8">
+        <v>9999</v>
+      </c>
+      <c r="CU8" s="2"/>
+    </row>
+    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="K9" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="AC9">
+        <v>3</v>
+      </c>
+      <c r="AD9">
         <v>1</v>
       </c>
-      <c r="AG8" s="2"/>
-      <c r="AH8" s="2">
+      <c r="AF9">
         <v>1</v>
       </c>
-      <c r="AO8" s="2"/>
-      <c r="AX8" s="2"/>
-      <c r="BD8">
+      <c r="AG9" s="2"/>
+      <c r="AH9" s="2">
         <v>1</v>
       </c>
-      <c r="CG8" s="2"/>
-      <c r="CL8" s="2"/>
-      <c r="CN8" s="2"/>
-      <c r="CO8" s="2"/>
-      <c r="CU8" s="2" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="9" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="AG9" s="2"/>
       <c r="AO9" s="2"/>
       <c r="AX9" s="2"/>
+      <c r="BD9">
+        <v>1</v>
+      </c>
       <c r="CG9" s="2"/>
       <c r="CL9" s="2"/>
       <c r="CN9" s="2"/>
       <c r="CO9" s="2"/>
+      <c r="CU9" s="2" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="10" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>445</v>
-      </c>
+      <c r="A10" s="2"/>
+      <c r="C10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="K10" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="AC10">
-        <v>2</v>
-      </c>
-      <c r="AD10">
-        <v>1</v>
-      </c>
       <c r="AG10" s="2"/>
-      <c r="AH10" s="2">
-        <v>1</v>
-      </c>
+      <c r="AH10" s="2"/>
       <c r="AO10" s="2"/>
       <c r="AX10" s="2"/>
-      <c r="BD10">
-        <v>1</v>
-      </c>
       <c r="CG10" s="2"/>
       <c r="CL10" s="2"/>
       <c r="CN10" s="2"/>
       <c r="CO10" s="2"/>
-      <c r="CU10" s="2" t="s">
-        <v>481</v>
-      </c>
+      <c r="CU10" s="2"/>
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>488</v>
+        <v>515</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
+      </c>
+      <c r="F11" t="s">
+        <v>550</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>523</v>
       </c>
       <c r="AC11">
         <v>2</v>
@@ -7414,160 +7887,238 @@
       <c r="AD11">
         <v>1</v>
       </c>
-      <c r="AG11" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="AJ11" s="2"/>
-      <c r="AO11" s="2"/>
+      <c r="AG11" s="2"/>
+      <c r="AO11" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>516</v>
+      </c>
+      <c r="AX11" s="2" t="s">
+        <v>459</v>
+      </c>
       <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD11">
         <v>1</v>
       </c>
-      <c r="BT11">
-        <v>0.1</v>
-      </c>
-      <c r="BV11">
-        <v>0</v>
-      </c>
-      <c r="BW11" s="6">
-        <v>3</v>
-      </c>
-      <c r="BX11" s="6">
-        <v>1</v>
-      </c>
-      <c r="BY11" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="CL11" s="5"/>
-      <c r="CN11" s="2" t="s">
-        <v>485</v>
-      </c>
+      <c r="CB11" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="CG11" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="CH11" t="s">
+        <v>461</v>
+      </c>
+      <c r="CI11" t="s">
+        <v>462</v>
+      </c>
+      <c r="CL11" s="2"/>
+      <c r="CN11" s="2"/>
       <c r="CO11" s="2"/>
-      <c r="CR11">
-        <v>9999</v>
-      </c>
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>486</v>
+        <v>529</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>483</v>
+        <v>456</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>523</v>
       </c>
       <c r="AC12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD12">
         <v>1</v>
       </c>
-      <c r="AG12" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="AJ12" s="2"/>
-      <c r="AO12" s="2"/>
+      <c r="AG12" s="2"/>
+      <c r="AO12" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>516</v>
+      </c>
+      <c r="AX12" s="2" t="s">
+        <v>459</v>
+      </c>
       <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD12">
         <v>1</v>
       </c>
-      <c r="BV12"/>
-      <c r="CL12" s="5"/>
-      <c r="CN12" s="2" t="s">
+      <c r="BJ12">
+        <v>1.7</v>
+      </c>
+      <c r="BK12">
+        <v>1</v>
+      </c>
+      <c r="BL12">
+        <v>1</v>
+      </c>
+      <c r="CB12" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="CG12" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="CH12" t="s">
+        <v>461</v>
+      </c>
+      <c r="CI12" t="s">
+        <v>462</v>
+      </c>
+      <c r="CL12" s="2"/>
+      <c r="CN12" s="2"/>
+      <c r="CO12" s="2"/>
+    </row>
+    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="K13" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AD13">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO13" s="2"/>
+      <c r="AX13" s="2"/>
+      <c r="BD13">
+        <v>1</v>
+      </c>
+      <c r="BO13" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="CG13" s="2"/>
+      <c r="CL13" s="2"/>
+      <c r="CN13" s="2"/>
+      <c r="CO13" s="2"/>
+      <c r="CU13" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="CO12" s="2"/>
-      <c r="CR12">
+      <c r="C14" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="P14" s="2"/>
+      <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AD14">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="AJ14" s="2"/>
+      <c r="AO14" s="2"/>
+      <c r="BD14">
+        <v>1</v>
+      </c>
+      <c r="BT14">
         <v>9999</v>
       </c>
-    </row>
-    <row r="13" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="BV13" s="10"/>
-      <c r="BW13" s="10"/>
-      <c r="BX13" s="10"/>
-      <c r="BY13" s="10"/>
-      <c r="BZ13" s="10"/>
-      <c r="CA13" s="10"/>
-      <c r="CL13" s="7"/>
-    </row>
-    <row r="14" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="BV14"/>
-      <c r="BW14" s="10"/>
-      <c r="BX14" s="10"/>
-      <c r="BY14" s="10"/>
-      <c r="BZ14" s="10"/>
-      <c r="CA14" s="10"/>
-      <c r="CL14" s="7"/>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14" s="6">
+        <v>3</v>
+      </c>
+      <c r="BX14" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY14" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="CL14" s="5"/>
+      <c r="CN14" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="CO14" s="2"/>
+      <c r="CR14">
+        <v>9999</v>
+      </c>
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="BV15" s="10"/>
-      <c r="BW15" s="10"/>
-      <c r="BX15" s="10"/>
-      <c r="BY15" s="10"/>
-      <c r="BZ15" s="10"/>
-      <c r="CA15" s="10"/>
-      <c r="CL15" s="7"/>
-      <c r="CU15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="AJ15" s="2"/>
+      <c r="AO15" s="2"/>
+      <c r="AT15" s="2"/>
+      <c r="BD15">
+        <v>1</v>
+      </c>
+      <c r="BV15"/>
+      <c r="CL15" s="5"/>
+      <c r="CN15" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="CO15" s="2"/>
+      <c r="CR15">
+        <v>9999</v>
+      </c>
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
+      <c r="A16" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>480</v>
+      </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
@@ -7580,106 +8131,234 @@
       <c r="V16" s="7"/>
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
-      <c r="BV16"/>
+      <c r="AC16">
+        <v>1</v>
+      </c>
+      <c r="AD16">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="BD16">
+        <v>1</v>
+      </c>
+      <c r="BV16" s="10"/>
       <c r="BW16" s="10"/>
       <c r="BX16" s="10"/>
       <c r="BY16" s="10"/>
       <c r="BZ16" s="10"/>
       <c r="CA16" s="10"/>
       <c r="CL16" s="7"/>
+      <c r="CN16" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="CR16">
+        <v>9999</v>
+      </c>
     </row>
     <row r="17" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="BV17" s="10"/>
-      <c r="BW17" s="10"/>
-      <c r="BX17" s="10"/>
-      <c r="BY17" s="10"/>
-      <c r="BZ17" s="10"/>
-      <c r="CA17" s="10"/>
-      <c r="CL17" s="7"/>
+      <c r="A17" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC17">
+        <v>1</v>
+      </c>
+      <c r="AD17">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="AO17" s="2"/>
+      <c r="AT17" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="BD17">
+        <v>1</v>
+      </c>
+      <c r="BV17"/>
+      <c r="CL17" s="5"/>
+      <c r="CN17" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="CO17" s="2"/>
+      <c r="CR17">
+        <v>9999</v>
+      </c>
     </row>
     <row r="18" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="BV18" s="10"/>
-      <c r="BW18" s="10"/>
-      <c r="BX18" s="10"/>
-      <c r="BY18" s="10"/>
-      <c r="BZ18" s="10"/>
-      <c r="CA18" s="10"/>
-      <c r="CL18" s="7"/>
+      <c r="A18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="AG18" s="2"/>
+      <c r="AJ18" s="2"/>
+      <c r="AO18" s="2"/>
+      <c r="AT18" s="2"/>
+      <c r="BV18"/>
+      <c r="CL18" s="5"/>
+      <c r="CN18" s="2"/>
+      <c r="CO18" s="2"/>
     </row>
     <row r="19" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19"/>
-      <c r="N19"/>
-      <c r="O19" s="8"/>
-      <c r="P19"/>
-      <c r="Q19"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="8"/>
-      <c r="BV19" s="11"/>
-      <c r="BW19" s="11"/>
-      <c r="BX19" s="11"/>
-      <c r="BY19" s="11"/>
-      <c r="BZ19" s="11"/>
-      <c r="CA19" s="11"/>
+      <c r="A19" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="AC19">
+        <v>3</v>
+      </c>
+      <c r="AD19">
+        <v>1</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>516</v>
+      </c>
+      <c r="AX19" s="2"/>
+      <c r="BD19">
+        <v>99</v>
+      </c>
+      <c r="BL19">
+        <v>1</v>
+      </c>
+      <c r="BS19">
+        <v>0.01</v>
+      </c>
+      <c r="BV19" s="10"/>
+      <c r="BW19" s="10"/>
+      <c r="BX19" s="10"/>
+      <c r="BY19" s="10"/>
+      <c r="BZ19" s="10"/>
+      <c r="CA19" s="10"/>
+      <c r="CB19" s="2"/>
+      <c r="CG19" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="CI19" s="2"/>
+      <c r="CJ19" s="22"/>
+      <c r="CL19" s="7"/>
+      <c r="CN19" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="CR19">
+        <v>0.02</v>
+      </c>
+      <c r="CU19" s="2"/>
     </row>
     <row r="20" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="BV20"/>
-      <c r="BW20" s="10"/>
-      <c r="BX20" s="10"/>
-      <c r="BY20" s="10"/>
-      <c r="BZ20" s="10"/>
-      <c r="CA20" s="10"/>
-      <c r="CL20" s="7"/>
+      <c r="A20" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="AC20">
+        <v>3</v>
+      </c>
+      <c r="AD20">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="AJ20" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="AO20" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="AT20" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="AX20" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="AZ20">
+        <v>5</v>
+      </c>
+      <c r="BB20">
+        <v>3</v>
+      </c>
+      <c r="BD20">
+        <v>3</v>
+      </c>
+      <c r="BT20">
+        <v>0.3</v>
+      </c>
+      <c r="BV20">
+        <v>4</v>
+      </c>
+      <c r="BW20" s="6">
+        <v>4</v>
+      </c>
+      <c r="BX20" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY20" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="CB20" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="CG20" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="CH20" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="CJ20" s="22" t="s">
+        <v>487</v>
+      </c>
+      <c r="CL20" s="5"/>
+      <c r="CN20" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="CO20" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="CR20">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="21" spans="1:99" x14ac:dyDescent="0.25">
       <c r="K21" s="7"/>
@@ -7704,9 +8383,28 @@
       <c r="CA21" s="10"/>
       <c r="CL21" s="7"/>
     </row>
-    <row r="22" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+    <row r="22" spans="1:99" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F22" t="s">
+        <v>510</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>447</v>
+      </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
@@ -7719,40 +8417,90 @@
       <c r="V22" s="7"/>
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
+      <c r="AC22">
+        <v>1</v>
+      </c>
+      <c r="AD22">
+        <v>1</v>
+      </c>
+      <c r="AF22">
+        <v>1</v>
+      </c>
+      <c r="AZ22">
+        <v>2.5</v>
+      </c>
+      <c r="BD22">
+        <v>99</v>
+      </c>
       <c r="BV22" s="10"/>
       <c r="BW22" s="10"/>
       <c r="BX22" s="10"/>
-      <c r="BY22" s="10"/>
       <c r="BZ22" s="10"/>
-      <c r="CA22" s="10"/>
+      <c r="CG22" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="CH22" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="CI22" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="CJ22" s="22" t="s">
+        <v>487</v>
+      </c>
       <c r="CL22" s="7"/>
+      <c r="CU22" s="2"/>
     </row>
     <row r="23" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K23" s="7"/>
-      <c r="L23" s="8"/>
-      <c r="M23"/>
-      <c r="N23"/>
-      <c r="O23" s="8"/>
-      <c r="P23"/>
-      <c r="Q23"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="8"/>
-      <c r="V23" s="8"/>
-      <c r="W23" s="8"/>
-      <c r="X23" s="8"/>
-      <c r="Y23" s="8"/>
-      <c r="BV23" s="11"/>
-      <c r="BW23" s="11"/>
-      <c r="BX23" s="11"/>
-      <c r="BY23" s="11"/>
-      <c r="BZ23" s="11"/>
-      <c r="CA23" s="11"/>
+      <c r="A23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="BV23" s="10"/>
+      <c r="BW23" s="10"/>
+      <c r="BX23" s="10"/>
+      <c r="BZ23" s="10"/>
+      <c r="CG23" s="2"/>
+      <c r="CH23" s="2"/>
+      <c r="CI23" s="2"/>
+      <c r="CJ23" s="22"/>
       <c r="CL23" s="7"/>
-    </row>
-    <row r="24" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K24" s="7"/>
+      <c r="CU23" s="2"/>
+    </row>
+    <row r="24" spans="1:99" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>522</v>
+      </c>
       <c r="L24" s="7"/>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
@@ -7766,20 +8514,68 @@
       <c r="V24" s="7"/>
       <c r="W24" s="7"/>
       <c r="X24" s="7"/>
-      <c r="BV24"/>
-      <c r="BW24" s="10"/>
-      <c r="BX24" s="10"/>
-      <c r="BY24" s="10"/>
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="AO24" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="AT24" t="s">
+        <v>458</v>
+      </c>
+      <c r="BD24">
+        <v>1</v>
+      </c>
+      <c r="BO24" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="BP24" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="BT24">
+        <v>16</v>
+      </c>
+      <c r="BV24">
+        <v>36</v>
+      </c>
+      <c r="BW24" s="10">
+        <v>49</v>
+      </c>
+      <c r="BX24" s="10">
+        <v>1</v>
+      </c>
+      <c r="BY24" s="6" t="s">
+        <v>456</v>
+      </c>
       <c r="BZ24" s="10"/>
       <c r="CA24" s="10"/>
       <c r="CL24" s="7"/>
+      <c r="CN24" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="CR24">
+        <v>16</v>
+      </c>
     </row>
     <row r="25" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K25" s="7"/>
+      <c r="A25" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>456</v>
+      </c>
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
+      <c r="O25" s="5" t="s">
+        <v>523</v>
+      </c>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
@@ -7789,217 +8585,611 @@
       <c r="V25" s="7"/>
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
-      <c r="BV25"/>
+      <c r="AC25">
+        <v>2</v>
+      </c>
+      <c r="AD25">
+        <v>1</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>458</v>
+      </c>
+      <c r="AX25" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="AZ25">
+        <v>1</v>
+      </c>
+      <c r="BD25">
+        <v>5</v>
+      </c>
+      <c r="BI25">
+        <v>1</v>
+      </c>
+      <c r="BJ25">
+        <v>1.7</v>
+      </c>
+      <c r="BK25">
+        <v>1</v>
+      </c>
+      <c r="BL25">
+        <v>1</v>
+      </c>
+      <c r="BV25" s="10"/>
       <c r="BW25" s="10"/>
       <c r="BX25" s="10"/>
       <c r="BY25" s="10"/>
       <c r="BZ25" s="10"/>
       <c r="CA25" s="10"/>
+      <c r="CB25" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="CG25" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="CH25" t="s">
+        <v>461</v>
+      </c>
+      <c r="CI25" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="CJ25" s="22" t="s">
+        <v>487</v>
+      </c>
       <c r="CL25" s="7"/>
+      <c r="CN25" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="CR25">
+        <v>9999</v>
+      </c>
+      <c r="CU25" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="26" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7"/>
+      <c r="X26" s="7"/>
+      <c r="AC26">
+        <v>3</v>
+      </c>
+      <c r="AD26">
+        <v>1</v>
+      </c>
+      <c r="AT26" t="s">
+        <v>458</v>
+      </c>
+      <c r="AX26" s="2"/>
+      <c r="BD26">
+        <v>99</v>
+      </c>
+      <c r="BL26">
+        <v>1</v>
+      </c>
+      <c r="BS26">
+        <v>0.01</v>
+      </c>
+      <c r="BV26" s="10"/>
+      <c r="BW26" s="10"/>
+      <c r="BX26" s="10"/>
+      <c r="BY26" s="10"/>
+      <c r="BZ26" s="10"/>
+      <c r="CA26" s="10"/>
+      <c r="CB26" s="2"/>
+      <c r="CG26" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="CI26" s="2"/>
+      <c r="CJ26" s="22"/>
+      <c r="CL26" s="7"/>
+      <c r="CN26" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="CR26">
+        <v>0.02</v>
+      </c>
+      <c r="CU26" s="2"/>
     </row>
     <row r="27" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="AT27" s="2"/>
-      <c r="BV27"/>
-      <c r="CL27" s="5"/>
-      <c r="CU27" s="2"/>
+      <c r="A27" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
+      <c r="X27" s="7"/>
+      <c r="AC27">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="BD27">
+        <v>1</v>
+      </c>
+      <c r="BV27" s="10"/>
+      <c r="BW27" s="10"/>
+      <c r="BX27" s="10"/>
+      <c r="BY27" s="10"/>
+      <c r="BZ27" s="10"/>
+      <c r="CA27" s="10"/>
+      <c r="CL27" s="7"/>
+      <c r="CU27" s="2" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="28" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="J28" s="2"/>
-      <c r="O28"/>
-      <c r="AO28" s="2"/>
-      <c r="CU28" s="2"/>
+      <c r="A28" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="L28" s="8"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="P28"/>
+      <c r="Q28"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
+      <c r="W28" s="8"/>
+      <c r="X28" s="8"/>
+      <c r="Y28" s="8"/>
+      <c r="AC28">
+        <v>1</v>
+      </c>
+      <c r="AD28">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="AJ28" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="AV28">
+        <v>20</v>
+      </c>
+      <c r="BD28">
+        <v>99</v>
+      </c>
+      <c r="BS28">
+        <v>0.01</v>
+      </c>
+      <c r="BV28" s="11"/>
+      <c r="BW28" s="11"/>
+      <c r="BX28" s="11"/>
+      <c r="BY28" s="11"/>
+      <c r="BZ28" s="11"/>
+      <c r="CA28" s="11"/>
+      <c r="CN28" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="CP28">
+        <v>2</v>
+      </c>
+      <c r="CR28">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="29" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="P29"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7"/>
+      <c r="X29" s="7"/>
+      <c r="BV29"/>
+      <c r="BW29" s="10"/>
+      <c r="BX29" s="10"/>
+      <c r="BY29" s="10"/>
+      <c r="BZ29" s="10"/>
+      <c r="CA29" s="10"/>
+      <c r="CL29" s="7"/>
     </row>
     <row r="30" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="CL30" s="5"/>
+      <c r="A30" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>551</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="7"/>
+      <c r="X30" s="7"/>
+      <c r="AC30">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="AT30" t="s">
+        <v>458</v>
+      </c>
+      <c r="BD30">
+        <v>1</v>
+      </c>
+      <c r="BO30" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="BP30" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="BT30">
+        <v>0.1</v>
+      </c>
+      <c r="BV30">
+        <v>16</v>
+      </c>
+      <c r="BW30" s="10">
+        <v>16</v>
+      </c>
+      <c r="BX30" s="10">
+        <v>1</v>
+      </c>
+      <c r="BY30" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="BZ30" s="10"/>
+      <c r="CA30" s="10"/>
+      <c r="CL30" s="7"/>
+      <c r="CN30" s="2"/>
     </row>
     <row r="31" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
+      <c r="A31" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="L31" s="8"/>
       <c r="M31"/>
       <c r="N31"/>
-      <c r="O31" s="9"/>
+      <c r="O31" s="8"/>
       <c r="P31"/>
       <c r="Q31"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31"/>
-      <c r="BU31" s="12"/>
-      <c r="BV31" s="12"/>
-      <c r="BW31" s="12"/>
-      <c r="BX31" s="12"/>
-      <c r="BY31" s="12"/>
-      <c r="BZ31" s="12"/>
-      <c r="CA31"/>
+      <c r="R31" s="8"/>
+      <c r="S31" s="8"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="8"/>
+      <c r="V31" s="8"/>
+      <c r="W31" s="8"/>
+      <c r="X31" s="8"/>
+      <c r="Y31" s="8"/>
+      <c r="AC31">
+        <v>1</v>
+      </c>
+      <c r="AD31">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="AJ31" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="AV31">
+        <v>20</v>
+      </c>
+      <c r="BD31">
+        <v>99</v>
+      </c>
+      <c r="BS31">
+        <v>0.1</v>
+      </c>
+      <c r="BV31" s="11"/>
+      <c r="BW31" s="11"/>
+      <c r="BX31" s="11"/>
+      <c r="BY31" s="11"/>
+      <c r="BZ31" s="11"/>
+      <c r="CA31" s="11"/>
+      <c r="CN31" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="CR31">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="32" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32"/>
-      <c r="N32"/>
-      <c r="O32" s="9"/>
-      <c r="P32"/>
-      <c r="Q32"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="9"/>
-      <c r="W32" s="9"/>
-      <c r="X32"/>
-      <c r="BU32" s="12"/>
-      <c r="BV32" s="12"/>
-      <c r="BW32" s="12"/>
-      <c r="BX32" s="12"/>
-      <c r="BY32" s="12"/>
-      <c r="BZ32" s="12"/>
-      <c r="CA32"/>
-      <c r="CN32" s="3"/>
-    </row>
-    <row r="33" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="AY33" s="5"/>
+      <c r="A32" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="7"/>
+      <c r="V32" s="7"/>
+      <c r="W32" s="7"/>
+      <c r="X32" s="7"/>
+      <c r="AC32">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="BD32">
+        <v>1</v>
+      </c>
+      <c r="BV32" s="10"/>
+      <c r="BW32" s="10"/>
+      <c r="BX32" s="10"/>
+      <c r="BY32" s="10"/>
+      <c r="BZ32" s="10"/>
+      <c r="CA32" s="10"/>
+      <c r="CL32" s="7"/>
+      <c r="CU32" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="33" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
       <c r="BV33"/>
-      <c r="BW33"/>
-      <c r="BX33"/>
-      <c r="BY33"/>
-      <c r="BZ33"/>
-      <c r="CA33"/>
-      <c r="CB33" s="5"/>
-      <c r="CC33" s="5"/>
-      <c r="CD33" s="5"/>
-      <c r="CE33" s="5"/>
-      <c r="CF33" s="5"/>
-      <c r="CH33" s="5"/>
-      <c r="CI33" s="5"/>
-      <c r="CJ33" s="5"/>
-      <c r="CK33" s="5"/>
-      <c r="CL33" s="5"/>
-      <c r="CM33" s="5"/>
-    </row>
-    <row r="34" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="M34"/>
-      <c r="N34"/>
-      <c r="P34" s="3"/>
-      <c r="R34" s="3"/>
-      <c r="S34"/>
-      <c r="X34"/>
+      <c r="BW33" s="10"/>
+      <c r="BX33" s="10"/>
+      <c r="BY33" s="10"/>
+      <c r="BZ33" s="10"/>
+      <c r="CA33" s="10"/>
+      <c r="CL33" s="7"/>
+    </row>
+    <row r="34" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7"/>
+      <c r="X34" s="7"/>
       <c r="BV34"/>
-      <c r="CB34" s="6"/>
-    </row>
-    <row r="35" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="BV35"/>
-    </row>
-    <row r="36" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="M36"/>
-      <c r="O36"/>
-      <c r="BO36" s="2"/>
-      <c r="BP36" s="2"/>
-      <c r="CN36" s="3"/>
-    </row>
-    <row r="37" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="J37" s="5"/>
-      <c r="M37"/>
-      <c r="O37" s="3"/>
-      <c r="P37"/>
-      <c r="Q37"/>
-      <c r="CN37" s="2"/>
-    </row>
-    <row r="38" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="M38"/>
-      <c r="CB38" s="13"/>
-    </row>
-    <row r="39" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="M39"/>
-      <c r="O39" s="3"/>
-      <c r="P39"/>
-      <c r="Q39"/>
-    </row>
-    <row r="40" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
+      <c r="BW34" s="10"/>
+      <c r="BX34" s="10"/>
+      <c r="BY34" s="10"/>
+      <c r="BZ34" s="10"/>
+      <c r="CA34" s="10"/>
+      <c r="CL34" s="7"/>
+    </row>
+    <row r="36" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="AT36" s="2"/>
+      <c r="BV36"/>
+      <c r="CL36" s="5"/>
+      <c r="CU36" s="2"/>
+    </row>
+    <row r="37" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="J37" s="2"/>
+      <c r="O37"/>
+      <c r="AO37" s="2"/>
+      <c r="CU37" s="2"/>
+    </row>
+    <row r="38" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="P38"/>
+    </row>
+    <row r="39" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CL39" s="5"/>
+    </row>
+    <row r="40" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
       <c r="M40"/>
-      <c r="O40" s="3"/>
+      <c r="N40"/>
+      <c r="O40" s="9"/>
       <c r="P40"/>
       <c r="Q40"/>
-      <c r="CN40" s="3"/>
-    </row>
-    <row r="41" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="R40" s="9"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="X40"/>
+      <c r="BU40" s="12"/>
+      <c r="BV40" s="12"/>
+      <c r="BW40" s="12"/>
+      <c r="BX40" s="12"/>
+      <c r="BY40" s="12"/>
+      <c r="BZ40" s="12"/>
+      <c r="CA40"/>
+    </row>
+    <row r="41" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
       <c r="M41"/>
-      <c r="AY41" s="5"/>
-      <c r="BV41"/>
-      <c r="BW41"/>
-      <c r="BX41"/>
-      <c r="BY41"/>
-      <c r="BZ41"/>
+      <c r="N41"/>
+      <c r="O41" s="9"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41"/>
+      <c r="BU41" s="12"/>
+      <c r="BV41" s="12"/>
+      <c r="BW41" s="12"/>
+      <c r="BX41" s="12"/>
+      <c r="BY41" s="12"/>
+      <c r="BZ41" s="12"/>
       <c r="CA41"/>
-      <c r="CB41" s="5"/>
-      <c r="CC41" s="5"/>
-      <c r="CD41" s="5"/>
-      <c r="CE41" s="5"/>
-      <c r="CF41" s="5"/>
-      <c r="CH41" s="5"/>
-      <c r="CI41" s="5"/>
-      <c r="CJ41" s="5"/>
-      <c r="CK41" s="5"/>
       <c r="CN41" s="3"/>
     </row>
-    <row r="42" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="M42"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="1:92" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="AY42" s="5"/>
+      <c r="BV42"/>
+      <c r="BW42"/>
+      <c r="BX42"/>
+      <c r="BY42"/>
+      <c r="BZ42"/>
+      <c r="CA42"/>
+      <c r="CB42" s="5"/>
+      <c r="CC42" s="5"/>
+      <c r="CD42" s="5"/>
+      <c r="CE42" s="5"/>
+      <c r="CF42" s="5"/>
+      <c r="CH42" s="5"/>
+      <c r="CI42" s="5"/>
+      <c r="CJ42" s="5"/>
+      <c r="CK42" s="5"/>
+      <c r="CL42" s="5"/>
+      <c r="CM42" s="5"/>
+    </row>
+    <row r="43" spans="1:99" x14ac:dyDescent="0.25">
       <c r="M43"/>
       <c r="N43"/>
+      <c r="P43" s="3"/>
+      <c r="R43" s="3"/>
+      <c r="S43"/>
+      <c r="X43"/>
       <c r="BV43"/>
-      <c r="CI43" s="5"/>
-      <c r="CJ43" s="5"/>
-    </row>
-    <row r="44" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="M44"/>
-      <c r="N44"/>
+      <c r="CB43" s="6"/>
+    </row>
+    <row r="44" spans="1:99" x14ac:dyDescent="0.25">
       <c r="BV44"/>
-      <c r="CJ44" s="5"/>
-    </row>
-    <row r="45" spans="1:92" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:99" x14ac:dyDescent="0.25">
       <c r="M45"/>
-      <c r="O45" s="3"/>
-      <c r="AG45" s="2"/>
-      <c r="AO45" s="2"/>
+      <c r="O45"/>
       <c r="BO45" s="2"/>
       <c r="BP45" s="2"/>
-      <c r="CG45" s="2"/>
-      <c r="CM45" s="2"/>
-    </row>
-    <row r="46" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
+      <c r="CN45" s="3"/>
+    </row>
+    <row r="46" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="J46" s="5"/>
       <c r="M46"/>
       <c r="O46" s="3"/>
-      <c r="AG46" s="2"/>
-      <c r="AO46" s="2"/>
-      <c r="CG46" s="2"/>
-    </row>
-    <row r="47" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="BU47" s="6"/>
-      <c r="CA47"/>
-    </row>
-    <row r="48" spans="1:92" x14ac:dyDescent="0.25">
-      <c r="E48" s="2"/>
-      <c r="O48"/>
-      <c r="W48"/>
-      <c r="X48"/>
-      <c r="BO48" s="2"/>
-      <c r="BP48" s="2"/>
-      <c r="CN48" s="3"/>
+      <c r="P46"/>
+      <c r="Q46"/>
+      <c r="CN46" s="2"/>
+    </row>
+    <row r="47" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="M47"/>
+      <c r="CB47" s="13"/>
+    </row>
+    <row r="48" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="M48"/>
+      <c r="O48" s="3"/>
+      <c r="P48"/>
+      <c r="Q48"/>
     </row>
     <row r="49" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A49" s="2"/>
       <c r="M49"/>
       <c r="O49" s="3"/>
       <c r="P49"/>
@@ -8007,147 +9197,207 @@
       <c r="CN49" s="3"/>
     </row>
     <row r="50" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
       <c r="M50"/>
-      <c r="O50" s="3"/>
-      <c r="P50"/>
-      <c r="Q50"/>
+      <c r="AY50" s="5"/>
+      <c r="BV50"/>
+      <c r="BW50"/>
+      <c r="BX50"/>
+      <c r="BY50"/>
+      <c r="BZ50"/>
+      <c r="CA50"/>
+      <c r="CB50" s="5"/>
+      <c r="CC50" s="5"/>
+      <c r="CD50" s="5"/>
+      <c r="CE50" s="5"/>
+      <c r="CF50" s="5"/>
+      <c r="CH50" s="5"/>
+      <c r="CI50" s="5"/>
+      <c r="CJ50" s="5"/>
+      <c r="CK50" s="5"/>
       <c r="CN50" s="3"/>
     </row>
     <row r="51" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
+      <c r="M51"/>
       <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
     </row>
     <row r="52" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
-      <c r="CL52" s="5"/>
+      <c r="M52"/>
+      <c r="N52"/>
+      <c r="BV52"/>
+      <c r="CI52" s="5"/>
+      <c r="CJ52" s="5"/>
     </row>
     <row r="53" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="CL53" s="5"/>
+      <c r="M53"/>
+      <c r="N53"/>
+      <c r="BV53"/>
+      <c r="CJ53" s="5"/>
     </row>
     <row r="54" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="AJ54" s="2"/>
-      <c r="CL54" s="5"/>
-      <c r="CU54" s="2"/>
+      <c r="M54"/>
+      <c r="O54" s="3"/>
+      <c r="AG54" s="2"/>
+      <c r="AO54" s="2"/>
+      <c r="BO54" s="2"/>
+      <c r="BP54" s="2"/>
+      <c r="CG54" s="2"/>
+      <c r="CM54" s="2"/>
     </row>
     <row r="55" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="CL55" s="5"/>
+      <c r="A55" s="2"/>
+      <c r="M55"/>
+      <c r="O55" s="3"/>
+      <c r="AG55" s="2"/>
+      <c r="AO55" s="2"/>
+      <c r="CG55" s="2"/>
     </row>
     <row r="56" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="O56"/>
-      <c r="W56"/>
-      <c r="X56"/>
-      <c r="CN56" s="3"/>
+      <c r="BU56" s="6"/>
+      <c r="CA56"/>
     </row>
     <row r="57" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="O57" s="3"/>
+      <c r="E57" s="2"/>
+      <c r="O57"/>
+      <c r="W57"/>
       <c r="X57"/>
+      <c r="BO57" s="2"/>
+      <c r="BP57" s="2"/>
+      <c r="CN57" s="3"/>
     </row>
     <row r="58" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="M58"/>
       <c r="O58" s="3"/>
       <c r="P58"/>
       <c r="Q58"/>
-      <c r="X58"/>
+      <c r="CN58" s="3"/>
     </row>
     <row r="59" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="M59"/>
       <c r="O59" s="3"/>
-      <c r="X59"/>
+      <c r="P59"/>
+      <c r="Q59"/>
+      <c r="CN59" s="3"/>
+    </row>
+    <row r="60" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A60" s="2"/>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="CL61" s="5"/>
     </row>
     <row r="62" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="CM62" s="3"/>
-      <c r="CN62" s="3"/>
+      <c r="CL62" s="5"/>
+    </row>
+    <row r="63" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="AJ63" s="2"/>
+      <c r="CL63" s="5"/>
+      <c r="CU63" s="2"/>
     </row>
     <row r="64" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="M64"/>
-      <c r="N64"/>
-      <c r="BV64"/>
-      <c r="CB64" s="14"/>
-      <c r="CI64" s="5"/>
-      <c r="CJ64" s="5"/>
-    </row>
-    <row r="65" spans="13:91" x14ac:dyDescent="0.25">
-      <c r="M65"/>
-      <c r="N65"/>
-      <c r="BV65"/>
-      <c r="CB65" s="14"/>
-      <c r="CJ65" s="5"/>
-    </row>
-    <row r="66" spans="13:91" x14ac:dyDescent="0.25">
-      <c r="O66"/>
+      <c r="CL64" s="5"/>
+    </row>
+    <row r="65" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="O65"/>
+      <c r="W65"/>
+      <c r="X65"/>
+      <c r="CN65" s="3"/>
+    </row>
+    <row r="66" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="O66" s="3"/>
       <c r="X66"/>
-      <c r="CM66" s="3"/>
-    </row>
-    <row r="69" spans="13:91" x14ac:dyDescent="0.25">
-      <c r="CL69" s="5"/>
-    </row>
-    <row r="70" spans="13:91" x14ac:dyDescent="0.25">
-      <c r="CL70" s="5"/>
-    </row>
-    <row r="76" spans="13:91" x14ac:dyDescent="0.25">
-      <c r="CL76" s="5"/>
-    </row>
-    <row r="77" spans="13:91" x14ac:dyDescent="0.25">
-      <c r="CL77" s="5"/>
-    </row>
-    <row r="79" spans="13:91" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="O67" s="3"/>
+      <c r="P67"/>
+      <c r="Q67"/>
+      <c r="X67"/>
+    </row>
+    <row r="68" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="O68" s="3"/>
+      <c r="X68"/>
+    </row>
+    <row r="71" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="CM71" s="3"/>
+      <c r="CN71" s="3"/>
+    </row>
+    <row r="73" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="M73"/>
+      <c r="N73"/>
+      <c r="BV73"/>
+      <c r="CB73" s="14"/>
+      <c r="CI73" s="5"/>
+      <c r="CJ73" s="5"/>
+    </row>
+    <row r="74" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="M74"/>
+      <c r="N74"/>
+      <c r="BV74"/>
+      <c r="CB74" s="14"/>
+      <c r="CJ74" s="5"/>
+    </row>
+    <row r="75" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="O75"/>
+      <c r="X75"/>
+      <c r="CM75" s="3"/>
+    </row>
+    <row r="78" spans="13:92" x14ac:dyDescent="0.25">
+      <c r="CL78" s="5"/>
+    </row>
+    <row r="79" spans="13:92" x14ac:dyDescent="0.25">
       <c r="CL79" s="5"/>
     </row>
-    <row r="80" spans="13:91" x14ac:dyDescent="0.25">
-      <c r="CL80" s="5"/>
-    </row>
-    <row r="81" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL81" s="5"/>
-    </row>
-    <row r="82" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL82" s="5"/>
-    </row>
-    <row r="83" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV83"/>
-    </row>
-    <row r="84" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV84"/>
-    </row>
     <row r="85" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV85"/>
       <c r="CL85" s="5"/>
     </row>
     <row r="86" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL86" s="5"/>
     </row>
-    <row r="87" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL87" s="5"/>
-    </row>
     <row r="88" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV88"/>
+      <c r="CL88" s="5"/>
     </row>
     <row r="89" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL89" s="5"/>
     </row>
+    <row r="90" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL90" s="5"/>
+    </row>
+    <row r="91" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL91" s="5"/>
+    </row>
+    <row r="92" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV92"/>
+    </row>
     <row r="93" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV93"/>
     </row>
     <row r="94" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV94"/>
       <c r="CL94" s="5"/>
     </row>
+    <row r="95" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL95" s="5"/>
+    </row>
+    <row r="96" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL96" s="5"/>
+    </row>
+    <row r="97" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV97"/>
+    </row>
+    <row r="98" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL98" s="5"/>
+    </row>
     <row r="102" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL102" s="5"/>
+      <c r="BV102"/>
     </row>
     <row r="103" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL103" s="5"/>
     </row>
-    <row r="104" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV104"/>
-    </row>
-    <row r="109" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV109"/>
-    </row>
-    <row r="110" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV110"/>
-      <c r="CL110" s="5"/>
-    </row>
     <row r="111" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL111" s="5"/>
     </row>
@@ -8155,28 +9405,17 @@
       <c r="CL112" s="5"/>
     </row>
     <row r="113" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL113" s="5"/>
-    </row>
-    <row r="114" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL114" s="5"/>
-    </row>
-    <row r="115" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV115"/>
-    </row>
-    <row r="116" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL116" s="5"/>
-    </row>
-    <row r="117" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL117" s="5"/>
+      <c r="BV113"/>
     </row>
     <row r="118" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL118" s="5"/>
+      <c r="BV118"/>
     </row>
     <row r="119" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV119"/>
       <c r="CL119" s="5"/>
     </row>
     <row r="120" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV120"/>
+      <c r="CL120" s="5"/>
     </row>
     <row r="121" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL121" s="5"/>
@@ -8188,7 +9427,13 @@
       <c r="CL123" s="5"/>
     </row>
     <row r="124" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL124" s="5"/>
+      <c r="BV124"/>
+    </row>
+    <row r="125" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL125" s="5"/>
+    </row>
+    <row r="126" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL126" s="5"/>
     </row>
     <row r="127" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL127" s="5"/>
@@ -8197,7 +9442,7 @@
       <c r="CL128" s="5"/>
     </row>
     <row r="129" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL129" s="5"/>
+      <c r="BV129"/>
     </row>
     <row r="130" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL130" s="5"/>
@@ -8205,14 +9450,11 @@
     <row r="131" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL131" s="5"/>
     </row>
+    <row r="132" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL132" s="5"/>
+    </row>
     <row r="133" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV133"/>
-    </row>
-    <row r="134" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL134" s="5"/>
-    </row>
-    <row r="135" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL135" s="5"/>
+      <c r="CL133" s="5"/>
     </row>
     <row r="136" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL136" s="5"/>
@@ -8220,14 +9462,22 @@
     <row r="137" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL137" s="5"/>
     </row>
-    <row r="141" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL141" s="5"/>
+    <row r="138" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL138" s="5"/>
+    </row>
+    <row r="139" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL139" s="5"/>
+    </row>
+    <row r="140" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL140" s="5"/>
+    </row>
+    <row r="142" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV142"/>
     </row>
     <row r="143" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV143"/>
+      <c r="CL143" s="5"/>
     </row>
     <row r="144" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV144"/>
       <c r="CL144" s="5"/>
     </row>
     <row r="145" spans="74:90" x14ac:dyDescent="0.25">
@@ -8236,20 +9486,15 @@
     <row r="146" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL146" s="5"/>
     </row>
-    <row r="147" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL147" s="5"/>
-    </row>
-    <row r="148" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL148" s="5"/>
-    </row>
     <row r="150" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV150"/>
-    </row>
-    <row r="151" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL151" s="5"/>
+      <c r="CL150" s="5"/>
     </row>
     <row r="152" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL152" s="5"/>
+      <c r="BV152"/>
+    </row>
+    <row r="153" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV153"/>
+      <c r="CL153" s="5"/>
     </row>
     <row r="154" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL154" s="5"/>
@@ -8257,161 +9502,168 @@
     <row r="155" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL155" s="5"/>
     </row>
+    <row r="156" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL156" s="5"/>
+    </row>
     <row r="157" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV157"/>
-    </row>
-    <row r="158" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL158" s="5"/>
+      <c r="CL157" s="5"/>
+    </row>
+    <row r="159" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV159"/>
+    </row>
+    <row r="160" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL160" s="5"/>
     </row>
     <row r="161" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL161" s="5"/>
     </row>
-    <row r="162" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL162" s="5"/>
-    </row>
-    <row r="165" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL165" s="5"/>
+    <row r="163" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL163" s="5"/>
+    </row>
+    <row r="164" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL164" s="5"/>
+    </row>
+    <row r="166" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV166"/>
     </row>
     <row r="167" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL167" s="5"/>
     </row>
-    <row r="169" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV169"/>
-    </row>
     <row r="170" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL170" s="5"/>
     </row>
     <row r="171" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL171" s="5"/>
     </row>
-    <row r="173" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL173" s="5"/>
-    </row>
     <row r="174" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL174" s="5"/>
     </row>
-    <row r="175" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL175" s="5"/>
-    </row>
-    <row r="180" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="176" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL176" s="5"/>
+    </row>
+    <row r="178" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV178"/>
+    </row>
+    <row r="179" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL179" s="5"/>
+    </row>
+    <row r="180" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL180" s="5"/>
     </row>
-    <row r="181" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL181" s="5"/>
-    </row>
-    <row r="184" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="182" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL182" s="5"/>
+    </row>
+    <row r="183" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL183" s="5"/>
+    </row>
+    <row r="184" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL184" s="5"/>
     </row>
-    <row r="185" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL185" s="5"/>
-    </row>
-    <row r="189" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="189" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL189" s="5"/>
     </row>
-    <row r="193" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="190" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL190" s="5"/>
+    </row>
+    <row r="193" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL193" s="5"/>
     </row>
-    <row r="195" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL195" s="5"/>
-    </row>
-    <row r="196" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL196" s="5"/>
-    </row>
-    <row r="198" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="194" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL194" s="5"/>
+    </row>
+    <row r="198" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL198" s="5"/>
     </row>
-    <row r="199" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL199" s="5"/>
-    </row>
-    <row r="201" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV201"/>
-    </row>
-    <row r="202" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV202"/>
+    <row r="202" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL202" s="5"/>
     </row>
-    <row r="203" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL203" s="5"/>
-    </row>
-    <row r="205" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="204" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL204" s="5"/>
+    </row>
+    <row r="205" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL205" s="5"/>
     </row>
+    <row r="207" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL207" s="5"/>
+    </row>
+    <row r="208" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL208" s="5"/>
+    </row>
+    <row r="210" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV210"/>
+    </row>
+    <row r="211" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV211"/>
+      <c r="CL211" s="5"/>
+    </row>
+    <row r="212" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL212" s="5"/>
+    </row>
     <row r="214" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV214"/>
-    </row>
-    <row r="215" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV215"/>
-      <c r="CL215" s="5"/>
-    </row>
-    <row r="216" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL216" s="5"/>
-    </row>
-    <row r="217" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL217" s="5"/>
-    </row>
-    <row r="218" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV218"/>
-    </row>
-    <row r="219" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV219"/>
-      <c r="CL219" s="5"/>
-    </row>
-    <row r="220" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL220" s="5"/>
-    </row>
-    <row r="222" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV222"/>
+      <c r="CL214" s="5"/>
     </row>
     <row r="223" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV223"/>
-      <c r="CL223" s="5"/>
     </row>
     <row r="224" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV224"/>
       <c r="CL224" s="5"/>
     </row>
+    <row r="225" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL225" s="5"/>
+    </row>
     <row r="226" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV226"/>
+      <c r="CL226" s="5"/>
     </row>
     <row r="227" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL227" s="5"/>
-    </row>
-    <row r="230" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL230" s="5"/>
-    </row>
-    <row r="234" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL234" s="5"/>
+      <c r="BV227"/>
+    </row>
+    <row r="228" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV228"/>
+      <c r="CL228" s="5"/>
+    </row>
+    <row r="229" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL229" s="5"/>
+    </row>
+    <row r="231" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV231"/>
+    </row>
+    <row r="232" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV232"/>
+      <c r="CL232" s="5"/>
+    </row>
+    <row r="233" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL233" s="5"/>
+    </row>
+    <row r="235" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV235"/>
     </row>
     <row r="236" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV236"/>
-    </row>
-    <row r="237" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL237" s="5"/>
-    </row>
-    <row r="244" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV244"/>
+      <c r="CL236" s="5"/>
+    </row>
+    <row r="239" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL239" s="5"/>
+    </row>
+    <row r="243" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL243" s="5"/>
     </row>
     <row r="245" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL245" s="5"/>
+      <c r="BV245"/>
     </row>
     <row r="246" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL246" s="5"/>
     </row>
-    <row r="248" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV248"/>
-    </row>
-    <row r="249" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV249"/>
-      <c r="CL249" s="5"/>
-    </row>
-    <row r="250" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL250" s="5"/>
-    </row>
-    <row r="256" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV256"/>
+    <row r="253" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV253"/>
+    </row>
+    <row r="254" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL254" s="5"/>
+    </row>
+    <row r="255" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL255" s="5"/>
     </row>
     <row r="257" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV257"/>
-      <c r="CL257" s="5"/>
     </row>
     <row r="258" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV258"/>
@@ -8420,35 +9672,43 @@
     <row r="259" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL259" s="5"/>
     </row>
-    <row r="264" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV264"/>
-    </row>
     <row r="265" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV265"/>
     </row>
-    <row r="269" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV269"/>
-    </row>
-    <row r="270" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL270" s="5"/>
-    </row>
-    <row r="271" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV271"/>
-    </row>
-    <row r="272" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL272" s="5"/>
-    </row>
-    <row r="282" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV282"/>
-    </row>
-    <row r="283" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL283" s="5"/>
-    </row>
-    <row r="285" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV285"/>
-    </row>
-    <row r="286" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL286" s="5"/>
+    <row r="266" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV266"/>
+      <c r="CL266" s="5"/>
+    </row>
+    <row r="267" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV267"/>
+      <c r="CL267" s="5"/>
+    </row>
+    <row r="268" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL268" s="5"/>
+    </row>
+    <row r="273" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV273"/>
+    </row>
+    <row r="274" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV274"/>
+    </row>
+    <row r="278" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV278"/>
+    </row>
+    <row r="279" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL279" s="5"/>
+    </row>
+    <row r="280" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV280"/>
+    </row>
+    <row r="281" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL281" s="5"/>
+    </row>
+    <row r="291" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV291"/>
+    </row>
+    <row r="292" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL292" s="5"/>
     </row>
     <row r="294" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV294"/>
@@ -8456,158 +9716,135 @@
     <row r="295" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL295" s="5"/>
     </row>
-    <row r="299" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV299"/>
-    </row>
-    <row r="300" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL300" s="5"/>
-    </row>
-    <row r="302" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV302"/>
-    </row>
     <row r="303" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL303" s="5"/>
-    </row>
-    <row r="319" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV319"/>
-    </row>
-    <row r="320" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV320"/>
-      <c r="CL320" s="5"/>
-    </row>
-    <row r="321" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV321"/>
-      <c r="CL321" s="5"/>
-    </row>
-    <row r="322" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV322"/>
-      <c r="CL322" s="5"/>
-    </row>
-    <row r="323" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV323"/>
-    </row>
-    <row r="325" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV325"/>
-    </row>
-    <row r="326" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV326"/>
-      <c r="CL326" s="5"/>
-    </row>
-    <row r="327" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV327"/>
-      <c r="CL327" s="5"/>
+      <c r="BV303"/>
+    </row>
+    <row r="304" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL304" s="5"/>
+    </row>
+    <row r="308" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV308"/>
+    </row>
+    <row r="309" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL309" s="5"/>
+    </row>
+    <row r="311" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV311"/>
+    </row>
+    <row r="312" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL312" s="5"/>
     </row>
     <row r="328" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL328" s="5"/>
+      <c r="BV328"/>
+    </row>
+    <row r="329" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV329"/>
+      <c r="CL329" s="5"/>
+    </row>
+    <row r="330" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV330"/>
+      <c r="CL330" s="5"/>
+    </row>
+    <row r="331" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV331"/>
+      <c r="CL331" s="5"/>
     </row>
     <row r="332" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV332"/>
     </row>
-    <row r="333" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL333" s="5"/>
+    <row r="334" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV334"/>
     </row>
     <row r="335" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV335"/>
+      <c r="CL335" s="5"/>
     </row>
     <row r="336" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV336"/>
       <c r="CL336" s="5"/>
     </row>
     <row r="337" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV337"/>
       <c r="CL337" s="5"/>
     </row>
-    <row r="338" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL338" s="5"/>
-    </row>
-    <row r="354" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV354"/>
-    </row>
-    <row r="355" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL355" s="5"/>
+    <row r="341" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV341"/>
+    </row>
+    <row r="342" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL342" s="5"/>
+    </row>
+    <row r="344" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV344"/>
+    </row>
+    <row r="345" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV345"/>
+      <c r="CL345" s="5"/>
+    </row>
+    <row r="346" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV346"/>
+      <c r="CL346" s="5"/>
+    </row>
+    <row r="347" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL347" s="5"/>
     </row>
     <row r="363" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL363" s="5"/>
+      <c r="BV363"/>
     </row>
     <row r="364" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL364" s="5"/>
     </row>
-    <row r="365" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL365" s="5"/>
-    </row>
-    <row r="366" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL366" s="5"/>
-    </row>
-    <row r="367" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL367" s="5"/>
-    </row>
-    <row r="369" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV369"/>
-    </row>
-    <row r="370" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL370" s="5"/>
-    </row>
-    <row r="371" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV371"/>
-    </row>
     <row r="372" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV372"/>
       <c r="CL372" s="5"/>
     </row>
     <row r="373" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL373" s="5"/>
     </row>
+    <row r="374" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL374" s="5"/>
+    </row>
     <row r="375" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV375"/>
+      <c r="CL375" s="5"/>
     </row>
     <row r="376" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV376"/>
       <c r="CL376" s="5"/>
     </row>
-    <row r="377" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV377"/>
-      <c r="CL377" s="5"/>
-    </row>
     <row r="378" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL378" s="5"/>
+      <c r="BV378"/>
+    </row>
+    <row r="379" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL379" s="5"/>
     </row>
     <row r="380" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL380" s="5"/>
+      <c r="BV380"/>
+    </row>
+    <row r="381" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV381"/>
+      <c r="CL381" s="5"/>
     </row>
     <row r="382" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL382" s="5"/>
     </row>
     <row r="384" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL384" s="5"/>
+      <c r="BV384"/>
+    </row>
+    <row r="385" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV385"/>
+      <c r="CL385" s="5"/>
+    </row>
+    <row r="386" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV386"/>
+      <c r="CL386" s="5"/>
     </row>
     <row r="387" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL387" s="5"/>
     </row>
-    <row r="388" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL388" s="5"/>
-    </row>
     <row r="389" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL389" s="5"/>
     </row>
-    <row r="390" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL390" s="5"/>
-    </row>
     <row r="391" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL391" s="5"/>
     </row>
-    <row r="392" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL392" s="5"/>
-    </row>
     <row r="393" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV393"/>
-    </row>
-    <row r="394" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV394"/>
-      <c r="CL394" s="5"/>
-    </row>
-    <row r="395" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV395"/>
-      <c r="CL395" s="5"/>
+      <c r="CL393" s="5"/>
     </row>
     <row r="396" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL396" s="5"/>
@@ -8621,21 +9858,24 @@
     <row r="399" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL399" s="5"/>
     </row>
+    <row r="400" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL400" s="5"/>
+    </row>
     <row r="401" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL401" s="5"/>
     </row>
     <row r="402" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL402" s="5"/>
+      <c r="BV402"/>
     </row>
     <row r="403" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV403"/>
+      <c r="CL403" s="5"/>
     </row>
     <row r="404" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV404"/>
       <c r="CL404" s="5"/>
     </row>
     <row r="405" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV405"/>
       <c r="CL405" s="5"/>
     </row>
     <row r="406" spans="74:90" x14ac:dyDescent="0.25">
@@ -8644,92 +9884,97 @@
     <row r="407" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL407" s="5"/>
     </row>
-    <row r="409" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL409" s="5"/>
+    <row r="408" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL408" s="5"/>
     </row>
     <row r="410" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL410" s="5"/>
     </row>
     <row r="411" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV411"/>
       <c r="CL411" s="5"/>
     </row>
     <row r="412" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV412"/>
-      <c r="CL412" s="5"/>
     </row>
     <row r="413" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV413"/>
       <c r="CL413" s="5"/>
     </row>
     <row r="414" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV414"/>
       <c r="CL414" s="5"/>
     </row>
     <row r="415" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL415" s="5"/>
     </row>
-    <row r="417" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV417"/>
-      <c r="CL417" s="5"/>
+    <row r="416" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL416" s="5"/>
     </row>
     <row r="418" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL418" s="5"/>
     </row>
     <row r="419" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL419" s="5"/>
+    </row>
+    <row r="420" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV420"/>
+      <c r="CL420" s="5"/>
     </row>
     <row r="421" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV421"/>
       <c r="CL421" s="5"/>
     </row>
     <row r="422" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV422"/>
       <c r="CL422" s="5"/>
     </row>
     <row r="423" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL423" s="5"/>
     </row>
-    <row r="425" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL425" s="5"/>
+    <row r="424" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL424" s="5"/>
+    </row>
+    <row r="426" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV426"/>
+      <c r="CL426" s="5"/>
     </row>
     <row r="427" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL427" s="5"/>
     </row>
+    <row r="428" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL428" s="5"/>
+    </row>
     <row r="430" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV430"/>
       <c r="CL430" s="5"/>
     </row>
     <row r="431" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV431"/>
       <c r="CL431" s="5"/>
     </row>
-    <row r="435" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV435"/>
+    <row r="432" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL432" s="5"/>
+    </row>
+    <row r="434" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL434" s="5"/>
     </row>
     <row r="436" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV436"/>
       <c r="CL436" s="5"/>
-    </row>
-    <row r="437" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV437"/>
-      <c r="CL437" s="5"/>
-    </row>
-    <row r="438" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL438" s="5"/>
     </row>
     <row r="439" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL439" s="5"/>
     </row>
     <row r="440" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV440"/>
-    </row>
-    <row r="441" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL441" s="5"/>
-    </row>
-    <row r="443" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL443" s="5"/>
+      <c r="CL440" s="5"/>
     </row>
     <row r="444" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL444" s="5"/>
+      <c r="BV444"/>
+    </row>
+    <row r="445" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV445"/>
+      <c r="CL445" s="5"/>
     </row>
     <row r="446" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV446"/>
       <c r="CL446" s="5"/>
     </row>
     <row r="447" spans="74:90" x14ac:dyDescent="0.25">
@@ -8739,19 +9984,16 @@
       <c r="CL448" s="5"/>
     </row>
     <row r="449" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL449" s="5"/>
+      <c r="BV449"/>
     </row>
     <row r="450" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL450" s="5"/>
     </row>
-    <row r="451" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL451" s="5"/>
-    </row>
     <row r="452" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL452" s="5"/>
     </row>
-    <row r="454" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV454"/>
+    <row r="453" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL453" s="5"/>
     </row>
     <row r="455" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL455" s="5"/>
@@ -8759,98 +10001,86 @@
     <row r="456" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL456" s="5"/>
     </row>
-    <row r="489" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU489" s="15"/>
-      <c r="BV489" s="16"/>
-    </row>
-    <row r="490" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H490" s="15"/>
-      <c r="CL490" s="15"/>
-    </row>
-    <row r="496" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV496"/>
-    </row>
-    <row r="497" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV497"/>
-      <c r="CL497" s="5"/>
-    </row>
-    <row r="498" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV498"/>
-      <c r="CL498" s="5"/>
-    </row>
-    <row r="499" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL499" s="5"/>
-    </row>
-    <row r="516" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV516"/>
-    </row>
-    <row r="517" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL517" s="5"/>
-    </row>
-    <row r="549" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV549"/>
-    </row>
-    <row r="550" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV550"/>
-      <c r="CL550" s="5"/>
-    </row>
-    <row r="551" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL551" s="5"/>
-    </row>
-    <row r="567" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV567"/>
-    </row>
-    <row r="568" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL568" s="5"/>
-    </row>
-    <row r="574" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV574"/>
-    </row>
-    <row r="575" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV575"/>
-      <c r="CL575" s="5"/>
-    </row>
-    <row r="576" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL576" s="5"/>
-    </row>
-    <row r="581" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV581"/>
-    </row>
-    <row r="582" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV582"/>
-      <c r="CL582" s="5"/>
+    <row r="457" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL457" s="5"/>
+    </row>
+    <row r="458" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL458" s="5"/>
+    </row>
+    <row r="459" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL459" s="5"/>
+    </row>
+    <row r="460" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL460" s="5"/>
+    </row>
+    <row r="461" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL461" s="5"/>
+    </row>
+    <row r="463" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV463"/>
+    </row>
+    <row r="464" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL464" s="5"/>
+    </row>
+    <row r="465" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL465" s="5"/>
+    </row>
+    <row r="498" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU498" s="15"/>
+      <c r="BV498" s="16"/>
+    </row>
+    <row r="499" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H499" s="15"/>
+      <c r="CL499" s="15"/>
+    </row>
+    <row r="505" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV505"/>
+    </row>
+    <row r="506" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV506"/>
+      <c r="CL506" s="5"/>
+    </row>
+    <row r="507" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV507"/>
+      <c r="CL507" s="5"/>
+    </row>
+    <row r="508" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL508" s="5"/>
+    </row>
+    <row r="525" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV525"/>
+    </row>
+    <row r="526" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL526" s="5"/>
+    </row>
+    <row r="558" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV558"/>
+    </row>
+    <row r="559" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV559"/>
+      <c r="CL559" s="5"/>
+    </row>
+    <row r="560" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL560" s="5"/>
+    </row>
+    <row r="576" spans="74:74" x14ac:dyDescent="0.25">
+      <c r="BV576"/>
+    </row>
+    <row r="577" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL577" s="5"/>
     </row>
     <row r="583" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV583"/>
-      <c r="CL583" s="5"/>
     </row>
     <row r="584" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV584"/>
       <c r="CL584" s="5"/>
     </row>
     <row r="585" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV585"/>
       <c r="CL585" s="5"/>
-    </row>
-    <row r="586" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV586"/>
-      <c r="CL586" s="5"/>
-    </row>
-    <row r="587" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV587"/>
-      <c r="CL587" s="5"/>
-    </row>
-    <row r="588" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV588"/>
-      <c r="CL588" s="5"/>
-    </row>
-    <row r="589" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV589"/>
-      <c r="CL589" s="5"/>
     </row>
     <row r="590" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV590"/>
-      <c r="CL590" s="5"/>
     </row>
     <row r="591" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV591"/>
@@ -8877,268 +10107,288 @@
       <c r="CL596" s="5"/>
     </row>
     <row r="597" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV597"/>
       <c r="CL597" s="5"/>
+    </row>
+    <row r="598" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV598"/>
+      <c r="CL598" s="5"/>
+    </row>
+    <row r="599" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV599"/>
+      <c r="CL599" s="5"/>
+    </row>
+    <row r="600" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV600"/>
+      <c r="CL600" s="5"/>
     </row>
     <row r="601" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV601"/>
+      <c r="CL601" s="5"/>
     </row>
     <row r="602" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV602"/>
       <c r="CL602" s="5"/>
     </row>
     <row r="603" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV603"/>
       <c r="CL603" s="5"/>
     </row>
     <row r="604" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV604"/>
+      <c r="CL604" s="5"/>
     </row>
     <row r="605" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV605"/>
       <c r="CL605" s="5"/>
     </row>
-    <row r="608" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV608"/>
-    </row>
-    <row r="609" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV609"/>
-      <c r="CL609" s="5"/>
+    <row r="606" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL606" s="5"/>
     </row>
     <row r="610" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL610" s="5"/>
-    </row>
-    <row r="641" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV641"/>
-    </row>
-    <row r="642" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV642"/>
-      <c r="CL642" s="5"/>
-    </row>
-    <row r="643" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV643"/>
-      <c r="CL643" s="5"/>
-    </row>
-    <row r="644" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV644"/>
-      <c r="CL644" s="5"/>
-    </row>
-    <row r="645" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV645"/>
-      <c r="CL645" s="5"/>
-    </row>
-    <row r="646" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV646"/>
-      <c r="CL646" s="5"/>
-    </row>
-    <row r="647" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV647"/>
-      <c r="CL647" s="5"/>
-    </row>
-    <row r="648" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV648"/>
-      <c r="CL648" s="5"/>
-    </row>
-    <row r="649" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL649" s="5"/>
+      <c r="BV610"/>
+    </row>
+    <row r="611" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV611"/>
+      <c r="CL611" s="5"/>
+    </row>
+    <row r="612" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL612" s="5"/>
+    </row>
+    <row r="613" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV613"/>
+    </row>
+    <row r="614" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL614" s="5"/>
+    </row>
+    <row r="617" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV617"/>
+    </row>
+    <row r="618" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV618"/>
+      <c r="CL618" s="5"/>
+    </row>
+    <row r="619" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL619" s="5"/>
+    </row>
+    <row r="650" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV650"/>
     </row>
     <row r="651" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV651"/>
+      <c r="CL651" s="5"/>
     </row>
     <row r="652" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV652"/>
       <c r="CL652" s="5"/>
+    </row>
+    <row r="653" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV653"/>
+      <c r="CL653" s="5"/>
+    </row>
+    <row r="654" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV654"/>
+      <c r="CL654" s="5"/>
+    </row>
+    <row r="655" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV655"/>
+      <c r="CL655" s="5"/>
     </row>
     <row r="656" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV656"/>
+      <c r="CL656" s="5"/>
     </row>
     <row r="657" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV657"/>
       <c r="CL657" s="5"/>
+    </row>
+    <row r="658" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL658" s="5"/>
     </row>
     <row r="660" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV660"/>
     </row>
     <row r="661" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV661"/>
       <c r="CL661" s="5"/>
     </row>
-    <row r="662" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV662"/>
-      <c r="CL662" s="5"/>
-    </row>
-    <row r="663" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV663"/>
-      <c r="CL663" s="5"/>
-    </row>
-    <row r="664" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL664" s="5"/>
+    <row r="665" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV665"/>
+    </row>
+    <row r="666" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL666" s="5"/>
+    </row>
+    <row r="669" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV669"/>
+    </row>
+    <row r="670" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV670"/>
+      <c r="CL670" s="5"/>
     </row>
     <row r="671" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV671"/>
+      <c r="CL671" s="5"/>
     </row>
     <row r="672" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV672"/>
       <c r="CL672" s="5"/>
     </row>
-    <row r="675" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV675"/>
-    </row>
-    <row r="676" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV676"/>
-      <c r="CL676" s="5"/>
-    </row>
-    <row r="677" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV677"/>
-      <c r="CL677" s="5"/>
-    </row>
-    <row r="678" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV678"/>
-      <c r="CL678" s="5"/>
-    </row>
-    <row r="679" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL679" s="5"/>
+    <row r="673" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL673" s="5"/>
+    </row>
+    <row r="680" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV680"/>
     </row>
     <row r="681" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV681"/>
-    </row>
-    <row r="682" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV682"/>
-      <c r="CL682" s="5"/>
-    </row>
-    <row r="683" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL683" s="5"/>
+      <c r="CL681" s="5"/>
     </row>
     <row r="684" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL684">
+      <c r="BV684"/>
+    </row>
+    <row r="685" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV685"/>
+      <c r="CL685" s="5"/>
+    </row>
+    <row r="686" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV686"/>
+      <c r="CL686" s="5"/>
+    </row>
+    <row r="687" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV687"/>
+      <c r="CL687" s="5"/>
+    </row>
+    <row r="688" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL688" s="5"/>
+    </row>
+    <row r="690" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV690"/>
+    </row>
+    <row r="691" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV691"/>
+      <c r="CL691" s="5"/>
+    </row>
+    <row r="692" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL692" s="5"/>
+    </row>
+    <row r="693" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL693">
         <v>0.15</v>
       </c>
     </row>
-    <row r="686" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL686">
+    <row r="695" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL695">
         <v>0.2</v>
       </c>
     </row>
-    <row r="687" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL687">
+    <row r="696" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL696">
         <v>0.1</v>
       </c>
     </row>
-    <row r="689" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL689">
+    <row r="698" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL698">
         <v>0.2</v>
       </c>
     </row>
-    <row r="696" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL696">
+    <row r="705" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL705">
         <v>1</v>
       </c>
     </row>
-    <row r="698" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL698">
+    <row r="707" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL707">
         <v>0.4</v>
       </c>
     </row>
-    <row r="699" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL699">
+    <row r="708" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL708">
         <v>0.6</v>
       </c>
     </row>
-    <row r="702" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL702">
+    <row r="711" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL711">
         <v>0.5</v>
       </c>
     </row>
-    <row r="703" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL703">
+    <row r="712" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL712">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="704" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL704">
+    <row r="713" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL713">
         <v>0.2</v>
       </c>
     </row>
-    <row r="707" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV707"/>
-    </row>
-    <row r="708" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV708"/>
-      <c r="CL708" s="5"/>
-    </row>
-    <row r="709" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV709"/>
-      <c r="CL709" s="5"/>
-    </row>
-    <row r="710" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV710"/>
-      <c r="CL710" s="5"/>
-    </row>
-    <row r="711" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV711"/>
-      <c r="CL711" s="5"/>
-    </row>
-    <row r="712" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV712"/>
-      <c r="CL712" s="5"/>
-    </row>
-    <row r="713" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV713"/>
-      <c r="CL713" s="5"/>
-    </row>
-    <row r="714" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV714"/>
-      <c r="CL714" s="5"/>
-    </row>
-    <row r="715" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV715"/>
-      <c r="CL715" s="5"/>
-    </row>
     <row r="716" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL716" s="5"/>
+      <c r="BV716"/>
     </row>
     <row r="717" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV717"/>
+      <c r="CL717" s="5"/>
     </row>
     <row r="718" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV718"/>
       <c r="CL718" s="5"/>
     </row>
+    <row r="719" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV719"/>
+      <c r="CL719" s="5"/>
+    </row>
+    <row r="720" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV720"/>
+      <c r="CL720" s="5"/>
+    </row>
+    <row r="721" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV721"/>
+      <c r="CL721" s="5"/>
+    </row>
+    <row r="722" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV722"/>
+      <c r="CL722" s="5"/>
+    </row>
+    <row r="723" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV723"/>
+      <c r="CL723" s="5"/>
+    </row>
+    <row r="724" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV724"/>
+      <c r="CL724" s="5"/>
+    </row>
+    <row r="725" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL725" s="5"/>
+    </row>
+    <row r="726" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV726"/>
+    </row>
     <row r="727" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV727"/>
-    </row>
-    <row r="728" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV728"/>
-      <c r="CL728" s="5"/>
-    </row>
-    <row r="729" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV729"/>
-      <c r="CL729" s="5"/>
-    </row>
-    <row r="730" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV730"/>
-      <c r="CL730" s="5"/>
-    </row>
-    <row r="731" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV731"/>
-      <c r="CL731" s="5"/>
-    </row>
-    <row r="732" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV732"/>
-      <c r="CL732" s="5"/>
-    </row>
-    <row r="733" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV733"/>
-      <c r="CL733" s="5"/>
-    </row>
-    <row r="734" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV734"/>
-      <c r="CL734" s="5"/>
-    </row>
-    <row r="735" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL735" s="5"/>
+      <c r="CL727" s="5"/>
     </row>
     <row r="736" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV736"/>
     </row>
     <row r="737" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV737"/>
       <c r="CL737" s="5"/>
+    </row>
+    <row r="738" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV738"/>
+      <c r="CL738" s="5"/>
+    </row>
+    <row r="739" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV739"/>
+      <c r="CL739" s="5"/>
+    </row>
+    <row r="740" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV740"/>
+      <c r="CL740" s="5"/>
+    </row>
+    <row r="741" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV741"/>
+      <c r="CL741" s="5"/>
     </row>
     <row r="742" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV742"/>
+      <c r="CL742" s="5"/>
     </row>
     <row r="743" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV743"/>
@@ -9151,128 +10401,114 @@
       <c r="BV745"/>
     </row>
     <row r="746" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV746"/>
       <c r="CL746" s="5"/>
-    </row>
-    <row r="747" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL747" s="5"/>
-    </row>
-    <row r="748" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV748"/>
-    </row>
-    <row r="749" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV749"/>
-      <c r="CL749" s="5"/>
-    </row>
-    <row r="750" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV750"/>
-      <c r="CL750" s="5"/>
     </row>
     <row r="751" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV751"/>
-      <c r="CL751" s="5"/>
     </row>
     <row r="752" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV752"/>
       <c r="CL752" s="5"/>
     </row>
-    <row r="756" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV756"/>
-    </row>
-    <row r="757" spans="8:90" x14ac:dyDescent="0.25">
+    <row r="753" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL753" s="5"/>
+    </row>
+    <row r="754" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV754"/>
+    </row>
+    <row r="755" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV755"/>
+      <c r="CL755" s="5"/>
+    </row>
+    <row r="756" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL756" s="5"/>
+    </row>
+    <row r="757" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV757"/>
-      <c r="CL757" s="5"/>
-    </row>
-    <row r="758" spans="8:90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="758" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV758"/>
       <c r="CL758" s="5"/>
     </row>
-    <row r="759" spans="8:90" x14ac:dyDescent="0.25">
+    <row r="759" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV759"/>
       <c r="CL759" s="5"/>
     </row>
-    <row r="760" spans="8:90" x14ac:dyDescent="0.25">
+    <row r="760" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV760"/>
-    </row>
-    <row r="761" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL760" s="5"/>
+    </row>
+    <row r="761" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL761" s="5"/>
     </row>
-    <row r="762" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU762" s="15"/>
-      <c r="BV762" s="16"/>
-    </row>
-    <row r="763" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H763" s="15"/>
-      <c r="CL763" s="15"/>
-    </row>
-    <row r="780" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV780"/>
-    </row>
-    <row r="781" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV781"/>
-      <c r="CL781" s="5"/>
-    </row>
-    <row r="782" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV782"/>
-      <c r="CL782" s="5"/>
-    </row>
-    <row r="783" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV783"/>
-      <c r="CL783" s="5"/>
-    </row>
-    <row r="784" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL784" s="5"/>
-    </row>
-    <row r="785" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV785"/>
-    </row>
-    <row r="786" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV786"/>
-      <c r="CL786" s="5"/>
-    </row>
-    <row r="787" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU787" s="15"/>
-      <c r="BV787" s="16"/>
-      <c r="CL787" s="5"/>
-    </row>
-    <row r="788" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H788" s="15"/>
-      <c r="CL788" s="15"/>
+    <row r="765" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV765"/>
+    </row>
+    <row r="766" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV766"/>
+      <c r="CL766" s="5"/>
+    </row>
+    <row r="767" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV767"/>
+      <c r="CL767" s="5"/>
+    </row>
+    <row r="768" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL768" s="5"/>
+    </row>
+    <row r="769" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV769"/>
+    </row>
+    <row r="770" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL770" s="5"/>
+    </row>
+    <row r="771" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU771" s="15"/>
+      <c r="BV771" s="16"/>
+    </row>
+    <row r="772" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H772" s="15"/>
+      <c r="CL772" s="15"/>
+    </row>
+    <row r="789" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV789"/>
+    </row>
+    <row r="790" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV790"/>
+      <c r="CL790" s="5"/>
     </row>
     <row r="791" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV791"/>
+      <c r="CL791" s="5"/>
     </row>
     <row r="792" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV792"/>
       <c r="CL792" s="5"/>
     </row>
     <row r="793" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV793"/>
       <c r="CL793" s="5"/>
     </row>
     <row r="794" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV794"/>
-      <c r="CL794" s="5"/>
     </row>
     <row r="795" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV795"/>
       <c r="CL795" s="5"/>
     </row>
     <row r="796" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV796"/>
+      <c r="BU796" s="15"/>
+      <c r="BV796" s="16"/>
       <c r="CL796" s="5"/>
     </row>
     <row r="797" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV797"/>
-      <c r="CL797" s="5"/>
-    </row>
-    <row r="798" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV798"/>
-      <c r="CL798" s="5"/>
-    </row>
-    <row r="799" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="CL799" s="5"/>
+      <c r="H797" s="15"/>
+      <c r="CL797" s="15"/>
+    </row>
+    <row r="800" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV800"/>
     </row>
     <row r="801" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV801"/>
+      <c r="CL801" s="5"/>
     </row>
     <row r="802" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV802"/>
@@ -9295,18 +10531,14 @@
       <c r="CL806" s="5"/>
     </row>
     <row r="807" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV807"/>
       <c r="CL807" s="5"/>
     </row>
     <row r="808" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV808"/>
-    </row>
-    <row r="809" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV809"/>
-      <c r="CL809" s="5"/>
+      <c r="CL808" s="5"/>
     </row>
     <row r="810" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV810"/>
-      <c r="CL810" s="5"/>
     </row>
     <row r="811" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV811"/>
@@ -9329,12 +10561,10 @@
       <c r="CL815" s="5"/>
     </row>
     <row r="816" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV816"/>
       <c r="CL816" s="5"/>
     </row>
     <row r="817" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV817"/>
-      <c r="CL817" s="5"/>
     </row>
     <row r="818" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV818"/>
@@ -9417,10 +10647,12 @@
       <c r="CL837" s="5"/>
     </row>
     <row r="838" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV838"/>
       <c r="CL838" s="5"/>
     </row>
     <row r="839" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV839"/>
+      <c r="CL839" s="5"/>
     </row>
     <row r="840" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV840"/>
@@ -9431,7 +10663,41 @@
       <c r="CL841" s="5"/>
     </row>
     <row r="842" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV842"/>
       <c r="CL842" s="5"/>
+    </row>
+    <row r="843" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV843"/>
+      <c r="CL843" s="5"/>
+    </row>
+    <row r="844" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV844"/>
+      <c r="CL844" s="5"/>
+    </row>
+    <row r="845" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV845"/>
+      <c r="CL845" s="5"/>
+    </row>
+    <row r="846" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV846"/>
+      <c r="CL846" s="5"/>
+    </row>
+    <row r="847" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL847" s="5"/>
+    </row>
+    <row r="848" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV848"/>
+    </row>
+    <row r="849" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV849"/>
+      <c r="CL849" s="5"/>
+    </row>
+    <row r="850" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV850"/>
+      <c r="CL850" s="5"/>
+    </row>
+    <row r="851" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL851" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
@@ -9443,10 +10709,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="1" max="1" width="18.08203125" customWidth="1"/>
     <col min="2" max="2" width="31.25" customWidth="1"/>
     <col min="7" max="7" width="18.75" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
@@ -9465,37 +10731,37 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>361</v>
+      </c>
+      <c r="F1" t="s">
         <v>362</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>363</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>364</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>365</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>366</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>367</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>368</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>369</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>370</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -9509,43 +10775,43 @@
         <v>76</v>
       </c>
       <c r="E2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F2" t="s">
         <v>373</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>374</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>375</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>376</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>377</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>378</v>
-      </c>
-      <c r="K2" t="s">
-        <v>379</v>
       </c>
       <c r="L2" t="s">
         <v>52</v>
       </c>
       <c r="M2" t="s">
+        <v>379</v>
+      </c>
+      <c r="N2" t="s">
         <v>380</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>381</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>383</v>
-      </c>
       <c r="Q2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -9574,13 +10840,13 @@
         <v>115</v>
       </c>
       <c r="J3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K3" t="s">
         <v>116</v>
       </c>
       <c r="L3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M3" t="s">
         <v>115</v>
@@ -9589,7 +10855,7 @@
         <v>115</v>
       </c>
       <c r="O3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P3" t="s">
         <v>115</v>
@@ -9600,58 +10866,121 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="Q4" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="K9"/>
-      <c r="P9"/>
-    </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="K11"/>
-      <c r="P11"/>
-    </row>
-    <row r="12" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="K12"/>
-      <c r="P12"/>
+        <v>466</v>
+      </c>
+      <c r="Q6" s="2"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="K10"/>
+      <c r="P10"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K13"/>
+      <c r="P13"/>
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="J14"/>
+      <c r="A14" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="K14"/>
       <c r="P14"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="J18"/>
-      <c r="P18"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="Q20" s="2"/>
+      <c r="Q14" s="3" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J16"/>
+      <c r="P16"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J20"/>
+      <c r="P20"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="Q22" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
@@ -9675,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9686,10 +11015,10 @@
         <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9700,7 +11029,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D3" t="s">
         <v>124</v>
@@ -9708,16 +11037,16 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -9729,7 +11058,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:I5"/>
+  <dimension ref="A2:I6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -9749,22 +11078,22 @@
         <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E2" t="s">
         <v>71</v>
       </c>
       <c r="F2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G2" t="s">
         <v>387</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>388</v>
       </c>
-      <c r="H2" t="s">
-        <v>389</v>
-      </c>
       <c r="I2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -9797,14 +11126,43 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>507</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I6" s="2" t="s">
+        <v>553</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
@@ -9830,34 +11188,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C1" t="s">
         <v>390</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>391</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>392</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>393</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>394</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>395</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>396</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>397</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>398</v>
-      </c>
-      <c r="L1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -9865,34 +11223,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C2" t="s">
         <v>400</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>401</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>402</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>403</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>404</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>405</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>406</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>407</v>
       </c>
-      <c r="J2" t="s">
-        <v>408</v>
-      </c>
       <c r="K2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L2" t="s">
         <v>96</v>
@@ -9909,7 +11267,7 @@
         <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -9969,22 +11327,22 @@
         <v>76</v>
       </c>
       <c r="D2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E2" t="s">
         <v>410</v>
-      </c>
-      <c r="E2" t="s">
-        <v>411</v>
       </c>
       <c r="F2" t="s">
         <v>78</v>
       </c>
       <c r="G2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H2" t="s">
         <v>269</v>
       </c>
       <c r="I2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J2" t="s">
         <v>53</v>
@@ -10013,7 +11371,7 @@
         <v>117</v>
       </c>
       <c r="H3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I3" t="s">
         <v>117</v>
@@ -10050,28 +11408,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -10079,28 +11437,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -10134,28 +11492,28 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>437</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Diy优胜/第一届.xlsx
+++ b/Excel/Diy优胜/第一届.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Diy优胜\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD0DC7C-1995-44AD-8015-781A2459A876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43301943-2791-4B06-824F-F39CAD87FDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="588">
   <si>
     <t>Id</t>
   </si>
@@ -1738,18 +1738,10 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>部署干员</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>死亡</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>{"ExTarget":"流涟"}</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>Target.MainSkill != null AND Target.MainSkill.SkillData.PowerType == 1</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -1809,9 +1801,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>流涟可生成标记</t>
-  </si>
-  <si>
     <t>流涟回复技力</t>
   </si>
   <si>
@@ -1823,10 +1812,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>{"召唤物ID":"流涟","召唤位置":"使用本技能索敌位置","部署模式":"追加","召唤物方向":"固定方向"}</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>{"召唤物ID":"流涟","召唤位置":"使用自身位置","部署模式":"追加","召唤物方向":"固定方向"}</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -1888,10 +1873,6 @@
   </si>
   <si>
     <t>时蒙1</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"LifeTime":8,"InitRadius":0.8,"MaxRadius":2.4,"RadiusExponentRate":0.2,"Trigger":1,"MoveHeight":2,"TriggerTimes":-1,"TargetTeam":2,"MaxTargetCount":-1}</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -2200,10 +2181,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>减速</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>时蒙1,时蒙2,时蒙3</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -2218,14 +2195,6 @@
     <t>midn_skill_01_trail</t>
   </si>
   <si>
-    <t>{"LifeTime":0,"Radius":1.4,"Trigger":0.02,"MoveHeight":0,"TriggerTimes":1,"TargetTeam":2,"MaxTargetCount":6}</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"LiftTime":0,"Radius":0.8,"Trigger":0.02,"MoveHeight":0.5,"TriggerTimes":1,"TargetTeam":2,"MaxTargetCount":-1}</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>终点距离</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -2234,10 +2203,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>时蒙2普攻,时蒙2获取流涟,时蒙2影响流涟,时蒙2锁血</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>锁血</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -2250,15 +2215,143 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>流涟普攻,流涟2普攻,流涟2锁血,生成下级流涟,通用绝食,流涟相互连接</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>时蒙a流涟</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>打数溢出转换</t>
+    <t>未攻击</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>ew3类部署干员</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"LifeTime":8,"InitRadius":0.8,"MaxRadius":2.4,"RadiusExponentRate":0.2,"Trigger":1,"MoveHeight":2,"TriggerTimes":-1,"TargetTeam":3,"MaxTargetCount":-1}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙1索敌</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙1攻击</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙1对流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙1攻击,时蒙1对流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙3索敌</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙3对敌</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙3对流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙3影响流涟,时蒙3对敌,时蒙3对流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙3索敌,减速</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>史都华德击中</t>
+  </si>
+  <si>
+    <t>深海色击中</t>
+  </si>
+  <si>
+    <t>守林人2击中</t>
+  </si>
+  <si>
+    <t>{"召唤物ID":"流涟","召唤位置":"使用本技能索敌位置","半径":1.7}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>-生成流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>溢出打数转化</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>打数溢出</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙3加攻速</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值变化叠加</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"MaxLevel":99,"t":["AgiAdd"]}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟3加攻速</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙3额外打数</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外目标依层数</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟3回复技力</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"目标技能":"流涟相互连接","技力":1,"提示":0,"无视阻回":0}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>流涟回复技力,流涟3回复技力</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙2a流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙2索敌</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"LiftTime":0,"Radius":0.8,"Trigger":0.02,"MoveHeight":0.5,"TriggerTimes":1,"TargetTeam":3,"MaxTargetCount":-1}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙2普攻,时蒙2获取流涟,时蒙2影响流涟,时蒙2锁血,时蒙2索敌</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>时蒙a流涟,时蒙2a流涟</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>空爆击中</t>
+  </si>
+  <si>
+    <t>流涟普攻,流涟2普攻,流涟2锁血,通用绝食,流涟3加攻速,流涟可生成标记</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -2411,6 +2504,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2526,7 +2620,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3524,10 +3618,10 @@
         <v>126</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3548,7 +3642,7 @@
         <v>0.25</v>
       </c>
       <c r="BB5" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="BD5" s="2" t="s">
         <v>441</v>
@@ -3654,10 +3748,10 @@
         <v>439</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>486</v>
+        <v>587</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>475</v>
       </c>
       <c r="AK6">
         <v>0</v>
@@ -3674,9 +3768,6 @@
       <c r="AP6">
         <v>0.5</v>
       </c>
-      <c r="AQ6">
-        <v>1</v>
-      </c>
       <c r="AV6" s="2" t="s">
         <v>463</v>
       </c>
@@ -3693,7 +3784,7 @@
         <v>132</v>
       </c>
       <c r="BN6" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="BP6" s="2" t="s">
         <v>134</v>
@@ -3702,7 +3793,7 @@
         <v>134</v>
       </c>
       <c r="BR6" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="BS6">
         <v>1</v>
@@ -6542,7 +6633,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DJ851"/>
+  <dimension ref="A1:DJ856"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -7180,7 +7271,7 @@
         <v>304</v>
       </c>
       <c r="BW2" s="6" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BX2" s="6" t="s">
         <v>305</v>
@@ -7657,7 +7748,7 @@
         <v>445</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="5" t="s">
@@ -7709,7 +7800,7 @@
       </c>
       <c r="O7"/>
       <c r="P7" s="2" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="AC7">
         <v>2</v>
@@ -7718,7 +7809,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="AT7" t="s">
         <v>458</v>
@@ -7732,11 +7823,12 @@
       <c r="BD7">
         <v>1</v>
       </c>
-      <c r="BP7" s="2" t="s">
-        <v>562</v>
-      </c>
+      <c r="BO7" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="BP7" s="2"/>
       <c r="CB7" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="CG7" s="2" t="s">
         <v>460</v>
@@ -7747,7 +7839,9 @@
       <c r="CI7" t="s">
         <v>462</v>
       </c>
-      <c r="CJ7" s="22"/>
+      <c r="CJ7" s="2" t="s">
+        <v>576</v>
+      </c>
       <c r="CN7" s="2" t="s">
         <v>463</v>
       </c>
@@ -7755,20 +7849,30 @@
         <v>9999</v>
       </c>
       <c r="CU7" s="2"/>
+      <c r="CY7" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="J8" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>553</v>
+      </c>
       <c r="K8" s="5" t="s">
-        <v>446</v>
+        <v>456</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>571</v>
       </c>
       <c r="O8"/>
-      <c r="P8" s="2"/>
+      <c r="P8" s="2" t="s">
+        <v>518</v>
+      </c>
       <c r="AC8">
         <v>1</v>
       </c>
@@ -7776,17 +7880,26 @@
         <v>1</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="AO8" s="2" t="s">
-        <v>542</v>
+        <v>537</v>
+      </c>
+      <c r="AR8" s="23" t="s">
+        <v>569</v>
       </c>
       <c r="AV8">
         <v>20</v>
       </c>
       <c r="AX8" s="2"/>
+      <c r="BO8" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="BP8" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="CB8" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="CG8" s="2" t="s">
         <v>460</v>
@@ -7798,7 +7911,7 @@
         <v>462</v>
       </c>
       <c r="CJ8" s="22" t="s">
-        <v>487</v>
+        <v>580</v>
       </c>
       <c r="CN8" s="2" t="s">
         <v>463</v>
@@ -7807,130 +7920,160 @@
         <v>9999</v>
       </c>
       <c r="CU8" s="2"/>
+      <c r="CY8" t="s">
+        <v>566</v>
+      </c>
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>467</v>
+        <v>581</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="H9" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>553</v>
+      </c>
       <c r="K9" s="5" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>465</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="P9" s="2"/>
       <c r="AC9">
         <v>3</v>
       </c>
       <c r="AD9">
         <v>1</v>
       </c>
-      <c r="AF9">
+      <c r="AJ9" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="AO9" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="AR9" s="23" t="s">
+        <v>569</v>
+      </c>
+      <c r="AV9">
+        <v>20</v>
+      </c>
+      <c r="AX9" s="2"/>
+      <c r="BJ9">
+        <v>1.7</v>
+      </c>
+      <c r="BK9">
         <v>1</v>
       </c>
-      <c r="AG9" s="2"/>
-      <c r="AH9" s="2">
+      <c r="BL9">
         <v>1</v>
       </c>
-      <c r="AO9" s="2"/>
-      <c r="AX9" s="2"/>
-      <c r="BD9">
+      <c r="BO9" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="BP9" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="CB9" s="2"/>
+      <c r="CG9" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="CH9" t="s">
+        <v>461</v>
+      </c>
+      <c r="CI9" t="s">
+        <v>462</v>
+      </c>
+      <c r="CJ9" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="CN9" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="CR9">
+        <v>9999</v>
+      </c>
+      <c r="CU9" s="2"/>
+      <c r="CY9" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="K10" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="AC10">
+        <v>3</v>
+      </c>
+      <c r="AD10">
         <v>1</v>
       </c>
-      <c r="CG9" s="2"/>
-      <c r="CL9" s="2"/>
-      <c r="CN9" s="2"/>
-      <c r="CO9" s="2"/>
-      <c r="CU9" s="2" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="10" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="AF10">
+        <v>1</v>
+      </c>
       <c r="AG10" s="2"/>
-      <c r="AH10" s="2"/>
+      <c r="AH10" s="2">
+        <v>1</v>
+      </c>
       <c r="AO10" s="2"/>
       <c r="AX10" s="2"/>
+      <c r="BD10">
+        <v>1</v>
+      </c>
       <c r="CG10" s="2"/>
       <c r="CL10" s="2"/>
       <c r="CN10" s="2"/>
       <c r="CO10" s="2"/>
-      <c r="CU10" s="2"/>
+      <c r="CU10" s="2" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F11" t="s">
-        <v>550</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="AC11">
-        <v>2</v>
-      </c>
-      <c r="AD11">
-        <v>1</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="H11" s="2"/>
       <c r="AG11" s="2"/>
-      <c r="AO11" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>516</v>
-      </c>
-      <c r="AX11" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="AZ11">
-        <v>1</v>
-      </c>
-      <c r="BD11">
-        <v>1</v>
-      </c>
-      <c r="CB11" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="CG11" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="CH11" t="s">
-        <v>461</v>
-      </c>
-      <c r="CI11" t="s">
-        <v>462</v>
-      </c>
+      <c r="AH11" s="2"/>
+      <c r="AO11" s="2"/>
+      <c r="AX11" s="2"/>
+      <c r="CG11" s="2"/>
       <c r="CL11" s="2"/>
       <c r="CN11" s="2"/>
       <c r="CO11" s="2"/>
+      <c r="CU11" s="2"/>
     </row>
     <row r="12" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>529</v>
+        <v>510</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="F12" t="s">
+        <v>544</v>
+      </c>
       <c r="K12" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="O12" s="5" t="s">
-        <v>523</v>
+      <c r="P12" s="5" t="s">
+        <v>518</v>
       </c>
       <c r="AC12">
         <v>2</v>
@@ -7940,10 +8083,10 @@
       </c>
       <c r="AG12" s="2"/>
       <c r="AO12" s="2" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="AT12" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="AX12" s="2" t="s">
         <v>459</v>
@@ -7954,17 +8097,8 @@
       <c r="BD12">
         <v>1</v>
       </c>
-      <c r="BJ12">
-        <v>1.7</v>
-      </c>
-      <c r="BK12">
-        <v>1</v>
-      </c>
-      <c r="BL12">
-        <v>1</v>
-      </c>
       <c r="CB12" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="CG12" s="2" t="s">
         <v>460</v>
@@ -7978,109 +8112,125 @@
       <c r="CL12" s="2"/>
       <c r="CN12" s="2"/>
       <c r="CO12" s="2"/>
+      <c r="CY12" t="s">
+        <v>586</v>
+      </c>
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>477</v>
+        <v>524</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="H13" s="2"/>
       <c r="K13" s="5" t="s">
-        <v>446</v>
+        <v>456</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>518</v>
       </c>
       <c r="AC13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD13">
         <v>1</v>
       </c>
       <c r="AG13" s="2"/>
-      <c r="AH13" s="2">
+      <c r="AO13" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>511</v>
+      </c>
+      <c r="AX13" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="AZ13">
         <v>1</v>
       </c>
-      <c r="AO13" s="2"/>
-      <c r="AX13" s="2"/>
       <c r="BD13">
         <v>1</v>
       </c>
-      <c r="BO13" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="CG13" s="2"/>
+      <c r="BJ13">
+        <v>1.7</v>
+      </c>
+      <c r="BK13">
+        <v>1</v>
+      </c>
+      <c r="BL13">
+        <v>1</v>
+      </c>
+      <c r="CB13" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="CG13" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="CH13" t="s">
+        <v>461</v>
+      </c>
+      <c r="CI13" t="s">
+        <v>462</v>
+      </c>
+      <c r="CJ13" s="22"/>
       <c r="CL13" s="2"/>
       <c r="CN13" s="2"/>
       <c r="CO13" s="2"/>
-      <c r="CU13" s="2" t="s">
-        <v>491</v>
+      <c r="CY13" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="14" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>489</v>
-      </c>
+      <c r="H14" s="2"/>
       <c r="K14" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="P14" s="2"/>
+        <v>446</v>
+      </c>
       <c r="AC14">
         <v>1</v>
       </c>
       <c r="AD14">
         <v>1</v>
       </c>
-      <c r="AG14" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="AJ14" s="2"/>
+      <c r="AG14" s="2"/>
+      <c r="AH14" s="2">
+        <v>1</v>
+      </c>
       <c r="AO14" s="2"/>
+      <c r="AX14" s="2"/>
       <c r="BD14">
         <v>1</v>
       </c>
-      <c r="BT14">
-        <v>9999</v>
-      </c>
-      <c r="BV14">
-        <v>0</v>
-      </c>
-      <c r="BW14" s="6">
-        <v>3</v>
-      </c>
-      <c r="BX14" s="6">
-        <v>1</v>
-      </c>
-      <c r="BY14" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="CL14" s="5"/>
-      <c r="CN14" s="2" t="s">
-        <v>482</v>
-      </c>
+      <c r="BO14" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="CG14" s="2"/>
+      <c r="CL14" s="2"/>
+      <c r="CN14" s="2"/>
       <c r="CO14" s="2"/>
-      <c r="CR14">
-        <v>9999</v>
+      <c r="CU14" s="2" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="J15" s="2" t="s">
+        <v>486</v>
+      </c>
       <c r="K15" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>480</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="P15" s="2"/>
       <c r="AC15">
         <v>1</v>
       </c>
@@ -8088,18 +8238,31 @@
         <v>1</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AJ15" s="2"/>
       <c r="AO15" s="2"/>
-      <c r="AT15" s="2"/>
       <c r="BD15">
         <v>1</v>
       </c>
-      <c r="BV15"/>
+      <c r="BT15">
+        <v>9999</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15" s="6">
+        <v>3</v>
+      </c>
+      <c r="BX15" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY15" s="6" t="s">
+        <v>476</v>
+      </c>
       <c r="CL15" s="5"/>
       <c r="CN15" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="CO15" s="2"/>
       <c r="CR15">
@@ -8108,7 +8271,7 @@
     </row>
     <row r="16" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>444</v>
@@ -8117,20 +8280,8 @@
         <v>446</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
+        <v>478</v>
+      </c>
       <c r="AC16">
         <v>1</v>
       </c>
@@ -8138,28 +8289,27 @@
         <v>1</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>495</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="AJ16" s="2"/>
+      <c r="AO16" s="2"/>
+      <c r="AT16" s="2"/>
       <c r="BD16">
         <v>1</v>
       </c>
-      <c r="BV16" s="10"/>
-      <c r="BW16" s="10"/>
-      <c r="BX16" s="10"/>
-      <c r="BY16" s="10"/>
-      <c r="BZ16" s="10"/>
-      <c r="CA16" s="10"/>
-      <c r="CL16" s="7"/>
+      <c r="BV16"/>
+      <c r="CL16" s="5"/>
       <c r="CN16" s="2" t="s">
-        <v>496</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="CO16" s="2"/>
       <c r="CR16">
         <v>9999</v>
       </c>
     </row>
-    <row r="17" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>444</v>
@@ -8168,8 +8318,20 @@
         <v>446</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>447</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
       <c r="AC17">
         <v>1</v>
       </c>
@@ -8177,285 +8339,274 @@
         <v>1</v>
       </c>
       <c r="AG17" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="AJ17" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="AO17" s="2"/>
-      <c r="AT17" s="2" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="BD17">
         <v>1</v>
       </c>
-      <c r="BV17"/>
-      <c r="CL17" s="5"/>
+      <c r="BV17" s="10"/>
+      <c r="BW17" s="10"/>
+      <c r="BX17" s="10"/>
+      <c r="BY17" s="10"/>
+      <c r="BZ17" s="10"/>
+      <c r="CA17" s="10"/>
+      <c r="CL17" s="7"/>
       <c r="CN17" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="CO17" s="2"/>
+        <v>492</v>
+      </c>
       <c r="CR17">
         <v>9999</v>
       </c>
     </row>
-    <row r="18" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="AG18" s="2"/>
-      <c r="AJ18" s="2"/>
+    <row r="18" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>495</v>
+      </c>
       <c r="AO18" s="2"/>
-      <c r="AT18" s="2"/>
+      <c r="AT18" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="BD18">
+        <v>1</v>
+      </c>
       <c r="BV18"/>
       <c r="CL18" s="5"/>
-      <c r="CN18" s="2"/>
+      <c r="CN18" s="2" t="s">
+        <v>499</v>
+      </c>
       <c r="CO18" s="2"/>
-    </row>
-    <row r="19" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="AC19">
-        <v>3</v>
-      </c>
-      <c r="AD19">
-        <v>1</v>
-      </c>
-      <c r="AT19" t="s">
-        <v>516</v>
-      </c>
-      <c r="AX19" s="2"/>
-      <c r="BD19">
-        <v>99</v>
-      </c>
-      <c r="BL19">
-        <v>1</v>
-      </c>
-      <c r="BS19">
-        <v>0.01</v>
-      </c>
-      <c r="BV19" s="10"/>
-      <c r="BW19" s="10"/>
-      <c r="BX19" s="10"/>
-      <c r="BY19" s="10"/>
-      <c r="BZ19" s="10"/>
-      <c r="CA19" s="10"/>
-      <c r="CB19" s="2"/>
-      <c r="CG19" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="CI19" s="2"/>
-      <c r="CJ19" s="22"/>
-      <c r="CL19" s="7"/>
-      <c r="CN19" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="CR19">
-        <v>0.02</v>
-      </c>
-      <c r="CU19" s="2"/>
-    </row>
-    <row r="20" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CR18">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="AG19" s="2"/>
+      <c r="AJ19" s="2"/>
+      <c r="AO19" s="2"/>
+      <c r="AT19" s="2"/>
+      <c r="BV19"/>
+      <c r="CL19" s="5"/>
+      <c r="CN19" s="2"/>
+      <c r="CO19" s="2"/>
+    </row>
+    <row r="20" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>489</v>
-      </c>
       <c r="K20" s="5" t="s">
         <v>456</v>
       </c>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
       <c r="O20" s="5" t="s">
-        <v>535</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
       <c r="AC20">
         <v>3</v>
       </c>
       <c r="AD20">
         <v>1</v>
       </c>
-      <c r="AG20" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="AJ20" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="AO20" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="AT20" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="AX20" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="AZ20">
-        <v>5</v>
-      </c>
-      <c r="BB20">
-        <v>3</v>
-      </c>
+      <c r="AT20" t="s">
+        <v>511</v>
+      </c>
+      <c r="AX20" s="2"/>
       <c r="BD20">
-        <v>3</v>
-      </c>
-      <c r="BT20">
-        <v>0.3</v>
-      </c>
-      <c r="BV20">
-        <v>4</v>
-      </c>
-      <c r="BW20" s="6">
-        <v>4</v>
-      </c>
-      <c r="BX20" s="6">
+        <v>99</v>
+      </c>
+      <c r="BL20">
         <v>1</v>
       </c>
-      <c r="BY20" s="6" t="s">
-        <v>544</v>
-      </c>
-      <c r="CB20" s="2" t="s">
-        <v>473</v>
-      </c>
+      <c r="BS20">
+        <v>0.01</v>
+      </c>
+      <c r="BV20" s="10"/>
+      <c r="BW20" s="10"/>
+      <c r="BX20" s="10"/>
+      <c r="BY20" s="10"/>
+      <c r="BZ20" s="10"/>
+      <c r="CA20" s="10"/>
+      <c r="CB20" s="2"/>
       <c r="CG20" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="CH20" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="CJ20" s="22" t="s">
-        <v>487</v>
-      </c>
-      <c r="CL20" s="5"/>
+        <v>507</v>
+      </c>
+      <c r="CI20" s="2"/>
+      <c r="CJ20" s="22"/>
+      <c r="CL20" s="7"/>
       <c r="CN20" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="CO20" s="2">
+      <c r="CR20">
+        <v>0.02</v>
+      </c>
+      <c r="CU20" s="2"/>
+    </row>
+    <row r="21" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="AC21">
+        <v>3</v>
+      </c>
+      <c r="AD21">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="AO21" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="AT21" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="AX21" s="2"/>
+      <c r="BD21">
+        <v>3</v>
+      </c>
+      <c r="BT21">
+        <v>0.3</v>
+      </c>
+      <c r="BV21">
+        <v>4</v>
+      </c>
+      <c r="BW21" s="6">
+        <v>4</v>
+      </c>
+      <c r="BX21" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY21" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="CB21" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="CG21" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="CH21" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="CJ21" s="22"/>
+      <c r="CL21" s="5"/>
+      <c r="CN21" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="CO21" s="2"/>
+      <c r="CP21">
         <v>-0.8</v>
       </c>
-      <c r="CR20">
+      <c r="CR21">
         <v>2.5</v>
       </c>
     </row>
-    <row r="21" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="BV21"/>
-      <c r="BW21" s="10"/>
-      <c r="BX21" s="10"/>
-      <c r="BY21" s="10"/>
-      <c r="BZ21" s="10"/>
-      <c r="CA21" s="10"/>
-      <c r="CL21" s="7"/>
-    </row>
-    <row r="22" spans="1:99" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>506</v>
+        <v>575</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="F22" t="s">
-        <v>510</v>
-      </c>
+      <c r="J22" s="2"/>
       <c r="K22" s="5" t="s">
         <v>446</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
+        <v>478</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>530</v>
+      </c>
       <c r="AC22">
         <v>1</v>
       </c>
       <c r="AD22">
         <v>1</v>
       </c>
-      <c r="AF22">
+      <c r="AG22" s="2"/>
+      <c r="AJ22" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="AO22" s="2"/>
+      <c r="AT22" s="2"/>
+      <c r="AV22">
+        <v>20</v>
+      </c>
+      <c r="AX22" s="2"/>
+      <c r="BD22">
         <v>1</v>
       </c>
-      <c r="AZ22">
-        <v>2.5</v>
-      </c>
-      <c r="BD22">
-        <v>99</v>
-      </c>
-      <c r="BV22" s="10"/>
-      <c r="BW22" s="10"/>
-      <c r="BX22" s="10"/>
-      <c r="BZ22" s="10"/>
-      <c r="CG22" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="CH22" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="CI22" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="CJ22" s="22" t="s">
-        <v>487</v>
-      </c>
-      <c r="CL22" s="7"/>
-      <c r="CU22" s="2"/>
-    </row>
-    <row r="23" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+      <c r="BV22"/>
+      <c r="CB22" s="2"/>
+      <c r="CG22" s="2"/>
+      <c r="CH22" s="2"/>
+      <c r="CJ22" s="22"/>
+      <c r="CL22" s="5"/>
+      <c r="CN22" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="CO22" s="2">
+        <v>10</v>
+      </c>
+      <c r="CR22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
@@ -8468,40 +8619,36 @@
       <c r="V23" s="7"/>
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
-      <c r="BV23" s="10"/>
+      <c r="BV23"/>
       <c r="BW23" s="10"/>
       <c r="BX23" s="10"/>
+      <c r="BY23" s="10"/>
       <c r="BZ23" s="10"/>
-      <c r="CG23" s="2"/>
-      <c r="CH23" s="2"/>
-      <c r="CI23" s="2"/>
-      <c r="CJ23" s="22"/>
+      <c r="CA23" s="10"/>
       <c r="CL23" s="7"/>
-      <c r="CU23" s="2"/>
-    </row>
-    <row r="24" spans="1:99" ht="14.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:103" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>444</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>489</v>
+        <v>504</v>
+      </c>
+      <c r="F24" t="s">
+        <v>505</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="L24" s="7"/>
+        <v>446</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>447</v>
+      </c>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
@@ -8517,67 +8664,57 @@
       <c r="AC24">
         <v>1</v>
       </c>
-      <c r="AG24" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="AO24" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="AT24" t="s">
-        <v>458</v>
-      </c>
-      <c r="BD24">
+      <c r="AD24">
         <v>1</v>
       </c>
+      <c r="AF24">
+        <v>1</v>
+      </c>
       <c r="BO24" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="BP24" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="BT24">
-        <v>16</v>
-      </c>
-      <c r="BV24">
-        <v>36</v>
-      </c>
-      <c r="BW24" s="10">
-        <v>49</v>
-      </c>
-      <c r="BX24" s="10">
-        <v>1</v>
-      </c>
-      <c r="BY24" s="6" t="s">
-        <v>456</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="BV24" s="10"/>
+      <c r="BW24" s="10"/>
+      <c r="BX24" s="10"/>
       <c r="BZ24" s="10"/>
-      <c r="CA24" s="10"/>
+      <c r="CG24" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="CH24" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="CI24" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="CJ24" s="22"/>
       <c r="CL24" s="7"/>
       <c r="CN24" s="2" t="s">
-        <v>523</v>
+        <v>556</v>
       </c>
       <c r="CR24">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:99" x14ac:dyDescent="0.25">
+        <v>9999</v>
+      </c>
+      <c r="CU24" s="2"/>
+    </row>
+    <row r="25" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>524</v>
+        <v>557</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
       <c r="K25" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="L25" s="7"/>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
-      <c r="O25" s="5" t="s">
-        <v>523</v>
-      </c>
+      <c r="O25" s="7"/>
       <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
+      <c r="Q25" s="5" t="s">
+        <v>556</v>
+      </c>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -8591,80 +8728,65 @@
       <c r="AD25">
         <v>1</v>
       </c>
-      <c r="AT25" t="s">
-        <v>458</v>
+      <c r="AV25">
+        <v>20</v>
       </c>
       <c r="AX25" s="2" t="s">
         <v>459</v>
       </c>
       <c r="AZ25">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="BD25">
-        <v>5</v>
-      </c>
-      <c r="BI25">
-        <v>1</v>
-      </c>
-      <c r="BJ25">
-        <v>1.7</v>
-      </c>
-      <c r="BK25">
-        <v>1</v>
-      </c>
-      <c r="BL25">
+        <v>99</v>
+      </c>
+      <c r="BS25">
         <v>1</v>
       </c>
       <c r="BV25" s="10"/>
       <c r="BW25" s="10"/>
       <c r="BX25" s="10"/>
-      <c r="BY25" s="10"/>
       <c r="BZ25" s="10"/>
-      <c r="CA25" s="10"/>
-      <c r="CB25" s="2" t="s">
-        <v>473</v>
-      </c>
       <c r="CG25" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="CH25" t="s">
-        <v>461</v>
-      </c>
-      <c r="CI25" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="CJ25" s="22" t="s">
-        <v>487</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="CH25" s="2"/>
+      <c r="CI25" s="2"/>
+      <c r="CJ25" s="22"/>
       <c r="CL25" s="7"/>
+      <c r="CM25" s="2" t="s">
+        <v>556</v>
+      </c>
       <c r="CN25" s="2" t="s">
         <v>463</v>
       </c>
       <c r="CR25">
         <v>9999</v>
       </c>
-      <c r="CU25" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="26" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CU25" s="2"/>
+      <c r="CY25" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="26" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>444</v>
       </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
       <c r="K26" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="L26" s="7"/>
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
-      <c r="O26" s="5" t="s">
-        <v>523</v>
-      </c>
+      <c r="O26" s="7"/>
       <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
+      <c r="Q26" s="5" t="s">
+        <v>556</v>
+      </c>
       <c r="R26" s="7"/>
       <c r="S26" s="7"/>
       <c r="T26" s="7"/>
@@ -8673,56 +8795,59 @@
       <c r="W26" s="7"/>
       <c r="X26" s="7"/>
       <c r="AC26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD26">
         <v>1</v>
       </c>
-      <c r="AT26" t="s">
-        <v>458</v>
+      <c r="AG26" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="AJ26" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="AV26">
+        <v>20</v>
       </c>
       <c r="AX26" s="2"/>
       <c r="BD26">
         <v>99</v>
       </c>
-      <c r="BL26">
+      <c r="BS26">
         <v>1</v>
-      </c>
-      <c r="BS26">
-        <v>0.01</v>
       </c>
       <c r="BV26" s="10"/>
       <c r="BW26" s="10"/>
       <c r="BX26" s="10"/>
-      <c r="BY26" s="10"/>
       <c r="BZ26" s="10"/>
-      <c r="CA26" s="10"/>
-      <c r="CB26" s="2"/>
       <c r="CG26" s="2" t="s">
-        <v>512</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="CH26" s="2"/>
       <c r="CI26" s="2"/>
-      <c r="CJ26" s="22"/>
+      <c r="CJ26" s="22" t="s">
+        <v>484</v>
+      </c>
       <c r="CL26" s="7"/>
+      <c r="CM26" s="2" t="s">
+        <v>556</v>
+      </c>
       <c r="CN26" s="2" t="s">
-        <v>556</v>
+        <v>463</v>
       </c>
       <c r="CR26">
-        <v>0.02</v>
+        <v>9999</v>
       </c>
       <c r="CU26" s="2"/>
-    </row>
-    <row r="27" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="L27" s="7"/>
+      <c r="CY26" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="27" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
@@ -8735,96 +8860,111 @@
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
-      <c r="AC27">
-        <v>1</v>
-      </c>
-      <c r="AG27" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="BD27">
-        <v>1</v>
-      </c>
       <c r="BV27" s="10"/>
       <c r="BW27" s="10"/>
       <c r="BX27" s="10"/>
-      <c r="BY27" s="10"/>
       <c r="BZ27" s="10"/>
-      <c r="CA27" s="10"/>
+      <c r="CG27" s="2"/>
+      <c r="CH27" s="2"/>
+      <c r="CI27" s="2"/>
+      <c r="CJ27" s="22"/>
       <c r="CL27" s="7"/>
-      <c r="CU27" s="2" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="28" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CU27" s="2"/>
+    </row>
+    <row r="28" spans="1:103" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="L28" s="8"/>
-      <c r="M28"/>
-      <c r="N28"/>
-      <c r="O28" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="P28"/>
-      <c r="Q28"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
-      <c r="V28" s="8"/>
-      <c r="W28" s="8"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="8"/>
+      <c r="D28" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7"/>
+      <c r="X28" s="7"/>
       <c r="AC28">
         <v>1</v>
       </c>
-      <c r="AD28">
+      <c r="AG28" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="AT28" t="s">
+        <v>458</v>
+      </c>
+      <c r="BD28">
         <v>1</v>
       </c>
-      <c r="AG28" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="AJ28" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="AV28">
-        <v>20</v>
-      </c>
-      <c r="BD28">
-        <v>99</v>
-      </c>
-      <c r="BS28">
-        <v>0.01</v>
-      </c>
-      <c r="BV28" s="11"/>
-      <c r="BW28" s="11"/>
-      <c r="BX28" s="11"/>
-      <c r="BY28" s="11"/>
-      <c r="BZ28" s="11"/>
-      <c r="CA28" s="11"/>
+      <c r="BO28" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="BP28" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="BT28">
+        <v>16</v>
+      </c>
+      <c r="BV28">
+        <v>36</v>
+      </c>
+      <c r="BW28" s="10">
+        <v>49</v>
+      </c>
+      <c r="BX28" s="10">
+        <v>1</v>
+      </c>
+      <c r="BY28" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="BZ28" s="10"/>
+      <c r="CA28" s="10"/>
+      <c r="CL28" s="7"/>
       <c r="CN28" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="CP28">
-        <v>2</v>
+        <v>518</v>
       </c>
       <c r="CR28">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="29" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K29" s="7"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>456</v>
+      </c>
       <c r="L29" s="7"/>
       <c r="M29" s="7"/>
       <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
+      <c r="O29" s="5" t="s">
+        <v>518</v>
+      </c>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
@@ -8834,42 +8974,88 @@
       <c r="V29" s="7"/>
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
-      <c r="BV29"/>
+      <c r="AC29">
+        <v>3</v>
+      </c>
+      <c r="AD29">
+        <v>1</v>
+      </c>
+      <c r="AO29" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="AT29" t="s">
+        <v>458</v>
+      </c>
+      <c r="AX29" s="2"/>
+      <c r="BD29">
+        <v>5</v>
+      </c>
+      <c r="BI29">
+        <v>1</v>
+      </c>
+      <c r="BJ29">
+        <v>1.7</v>
+      </c>
+      <c r="BK29">
+        <v>1</v>
+      </c>
+      <c r="BL29">
+        <v>1</v>
+      </c>
+      <c r="BV29" s="10"/>
       <c r="BW29" s="10"/>
       <c r="BX29" s="10"/>
       <c r="BY29" s="10"/>
       <c r="BZ29" s="10"/>
       <c r="CA29" s="10"/>
+      <c r="CB29" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="CG29" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="CH29" t="s">
+        <v>461</v>
+      </c>
+      <c r="CI29" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="CJ29" s="22" t="s">
+        <v>484</v>
+      </c>
       <c r="CL29" s="7"/>
-    </row>
-    <row r="30" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CM29" s="2"/>
+      <c r="CN29" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="CR29">
+        <v>9999</v>
+      </c>
+      <c r="CU29" s="2"/>
+      <c r="CY29" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="30" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>551</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>489</v>
-      </c>
       <c r="K30" s="5" t="s">
-        <v>522</v>
+        <v>456</v>
       </c>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
+      <c r="O30" s="5" t="s">
+        <v>518</v>
+      </c>
       <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
+      <c r="Q30" s="5" t="s">
+        <v>582</v>
+      </c>
       <c r="R30" s="7"/>
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
@@ -8878,108 +9064,119 @@
       <c r="W30" s="7"/>
       <c r="X30" s="7"/>
       <c r="AC30">
+        <v>2</v>
+      </c>
+      <c r="AD30">
         <v>1</v>
       </c>
-      <c r="AG30" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="AT30" t="s">
-        <v>458</v>
+      <c r="AV30">
+        <v>20</v>
+      </c>
+      <c r="AX30" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="AZ30">
+        <v>1</v>
       </c>
       <c r="BD30">
-        <v>1</v>
-      </c>
-      <c r="BO30" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="BP30" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="BT30">
-        <v>0.1</v>
-      </c>
-      <c r="BV30">
-        <v>16</v>
-      </c>
-      <c r="BW30" s="10">
-        <v>16</v>
-      </c>
-      <c r="BX30" s="10">
-        <v>1</v>
-      </c>
-      <c r="BY30" s="6" t="s">
-        <v>456</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="BV30" s="10"/>
+      <c r="BW30" s="10"/>
+      <c r="BX30" s="10"/>
+      <c r="BY30" s="10"/>
       <c r="BZ30" s="10"/>
       <c r="CA30" s="10"/>
+      <c r="CB30" s="2"/>
+      <c r="CG30" s="2"/>
+      <c r="CI30" s="2"/>
+      <c r="CJ30" s="22"/>
       <c r="CL30" s="7"/>
-      <c r="CN30" s="2"/>
-    </row>
-    <row r="31" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CM30" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="CN30" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="CR30">
+        <v>9999</v>
+      </c>
+      <c r="CU30" s="2"/>
+      <c r="CY30" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="31" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8" t="s">
+      <c r="K31" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="L31" s="8"/>
-      <c r="M31"/>
-      <c r="N31"/>
-      <c r="O31" s="8"/>
-      <c r="P31"/>
-      <c r="Q31"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="8"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="8"/>
-      <c r="V31" s="8"/>
-      <c r="W31" s="8"/>
-      <c r="X31" s="8"/>
-      <c r="Y31" s="8"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
       <c r="AC31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD31">
         <v>1</v>
       </c>
-      <c r="AG31" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="AJ31" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="AV31">
-        <v>20</v>
-      </c>
+      <c r="AT31" t="s">
+        <v>458</v>
+      </c>
+      <c r="AX31" s="2"/>
       <c r="BD31">
         <v>99</v>
       </c>
+      <c r="BL31">
+        <v>1</v>
+      </c>
       <c r="BS31">
-        <v>0.1</v>
-      </c>
-      <c r="BV31" s="11"/>
-      <c r="BW31" s="11"/>
-      <c r="BX31" s="11"/>
-      <c r="BY31" s="11"/>
-      <c r="BZ31" s="11"/>
-      <c r="CA31" s="11"/>
+        <v>0.01</v>
+      </c>
+      <c r="BV31" s="10"/>
+      <c r="BW31" s="10"/>
+      <c r="BX31" s="10"/>
+      <c r="BY31" s="10"/>
+      <c r="BZ31" s="10"/>
+      <c r="CA31" s="10"/>
+      <c r="CB31" s="2"/>
+      <c r="CG31" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="CI31" s="2"/>
+      <c r="CJ31" s="22"/>
+      <c r="CL31" s="7"/>
       <c r="CN31" s="2" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="CR31">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:99" x14ac:dyDescent="0.25">
+        <v>0.02</v>
+      </c>
+      <c r="CU31" s="2"/>
+    </row>
+    <row r="32" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>547</v>
+        <v>520</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>446</v>
@@ -9001,7 +9198,7 @@
         <v>1</v>
       </c>
       <c r="AG32" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="BD32">
         <v>1</v>
@@ -9014,33 +9211,74 @@
       <c r="CA32" s="10"/>
       <c r="CL32" s="7"/>
       <c r="CU32" s="2" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="33" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="7"/>
-      <c r="V33" s="7"/>
-      <c r="W33" s="7"/>
-      <c r="X33" s="7"/>
-      <c r="BV33"/>
-      <c r="BW33" s="10"/>
-      <c r="BX33" s="10"/>
-      <c r="BY33" s="10"/>
-      <c r="BZ33" s="10"/>
-      <c r="CA33" s="10"/>
-      <c r="CL33" s="7"/>
-    </row>
-    <row r="34" spans="1:99" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="33" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="L33" s="8"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="P33"/>
+      <c r="Q33"/>
+      <c r="R33" s="8"/>
+      <c r="S33" s="8"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="8"/>
+      <c r="V33" s="8"/>
+      <c r="W33" s="8"/>
+      <c r="X33" s="8"/>
+      <c r="Y33" s="8"/>
+      <c r="AC33">
+        <v>1</v>
+      </c>
+      <c r="AD33">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="AJ33" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="AV33">
+        <v>20</v>
+      </c>
+      <c r="BD33">
+        <v>99</v>
+      </c>
+      <c r="BS33">
+        <v>0.01</v>
+      </c>
+      <c r="BV33" s="11"/>
+      <c r="BW33" s="11"/>
+      <c r="BX33" s="11"/>
+      <c r="BY33" s="11"/>
+      <c r="BZ33" s="11"/>
+      <c r="CA33" s="11"/>
+      <c r="CN33" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="CP33">
+        <v>2</v>
+      </c>
+      <c r="CR33">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="34" spans="1:103" x14ac:dyDescent="0.25">
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
@@ -9063,334 +9301,626 @@
       <c r="CA34" s="10"/>
       <c r="CL34" s="7"/>
     </row>
-    <row r="36" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="AT36" s="2"/>
-      <c r="BV36"/>
-      <c r="CL36" s="5"/>
-      <c r="CU36" s="2"/>
-    </row>
-    <row r="37" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="J37" s="2"/>
-      <c r="O37"/>
-      <c r="AO37" s="2"/>
-      <c r="CU37" s="2"/>
-    </row>
-    <row r="38" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="P38"/>
-    </row>
-    <row r="39" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="CL39" s="5"/>
-    </row>
-    <row r="40" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40"/>
-      <c r="N40"/>
-      <c r="O40" s="9"/>
-      <c r="P40"/>
-      <c r="Q40"/>
-      <c r="R40" s="9"/>
-      <c r="S40" s="9"/>
-      <c r="T40" s="9"/>
-      <c r="U40" s="9"/>
-      <c r="V40" s="9"/>
-      <c r="W40" s="9"/>
-      <c r="X40"/>
-      <c r="BU40" s="12"/>
-      <c r="BV40" s="12"/>
-      <c r="BW40" s="12"/>
-      <c r="BX40" s="12"/>
-      <c r="BY40" s="12"/>
-      <c r="BZ40" s="12"/>
-      <c r="CA40"/>
-    </row>
-    <row r="41" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41"/>
-      <c r="N41"/>
-      <c r="O41" s="9"/>
-      <c r="P41"/>
-      <c r="Q41"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
-      <c r="X41"/>
-      <c r="BU41" s="12"/>
-      <c r="BV41" s="12"/>
-      <c r="BW41" s="12"/>
-      <c r="BX41" s="12"/>
-      <c r="BY41" s="12"/>
-      <c r="BZ41" s="12"/>
-      <c r="CA41"/>
-      <c r="CN41" s="3"/>
-    </row>
-    <row r="42" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="AY42" s="5"/>
-      <c r="BV42"/>
-      <c r="BW42"/>
-      <c r="BX42"/>
-      <c r="BY42"/>
-      <c r="BZ42"/>
-      <c r="CA42"/>
-      <c r="CB42" s="5"/>
-      <c r="CC42" s="5"/>
-      <c r="CD42" s="5"/>
-      <c r="CE42" s="5"/>
-      <c r="CF42" s="5"/>
-      <c r="CH42" s="5"/>
-      <c r="CI42" s="5"/>
-      <c r="CJ42" s="5"/>
-      <c r="CK42" s="5"/>
-      <c r="CL42" s="5"/>
-      <c r="CM42" s="5"/>
-    </row>
-    <row r="43" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="M43"/>
-      <c r="N43"/>
-      <c r="P43" s="3"/>
-      <c r="R43" s="3"/>
-      <c r="S43"/>
-      <c r="X43"/>
-      <c r="BV43"/>
-      <c r="CB43" s="6"/>
-    </row>
-    <row r="44" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="BV44"/>
-    </row>
-    <row r="45" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="AC35">
+        <v>1</v>
+      </c>
+      <c r="AG35" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="AT35" t="s">
+        <v>458</v>
+      </c>
+      <c r="BD35">
+        <v>1</v>
+      </c>
+      <c r="BO35" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="BP35" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="BT35">
+        <v>0.1</v>
+      </c>
+      <c r="BV35">
+        <v>16</v>
+      </c>
+      <c r="BW35" s="10">
+        <v>16</v>
+      </c>
+      <c r="BX35" s="10">
+        <v>1</v>
+      </c>
+      <c r="BY35" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="BZ35" s="10"/>
+      <c r="CA35" s="10"/>
+      <c r="CL35" s="7"/>
+      <c r="CN35" s="2"/>
+    </row>
+    <row r="36" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="L36" s="8"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36" s="8"/>
+      <c r="P36"/>
+      <c r="Q36"/>
+      <c r="R36" s="8"/>
+      <c r="S36" s="8"/>
+      <c r="T36" s="8"/>
+      <c r="U36" s="8"/>
+      <c r="V36" s="8"/>
+      <c r="W36" s="8"/>
+      <c r="X36" s="8"/>
+      <c r="Y36" s="8"/>
+      <c r="AC36">
+        <v>1</v>
+      </c>
+      <c r="AD36">
+        <v>1</v>
+      </c>
+      <c r="AG36" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="AJ36" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="AV36">
+        <v>20</v>
+      </c>
+      <c r="BD36">
+        <v>99</v>
+      </c>
+      <c r="BS36">
+        <v>0.1</v>
+      </c>
+      <c r="BV36" s="11"/>
+      <c r="BW36" s="11"/>
+      <c r="BX36" s="11"/>
+      <c r="BY36" s="11"/>
+      <c r="BZ36" s="11"/>
+      <c r="CA36" s="11"/>
+      <c r="CN36" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="CR36">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
+      <c r="AC37">
+        <v>1</v>
+      </c>
+      <c r="AG37" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="BD37">
+        <v>1</v>
+      </c>
+      <c r="BV37" s="10"/>
+      <c r="BW37" s="10"/>
+      <c r="BX37" s="10"/>
+      <c r="BY37" s="10"/>
+      <c r="BZ37" s="10"/>
+      <c r="CA37" s="10"/>
+      <c r="CL37" s="7"/>
+      <c r="CU37" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="38" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="7"/>
+      <c r="W38" s="7"/>
+      <c r="X38" s="7"/>
+      <c r="AC38">
+        <v>2</v>
+      </c>
+      <c r="AD38">
+        <v>1</v>
+      </c>
+      <c r="AV38">
+        <v>20</v>
+      </c>
+      <c r="AX38" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="AZ38">
+        <v>5</v>
+      </c>
+      <c r="BD38">
+        <v>99</v>
+      </c>
+      <c r="BV38"/>
+      <c r="BW38" s="10"/>
+      <c r="BX38" s="10"/>
+      <c r="BY38" s="10"/>
+      <c r="BZ38" s="10"/>
+      <c r="CA38" s="10"/>
+      <c r="CL38" s="7"/>
+      <c r="CM38" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="CN38" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="CR38">
+        <v>9999</v>
+      </c>
+      <c r="CY38" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="39" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
+      <c r="AC39">
+        <v>1</v>
+      </c>
+      <c r="AD39">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="AJ39" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="AV39">
+        <v>20</v>
+      </c>
+      <c r="BD39">
+        <v>99</v>
+      </c>
+      <c r="BV39"/>
+      <c r="BW39" s="10"/>
+      <c r="BX39" s="10"/>
+      <c r="BY39" s="10"/>
+      <c r="BZ39" s="10"/>
+      <c r="CA39" s="10"/>
+      <c r="CJ39" s="22" t="s">
+        <v>580</v>
+      </c>
+      <c r="CL39" s="7"/>
+      <c r="CM39" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="CY39" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="41" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="AT41" s="2"/>
+      <c r="BV41"/>
+      <c r="CL41" s="5"/>
+      <c r="CU41" s="2"/>
+    </row>
+    <row r="42" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="J42" s="2"/>
+      <c r="O42"/>
+      <c r="AO42" s="2"/>
+      <c r="CU42" s="2"/>
+    </row>
+    <row r="43" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="P43"/>
+    </row>
+    <row r="44" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="CL44" s="5"/>
+    </row>
+    <row r="45" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
       <c r="M45"/>
-      <c r="O45"/>
-      <c r="BO45" s="2"/>
-      <c r="BP45" s="2"/>
-      <c r="CN45" s="3"/>
-    </row>
-    <row r="46" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="J46" s="5"/>
+      <c r="N45"/>
+      <c r="O45" s="9"/>
+      <c r="P45"/>
+      <c r="Q45"/>
+      <c r="R45" s="9"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="W45" s="9"/>
+      <c r="X45"/>
+      <c r="BU45" s="12"/>
+      <c r="BV45" s="12"/>
+      <c r="BW45" s="12"/>
+      <c r="BX45" s="12"/>
+      <c r="BY45" s="12"/>
+      <c r="BZ45" s="12"/>
+      <c r="CA45"/>
+    </row>
+    <row r="46" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
       <c r="M46"/>
-      <c r="O46" s="3"/>
+      <c r="N46"/>
+      <c r="O46" s="9"/>
       <c r="P46"/>
       <c r="Q46"/>
-      <c r="CN46" s="2"/>
-    </row>
-    <row r="47" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="M47"/>
-      <c r="CB47" s="13"/>
-    </row>
-    <row r="48" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="R46" s="9"/>
+      <c r="S46" s="9"/>
+      <c r="T46" s="9"/>
+      <c r="U46" s="9"/>
+      <c r="V46" s="9"/>
+      <c r="W46" s="9"/>
+      <c r="X46"/>
+      <c r="BU46" s="12"/>
+      <c r="BV46" s="12"/>
+      <c r="BW46" s="12"/>
+      <c r="BX46" s="12"/>
+      <c r="BY46" s="12"/>
+      <c r="BZ46" s="12"/>
+      <c r="CA46"/>
+      <c r="CN46" s="3"/>
+    </row>
+    <row r="47" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="AY47" s="5"/>
+      <c r="BV47"/>
+      <c r="BW47"/>
+      <c r="BX47"/>
+      <c r="BY47"/>
+      <c r="BZ47"/>
+      <c r="CA47"/>
+      <c r="CB47" s="5"/>
+      <c r="CC47" s="5"/>
+      <c r="CD47" s="5"/>
+      <c r="CE47" s="5"/>
+      <c r="CF47" s="5"/>
+      <c r="CH47" s="5"/>
+      <c r="CI47" s="5"/>
+      <c r="CJ47" s="5"/>
+      <c r="CK47" s="5"/>
+      <c r="CL47" s="5"/>
+      <c r="CM47" s="5"/>
+    </row>
+    <row r="48" spans="1:103" x14ac:dyDescent="0.25">
       <c r="M48"/>
-      <c r="O48" s="3"/>
-      <c r="P48"/>
-      <c r="Q48"/>
-    </row>
-    <row r="49" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="M49"/>
-      <c r="O49" s="3"/>
-      <c r="P49"/>
-      <c r="Q49"/>
-      <c r="CN49" s="3"/>
-    </row>
-    <row r="50" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="N48"/>
+      <c r="P48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48"/>
+      <c r="X48"/>
+      <c r="BV48"/>
+      <c r="CB48" s="6"/>
+    </row>
+    <row r="49" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="BV49"/>
+    </row>
+    <row r="50" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M50"/>
-      <c r="AY50" s="5"/>
-      <c r="BV50"/>
-      <c r="BW50"/>
-      <c r="BX50"/>
-      <c r="BY50"/>
-      <c r="BZ50"/>
-      <c r="CA50"/>
-      <c r="CB50" s="5"/>
-      <c r="CC50" s="5"/>
-      <c r="CD50" s="5"/>
-      <c r="CE50" s="5"/>
-      <c r="CF50" s="5"/>
-      <c r="CH50" s="5"/>
-      <c r="CI50" s="5"/>
-      <c r="CJ50" s="5"/>
-      <c r="CK50" s="5"/>
+      <c r="O50"/>
+      <c r="BO50" s="2"/>
+      <c r="BP50" s="2"/>
       <c r="CN50" s="3"/>
     </row>
-    <row r="51" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="J51" s="5"/>
       <c r="M51"/>
       <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="P51"/>
+      <c r="Q51"/>
+      <c r="CN51" s="2"/>
+    </row>
+    <row r="52" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M52"/>
-      <c r="N52"/>
-      <c r="BV52"/>
-      <c r="CI52" s="5"/>
-      <c r="CJ52" s="5"/>
-    </row>
-    <row r="53" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CB52" s="13"/>
+    </row>
+    <row r="53" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M53"/>
-      <c r="N53"/>
-      <c r="BV53"/>
-      <c r="CJ53" s="5"/>
-    </row>
-    <row r="54" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="O53" s="3"/>
+      <c r="P53"/>
+      <c r="Q53"/>
+    </row>
+    <row r="54" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="A54" s="2"/>
       <c r="M54"/>
       <c r="O54" s="3"/>
-      <c r="AG54" s="2"/>
-      <c r="AO54" s="2"/>
-      <c r="BO54" s="2"/>
-      <c r="BP54" s="2"/>
-      <c r="CG54" s="2"/>
-      <c r="CM54" s="2"/>
-    </row>
-    <row r="55" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
+      <c r="P54"/>
+      <c r="Q54"/>
+      <c r="CN54" s="3"/>
+    </row>
+    <row r="55" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M55"/>
-      <c r="O55" s="3"/>
-      <c r="AG55" s="2"/>
-      <c r="AO55" s="2"/>
-      <c r="CG55" s="2"/>
-    </row>
-    <row r="56" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="BU56" s="6"/>
-      <c r="CA56"/>
-    </row>
-    <row r="57" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="E57" s="2"/>
-      <c r="O57"/>
-      <c r="W57"/>
-      <c r="X57"/>
-      <c r="BO57" s="2"/>
-      <c r="BP57" s="2"/>
-      <c r="CN57" s="3"/>
-    </row>
-    <row r="58" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="AY55" s="5"/>
+      <c r="BV55"/>
+      <c r="BW55"/>
+      <c r="BX55"/>
+      <c r="BY55"/>
+      <c r="BZ55"/>
+      <c r="CA55"/>
+      <c r="CB55" s="5"/>
+      <c r="CC55" s="5"/>
+      <c r="CD55" s="5"/>
+      <c r="CE55" s="5"/>
+      <c r="CF55" s="5"/>
+      <c r="CH55" s="5"/>
+      <c r="CI55" s="5"/>
+      <c r="CJ55" s="5"/>
+      <c r="CK55" s="5"/>
+      <c r="CN55" s="3"/>
+    </row>
+    <row r="56" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="M56"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="M57"/>
+      <c r="N57"/>
+      <c r="BV57"/>
+      <c r="CI57" s="5"/>
+      <c r="CJ57" s="5"/>
+    </row>
+    <row r="58" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M58"/>
-      <c r="O58" s="3"/>
-      <c r="P58"/>
-      <c r="Q58"/>
-      <c r="CN58" s="3"/>
-    </row>
-    <row r="59" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
+      <c r="N58"/>
+      <c r="BV58"/>
+      <c r="CJ58" s="5"/>
+    </row>
+    <row r="59" spans="1:92" x14ac:dyDescent="0.25">
       <c r="M59"/>
       <c r="O59" s="3"/>
-      <c r="P59"/>
-      <c r="Q59"/>
-      <c r="CN59" s="3"/>
-    </row>
-    <row r="60" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="AG59" s="2"/>
+      <c r="AO59" s="2"/>
+      <c r="BO59" s="2"/>
+      <c r="BP59" s="2"/>
+      <c r="CG59" s="2"/>
+      <c r="CM59" s="2"/>
+    </row>
+    <row r="60" spans="1:92" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
+      <c r="M60"/>
       <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
-      <c r="CL61" s="5"/>
-    </row>
-    <row r="62" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="CL62" s="5"/>
-    </row>
-    <row r="63" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="AJ63" s="2"/>
-      <c r="CL63" s="5"/>
-      <c r="CU63" s="2"/>
-    </row>
-    <row r="64" spans="1:99" x14ac:dyDescent="0.25">
-      <c r="CL64" s="5"/>
-    </row>
-    <row r="65" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="O65"/>
-      <c r="W65"/>
-      <c r="X65"/>
-      <c r="CN65" s="3"/>
-    </row>
-    <row r="66" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="O66" s="3"/>
-      <c r="X66"/>
-    </row>
-    <row r="67" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="O67" s="3"/>
-      <c r="P67"/>
-      <c r="Q67"/>
-      <c r="X67"/>
-    </row>
-    <row r="68" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="O68" s="3"/>
-      <c r="X68"/>
-    </row>
-    <row r="71" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="CM71" s="3"/>
-      <c r="CN71" s="3"/>
-    </row>
-    <row r="73" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="M73"/>
-      <c r="N73"/>
-      <c r="BV73"/>
-      <c r="CB73" s="14"/>
-      <c r="CI73" s="5"/>
-      <c r="CJ73" s="5"/>
-    </row>
-    <row r="74" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="M74"/>
-      <c r="N74"/>
-      <c r="BV74"/>
-      <c r="CB74" s="14"/>
-      <c r="CJ74" s="5"/>
-    </row>
-    <row r="75" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="O75"/>
-      <c r="X75"/>
-      <c r="CM75" s="3"/>
-    </row>
-    <row r="78" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="CL78" s="5"/>
-    </row>
-    <row r="79" spans="13:92" x14ac:dyDescent="0.25">
-      <c r="CL79" s="5"/>
-    </row>
-    <row r="85" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL85" s="5"/>
-    </row>
-    <row r="86" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL86" s="5"/>
-    </row>
-    <row r="88" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL88" s="5"/>
-    </row>
-    <row r="89" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL89" s="5"/>
-    </row>
-    <row r="90" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="AG60" s="2"/>
+      <c r="AO60" s="2"/>
+      <c r="CG60" s="2"/>
+    </row>
+    <row r="61" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="BU61" s="6"/>
+      <c r="CA61"/>
+    </row>
+    <row r="62" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="E62" s="2"/>
+      <c r="O62"/>
+      <c r="W62"/>
+      <c r="X62"/>
+      <c r="BO62" s="2"/>
+      <c r="BP62" s="2"/>
+      <c r="CN62" s="3"/>
+    </row>
+    <row r="63" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="M63"/>
+      <c r="O63" s="3"/>
+      <c r="P63"/>
+      <c r="Q63"/>
+      <c r="CN63" s="3"/>
+    </row>
+    <row r="64" spans="1:92" x14ac:dyDescent="0.25">
+      <c r="A64" s="2"/>
+      <c r="M64"/>
+      <c r="O64" s="3"/>
+      <c r="P64"/>
+      <c r="Q64"/>
+      <c r="CN64" s="3"/>
+    </row>
+    <row r="65" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A65" s="2"/>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A66" s="2"/>
+      <c r="CL66" s="5"/>
+    </row>
+    <row r="67" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CL67" s="5"/>
+    </row>
+    <row r="68" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="A68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="AJ68" s="2"/>
+      <c r="CL68" s="5"/>
+      <c r="CU68" s="2"/>
+    </row>
+    <row r="69" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CL69" s="5"/>
+    </row>
+    <row r="70" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="O70"/>
+      <c r="W70"/>
+      <c r="X70"/>
+      <c r="CN70" s="3"/>
+    </row>
+    <row r="71" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="O71" s="3"/>
+      <c r="X71"/>
+    </row>
+    <row r="72" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="O72" s="3"/>
+      <c r="P72"/>
+      <c r="Q72"/>
+      <c r="X72"/>
+    </row>
+    <row r="73" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="O73" s="3"/>
+      <c r="X73"/>
+    </row>
+    <row r="76" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="CM76" s="3"/>
+      <c r="CN76" s="3"/>
+    </row>
+    <row r="78" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="M78"/>
+      <c r="N78"/>
+      <c r="BV78"/>
+      <c r="CB78" s="14"/>
+      <c r="CI78" s="5"/>
+      <c r="CJ78" s="5"/>
+    </row>
+    <row r="79" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="M79"/>
+      <c r="N79"/>
+      <c r="BV79"/>
+      <c r="CB79" s="14"/>
+      <c r="CJ79" s="5"/>
+    </row>
+    <row r="80" spans="1:99" x14ac:dyDescent="0.25">
+      <c r="O80"/>
+      <c r="X80"/>
+      <c r="CM80" s="3"/>
+    </row>
+    <row r="83" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL83" s="5"/>
+    </row>
+    <row r="84" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL84" s="5"/>
+    </row>
+    <row r="90" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL90" s="5"/>
     </row>
-    <row r="91" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="91" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL91" s="5"/>
     </row>
-    <row r="92" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV92"/>
-    </row>
-    <row r="93" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV93"/>
-    </row>
-    <row r="94" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV94"/>
+    <row r="93" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL93" s="5"/>
+    </row>
+    <row r="94" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL94" s="5"/>
     </row>
-    <row r="95" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="95" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL95" s="5"/>
     </row>
-    <row r="96" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="96" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL96" s="5"/>
     </row>
     <row r="97" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV97"/>
     </row>
     <row r="98" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL98" s="5"/>
+      <c r="BV98"/>
+    </row>
+    <row r="99" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV99"/>
+      <c r="CL99" s="5"/>
+    </row>
+    <row r="100" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL100" s="5"/>
+    </row>
+    <row r="101" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL101" s="5"/>
     </row>
     <row r="102" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV102"/>
@@ -9398,36 +9928,27 @@
     <row r="103" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL103" s="5"/>
     </row>
-    <row r="111" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL111" s="5"/>
-    </row>
-    <row r="112" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL112" s="5"/>
-    </row>
-    <row r="113" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV113"/>
+    <row r="107" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV107"/>
+    </row>
+    <row r="108" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL108" s="5"/>
+    </row>
+    <row r="116" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL116" s="5"/>
+    </row>
+    <row r="117" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL117" s="5"/>
     </row>
     <row r="118" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV118"/>
     </row>
-    <row r="119" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV119"/>
-      <c r="CL119" s="5"/>
-    </row>
-    <row r="120" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL120" s="5"/>
-    </row>
-    <row r="121" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL121" s="5"/>
-    </row>
-    <row r="122" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL122" s="5"/>
-    </row>
     <row r="123" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL123" s="5"/>
+      <c r="BV123"/>
     </row>
     <row r="124" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV124"/>
+      <c r="CL124" s="5"/>
     </row>
     <row r="125" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL125" s="5"/>
@@ -9456,6 +9977,12 @@
     <row r="133" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL133" s="5"/>
     </row>
+    <row r="134" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV134"/>
+    </row>
+    <row r="135" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL135" s="5"/>
+    </row>
     <row r="136" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL136" s="5"/>
     </row>
@@ -9465,14 +9992,11 @@
     <row r="138" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL138" s="5"/>
     </row>
-    <row r="139" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL139" s="5"/>
-    </row>
-    <row r="140" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL140" s="5"/>
+    <row r="141" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL141" s="5"/>
     </row>
     <row r="142" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV142"/>
+      <c r="CL142" s="5"/>
     </row>
     <row r="143" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL143" s="5"/>
@@ -9483,33 +10007,33 @@
     <row r="145" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL145" s="5"/>
     </row>
-    <row r="146" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL146" s="5"/>
+    <row r="147" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV147"/>
+    </row>
+    <row r="148" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL148" s="5"/>
+    </row>
+    <row r="149" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL149" s="5"/>
     </row>
     <row r="150" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL150" s="5"/>
     </row>
-    <row r="152" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV152"/>
-    </row>
-    <row r="153" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV153"/>
-      <c r="CL153" s="5"/>
-    </row>
-    <row r="154" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL154" s="5"/>
+    <row r="151" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL151" s="5"/>
     </row>
     <row r="155" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL155" s="5"/>
     </row>
-    <row r="156" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL156" s="5"/>
-    </row>
     <row r="157" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL157" s="5"/>
+      <c r="BV157"/>
+    </row>
+    <row r="158" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV158"/>
+      <c r="CL158" s="5"/>
     </row>
     <row r="159" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV159"/>
+      <c r="CL159" s="5"/>
     </row>
     <row r="160" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL160" s="5"/>
@@ -9517,210 +10041,216 @@
     <row r="161" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL161" s="5"/>
     </row>
-    <row r="163" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL163" s="5"/>
+    <row r="162" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL162" s="5"/>
     </row>
     <row r="164" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL164" s="5"/>
+      <c r="BV164"/>
+    </row>
+    <row r="165" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL165" s="5"/>
     </row>
     <row r="166" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV166"/>
-    </row>
-    <row r="167" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL167" s="5"/>
-    </row>
-    <row r="170" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL170" s="5"/>
+      <c r="CL166" s="5"/>
+    </row>
+    <row r="168" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL168" s="5"/>
+    </row>
+    <row r="169" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL169" s="5"/>
     </row>
     <row r="171" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL171" s="5"/>
-    </row>
-    <row r="174" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL174" s="5"/>
+      <c r="BV171"/>
+    </row>
+    <row r="172" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL172" s="5"/>
+    </row>
+    <row r="175" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL175" s="5"/>
     </row>
     <row r="176" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL176" s="5"/>
     </row>
-    <row r="178" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV178"/>
-    </row>
     <row r="179" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL179" s="5"/>
     </row>
-    <row r="180" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL180" s="5"/>
-    </row>
-    <row r="182" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL182" s="5"/>
+    <row r="181" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL181" s="5"/>
     </row>
     <row r="183" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL183" s="5"/>
+      <c r="BV183"/>
     </row>
     <row r="184" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL184" s="5"/>
     </row>
+    <row r="185" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL185" s="5"/>
+    </row>
+    <row r="187" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL187" s="5"/>
+    </row>
+    <row r="188" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL188" s="5"/>
+    </row>
     <row r="189" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL189" s="5"/>
     </row>
-    <row r="190" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL190" s="5"/>
-    </row>
-    <row r="193" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL193" s="5"/>
-    </row>
     <row r="194" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL194" s="5"/>
     </row>
+    <row r="195" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL195" s="5"/>
+    </row>
     <row r="198" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL198" s="5"/>
     </row>
-    <row r="202" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL202" s="5"/>
-    </row>
-    <row r="204" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL204" s="5"/>
-    </row>
-    <row r="205" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL205" s="5"/>
+    <row r="199" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL199" s="5"/>
+    </row>
+    <row r="203" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL203" s="5"/>
     </row>
     <row r="207" spans="90:90" x14ac:dyDescent="0.25">
       <c r="CL207" s="5"/>
     </row>
-    <row r="208" spans="90:90" x14ac:dyDescent="0.25">
-      <c r="CL208" s="5"/>
+    <row r="209" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL209" s="5"/>
     </row>
     <row r="210" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV210"/>
-    </row>
-    <row r="211" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV211"/>
-      <c r="CL211" s="5"/>
+      <c r="CL210" s="5"/>
     </row>
     <row r="212" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL212" s="5"/>
     </row>
-    <row r="214" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL214" s="5"/>
-    </row>
-    <row r="223" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV223"/>
-    </row>
-    <row r="224" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV224"/>
-      <c r="CL224" s="5"/>
-    </row>
-    <row r="225" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL225" s="5"/>
-    </row>
-    <row r="226" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL226" s="5"/>
-    </row>
-    <row r="227" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV227"/>
+    <row r="213" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL213" s="5"/>
+    </row>
+    <row r="215" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV215"/>
+    </row>
+    <row r="216" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV216"/>
+      <c r="CL216" s="5"/>
+    </row>
+    <row r="217" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL217" s="5"/>
+    </row>
+    <row r="219" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL219" s="5"/>
     </row>
     <row r="228" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV228"/>
-      <c r="CL228" s="5"/>
     </row>
     <row r="229" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV229"/>
       <c r="CL229" s="5"/>
     </row>
+    <row r="230" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL230" s="5"/>
+    </row>
     <row r="231" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV231"/>
+      <c r="CL231" s="5"/>
     </row>
     <row r="232" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV232"/>
-      <c r="CL232" s="5"/>
     </row>
     <row r="233" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV233"/>
       <c r="CL233" s="5"/>
     </row>
-    <row r="235" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV235"/>
+    <row r="234" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL234" s="5"/>
     </row>
     <row r="236" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL236" s="5"/>
-    </row>
-    <row r="239" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL239" s="5"/>
-    </row>
-    <row r="243" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL243" s="5"/>
-    </row>
-    <row r="245" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV245"/>
-    </row>
-    <row r="246" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL246" s="5"/>
-    </row>
-    <row r="253" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV253"/>
-    </row>
-    <row r="254" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL254" s="5"/>
-    </row>
-    <row r="255" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL255" s="5"/>
-    </row>
-    <row r="257" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV257"/>
+      <c r="BV236"/>
+    </row>
+    <row r="237" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV237"/>
+      <c r="CL237" s="5"/>
+    </row>
+    <row r="238" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL238" s="5"/>
+    </row>
+    <row r="240" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV240"/>
+    </row>
+    <row r="241" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL241" s="5"/>
+    </row>
+    <row r="244" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL244" s="5"/>
+    </row>
+    <row r="248" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL248" s="5"/>
+    </row>
+    <row r="250" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV250"/>
+    </row>
+    <row r="251" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL251" s="5"/>
     </row>
     <row r="258" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV258"/>
-      <c r="CL258" s="5"/>
     </row>
     <row r="259" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL259" s="5"/>
     </row>
-    <row r="265" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV265"/>
-    </row>
-    <row r="266" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV266"/>
-      <c r="CL266" s="5"/>
-    </row>
-    <row r="267" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV267"/>
-      <c r="CL267" s="5"/>
-    </row>
-    <row r="268" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL268" s="5"/>
+    <row r="260" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL260" s="5"/>
+    </row>
+    <row r="262" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV262"/>
+    </row>
+    <row r="263" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV263"/>
+      <c r="CL263" s="5"/>
+    </row>
+    <row r="264" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL264" s="5"/>
+    </row>
+    <row r="270" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV270"/>
+    </row>
+    <row r="271" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV271"/>
+      <c r="CL271" s="5"/>
+    </row>
+    <row r="272" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV272"/>
+      <c r="CL272" s="5"/>
     </row>
     <row r="273" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV273"/>
-    </row>
-    <row r="274" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV274"/>
+      <c r="CL273" s="5"/>
     </row>
     <row r="278" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV278"/>
     </row>
     <row r="279" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL279" s="5"/>
-    </row>
-    <row r="280" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV280"/>
-    </row>
-    <row r="281" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL281" s="5"/>
-    </row>
-    <row r="291" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV291"/>
-    </row>
-    <row r="292" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL292" s="5"/>
-    </row>
-    <row r="294" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV294"/>
-    </row>
-    <row r="295" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL295" s="5"/>
-    </row>
-    <row r="303" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV303"/>
-    </row>
-    <row r="304" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL304" s="5"/>
+      <c r="BV279"/>
+    </row>
+    <row r="283" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV283"/>
+    </row>
+    <row r="284" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL284" s="5"/>
+    </row>
+    <row r="285" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV285"/>
+    </row>
+    <row r="286" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL286" s="5"/>
+    </row>
+    <row r="296" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV296"/>
+    </row>
+    <row r="297" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL297" s="5"/>
+    </row>
+    <row r="299" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV299"/>
+    </row>
+    <row r="300" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL300" s="5"/>
     </row>
     <row r="308" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV308"/>
@@ -9728,32 +10258,24 @@
     <row r="309" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL309" s="5"/>
     </row>
-    <row r="311" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV311"/>
-    </row>
-    <row r="312" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL312" s="5"/>
-    </row>
-    <row r="328" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV328"/>
-    </row>
-    <row r="329" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV329"/>
-      <c r="CL329" s="5"/>
-    </row>
-    <row r="330" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV330"/>
-      <c r="CL330" s="5"/>
-    </row>
-    <row r="331" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV331"/>
-      <c r="CL331" s="5"/>
-    </row>
-    <row r="332" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV332"/>
+    <row r="313" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV313"/>
+    </row>
+    <row r="314" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL314" s="5"/>
+    </row>
+    <row r="316" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV316"/>
+    </row>
+    <row r="317" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL317" s="5"/>
+    </row>
+    <row r="333" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV333"/>
     </row>
     <row r="334" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV334"/>
+      <c r="CL334" s="5"/>
     </row>
     <row r="335" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV335"/>
@@ -9764,71 +10286,71 @@
       <c r="CL336" s="5"/>
     </row>
     <row r="337" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL337" s="5"/>
+      <c r="BV337"/>
+    </row>
+    <row r="339" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV339"/>
+    </row>
+    <row r="340" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV340"/>
+      <c r="CL340" s="5"/>
     </row>
     <row r="341" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV341"/>
+      <c r="CL341" s="5"/>
     </row>
     <row r="342" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL342" s="5"/>
     </row>
-    <row r="344" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV344"/>
-    </row>
-    <row r="345" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV345"/>
-      <c r="CL345" s="5"/>
-    </row>
     <row r="346" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV346"/>
-      <c r="CL346" s="5"/>
     </row>
     <row r="347" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL347" s="5"/>
     </row>
-    <row r="363" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV363"/>
-    </row>
-    <row r="364" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL364" s="5"/>
-    </row>
-    <row r="372" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL372" s="5"/>
-    </row>
-    <row r="373" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL373" s="5"/>
-    </row>
-    <row r="374" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL374" s="5"/>
-    </row>
-    <row r="375" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL375" s="5"/>
-    </row>
-    <row r="376" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL376" s="5"/>
+    <row r="349" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV349"/>
+    </row>
+    <row r="350" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV350"/>
+      <c r="CL350" s="5"/>
+    </row>
+    <row r="351" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV351"/>
+      <c r="CL351" s="5"/>
+    </row>
+    <row r="352" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL352" s="5"/>
+    </row>
+    <row r="368" spans="74:74" x14ac:dyDescent="0.25">
+      <c r="BV368"/>
+    </row>
+    <row r="369" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL369" s="5"/>
+    </row>
+    <row r="377" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL377" s="5"/>
     </row>
     <row r="378" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV378"/>
+      <c r="CL378" s="5"/>
     </row>
     <row r="379" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL379" s="5"/>
     </row>
     <row r="380" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV380"/>
+      <c r="CL380" s="5"/>
     </row>
     <row r="381" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV381"/>
       <c r="CL381" s="5"/>
     </row>
-    <row r="382" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL382" s="5"/>
+    <row r="383" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV383"/>
     </row>
     <row r="384" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV384"/>
+      <c r="CL384" s="5"/>
     </row>
     <row r="385" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV385"/>
-      <c r="CL385" s="5"/>
     </row>
     <row r="386" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV386"/>
@@ -9838,41 +10360,38 @@
       <c r="CL387" s="5"/>
     </row>
     <row r="389" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL389" s="5"/>
+      <c r="BV389"/>
+    </row>
+    <row r="390" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV390"/>
+      <c r="CL390" s="5"/>
     </row>
     <row r="391" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV391"/>
       <c r="CL391" s="5"/>
     </row>
-    <row r="393" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL393" s="5"/>
+    <row r="392" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL392" s="5"/>
+    </row>
+    <row r="394" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL394" s="5"/>
     </row>
     <row r="396" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL396" s="5"/>
     </row>
-    <row r="397" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL397" s="5"/>
-    </row>
     <row r="398" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL398" s="5"/>
     </row>
-    <row r="399" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL399" s="5"/>
-    </row>
-    <row r="400" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL400" s="5"/>
-    </row>
     <row r="401" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL401" s="5"/>
     </row>
     <row r="402" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV402"/>
+      <c r="CL402" s="5"/>
     </row>
     <row r="403" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV403"/>
       <c r="CL403" s="5"/>
     </row>
     <row r="404" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV404"/>
       <c r="CL404" s="5"/>
     </row>
     <row r="405" spans="74:90" x14ac:dyDescent="0.25">
@@ -9882,10 +10401,15 @@
       <c r="CL406" s="5"/>
     </row>
     <row r="407" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL407" s="5"/>
+      <c r="BV407"/>
     </row>
     <row r="408" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV408"/>
       <c r="CL408" s="5"/>
+    </row>
+    <row r="409" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV409"/>
+      <c r="CL409" s="5"/>
     </row>
     <row r="410" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL410" s="5"/>
@@ -9894,15 +10418,10 @@
       <c r="CL411" s="5"/>
     </row>
     <row r="412" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV412"/>
+      <c r="CL412" s="5"/>
     </row>
     <row r="413" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV413"/>
       <c r="CL413" s="5"/>
-    </row>
-    <row r="414" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV414"/>
-      <c r="CL414" s="5"/>
     </row>
     <row r="415" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL415" s="5"/>
@@ -9910,28 +10429,32 @@
     <row r="416" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL416" s="5"/>
     </row>
+    <row r="417" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV417"/>
+    </row>
     <row r="418" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV418"/>
       <c r="CL418" s="5"/>
     </row>
     <row r="419" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV419"/>
       <c r="CL419" s="5"/>
     </row>
     <row r="420" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV420"/>
       <c r="CL420" s="5"/>
     </row>
     <row r="421" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV421"/>
       <c r="CL421" s="5"/>
-    </row>
-    <row r="422" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL422" s="5"/>
     </row>
     <row r="423" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL423" s="5"/>
     </row>
     <row r="424" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL424" s="5"/>
+    </row>
+    <row r="425" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV425"/>
+      <c r="CL425" s="5"/>
     </row>
     <row r="426" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV426"/>
@@ -9943,9 +10466,8 @@
     <row r="428" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL428" s="5"/>
     </row>
-    <row r="430" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV430"/>
-      <c r="CL430" s="5"/>
+    <row r="429" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL429" s="5"/>
     </row>
     <row r="431" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV431"/>
@@ -9954,40 +10476,42 @@
     <row r="432" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL432" s="5"/>
     </row>
-    <row r="434" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL434" s="5"/>
+    <row r="433" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL433" s="5"/>
+    </row>
+    <row r="435" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV435"/>
+      <c r="CL435" s="5"/>
     </row>
     <row r="436" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV436"/>
       <c r="CL436" s="5"/>
+    </row>
+    <row r="437" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL437" s="5"/>
     </row>
     <row r="439" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL439" s="5"/>
     </row>
-    <row r="440" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL440" s="5"/>
+    <row r="441" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL441" s="5"/>
     </row>
     <row r="444" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV444"/>
+      <c r="CL444" s="5"/>
     </row>
     <row r="445" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV445"/>
       <c r="CL445" s="5"/>
-    </row>
-    <row r="446" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV446"/>
-      <c r="CL446" s="5"/>
-    </row>
-    <row r="447" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL447" s="5"/>
-    </row>
-    <row r="448" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL448" s="5"/>
     </row>
     <row r="449" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV449"/>
     </row>
     <row r="450" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV450"/>
       <c r="CL450" s="5"/>
+    </row>
+    <row r="451" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV451"/>
+      <c r="CL451" s="5"/>
     </row>
     <row r="452" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL452" s="5"/>
@@ -9995,112 +10519,104 @@
     <row r="453" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL453" s="5"/>
     </row>
+    <row r="454" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV454"/>
+    </row>
     <row r="455" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL455" s="5"/>
     </row>
-    <row r="456" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL456" s="5"/>
-    </row>
     <row r="457" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL457" s="5"/>
     </row>
     <row r="458" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL458" s="5"/>
     </row>
-    <row r="459" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL459" s="5"/>
-    </row>
     <row r="460" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL460" s="5"/>
     </row>
     <row r="461" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL461" s="5"/>
     </row>
+    <row r="462" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL462" s="5"/>
+    </row>
     <row r="463" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV463"/>
+      <c r="CL463" s="5"/>
     </row>
     <row r="464" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL464" s="5"/>
     </row>
-    <row r="465" spans="90:90" x14ac:dyDescent="0.25">
+    <row r="465" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL465" s="5"/>
     </row>
-    <row r="498" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU498" s="15"/>
-      <c r="BV498" s="16"/>
-    </row>
-    <row r="499" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H499" s="15"/>
-      <c r="CL499" s="15"/>
-    </row>
-    <row r="505" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV505"/>
-    </row>
-    <row r="506" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV506"/>
-      <c r="CL506" s="5"/>
-    </row>
-    <row r="507" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV507"/>
-      <c r="CL507" s="5"/>
-    </row>
-    <row r="508" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="CL508" s="5"/>
-    </row>
-    <row r="525" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV525"/>
-    </row>
-    <row r="526" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL526" s="5"/>
-    </row>
-    <row r="558" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV558"/>
-    </row>
-    <row r="559" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV559"/>
-      <c r="CL559" s="5"/>
-    </row>
-    <row r="560" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL560" s="5"/>
-    </row>
-    <row r="576" spans="74:74" x14ac:dyDescent="0.25">
-      <c r="BV576"/>
-    </row>
-    <row r="577" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL577" s="5"/>
-    </row>
-    <row r="583" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV583"/>
-    </row>
-    <row r="584" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV584"/>
-      <c r="CL584" s="5"/>
-    </row>
-    <row r="585" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL585" s="5"/>
+    <row r="466" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL466" s="5"/>
+    </row>
+    <row r="468" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV468"/>
+    </row>
+    <row r="469" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL469" s="5"/>
+    </row>
+    <row r="470" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL470" s="5"/>
+    </row>
+    <row r="503" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU503" s="15"/>
+      <c r="BV503" s="16"/>
+    </row>
+    <row r="504" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H504" s="15"/>
+      <c r="CL504" s="15"/>
+    </row>
+    <row r="510" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV510"/>
+    </row>
+    <row r="511" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV511"/>
+      <c r="CL511" s="5"/>
+    </row>
+    <row r="512" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV512"/>
+      <c r="CL512" s="5"/>
+    </row>
+    <row r="513" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL513" s="5"/>
+    </row>
+    <row r="530" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV530"/>
+    </row>
+    <row r="531" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL531" s="5"/>
+    </row>
+    <row r="563" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV563"/>
+    </row>
+    <row r="564" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV564"/>
+      <c r="CL564" s="5"/>
+    </row>
+    <row r="565" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL565" s="5"/>
+    </row>
+    <row r="581" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV581"/>
+    </row>
+    <row r="582" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL582" s="5"/>
+    </row>
+    <row r="588" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV588"/>
+    </row>
+    <row r="589" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV589"/>
+      <c r="CL589" s="5"/>
     </row>
     <row r="590" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV590"/>
-    </row>
-    <row r="591" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV591"/>
-      <c r="CL591" s="5"/>
-    </row>
-    <row r="592" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV592"/>
-      <c r="CL592" s="5"/>
-    </row>
-    <row r="593" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV593"/>
-      <c r="CL593" s="5"/>
-    </row>
-    <row r="594" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV594"/>
-      <c r="CL594" s="5"/>
+      <c r="CL590" s="5"/>
     </row>
     <row r="595" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV595"/>
-      <c r="CL595" s="5"/>
     </row>
     <row r="596" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV596"/>
@@ -10143,56 +10659,56 @@
       <c r="CL605" s="5"/>
     </row>
     <row r="606" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV606"/>
       <c r="CL606" s="5"/>
+    </row>
+    <row r="607" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV607"/>
+      <c r="CL607" s="5"/>
+    </row>
+    <row r="608" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV608"/>
+      <c r="CL608" s="5"/>
+    </row>
+    <row r="609" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV609"/>
+      <c r="CL609" s="5"/>
     </row>
     <row r="610" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV610"/>
+      <c r="CL610" s="5"/>
     </row>
     <row r="611" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV611"/>
       <c r="CL611" s="5"/>
     </row>
-    <row r="612" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL612" s="5"/>
-    </row>
-    <row r="613" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV613"/>
-    </row>
-    <row r="614" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL614" s="5"/>
+    <row r="615" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV615"/>
+    </row>
+    <row r="616" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV616"/>
+      <c r="CL616" s="5"/>
     </row>
     <row r="617" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV617"/>
+      <c r="CL617" s="5"/>
     </row>
     <row r="618" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV618"/>
-      <c r="CL618" s="5"/>
     </row>
     <row r="619" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL619" s="5"/>
     </row>
-    <row r="650" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV650"/>
-    </row>
-    <row r="651" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV651"/>
-      <c r="CL651" s="5"/>
-    </row>
-    <row r="652" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV652"/>
-      <c r="CL652" s="5"/>
-    </row>
-    <row r="653" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV653"/>
-      <c r="CL653" s="5"/>
-    </row>
-    <row r="654" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV654"/>
-      <c r="CL654" s="5"/>
+    <row r="622" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV622"/>
+    </row>
+    <row r="623" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV623"/>
+      <c r="CL623" s="5"/>
+    </row>
+    <row r="624" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL624" s="5"/>
     </row>
     <row r="655" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV655"/>
-      <c r="CL655" s="5"/>
     </row>
     <row r="656" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV656"/>
@@ -10203,13 +10719,27 @@
       <c r="CL657" s="5"/>
     </row>
     <row r="658" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV658"/>
       <c r="CL658" s="5"/>
+    </row>
+    <row r="659" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV659"/>
+      <c r="CL659" s="5"/>
     </row>
     <row r="660" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV660"/>
+      <c r="CL660" s="5"/>
     </row>
     <row r="661" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV661"/>
       <c r="CL661" s="5"/>
+    </row>
+    <row r="662" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV662"/>
+      <c r="CL662" s="5"/>
+    </row>
+    <row r="663" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL663" s="5"/>
     </row>
     <row r="665" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV665"/>
@@ -10217,130 +10747,116 @@
     <row r="666" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL666" s="5"/>
     </row>
-    <row r="669" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV669"/>
-    </row>
     <row r="670" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV670"/>
-      <c r="CL670" s="5"/>
     </row>
     <row r="671" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV671"/>
       <c r="CL671" s="5"/>
     </row>
-    <row r="672" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV672"/>
-      <c r="CL672" s="5"/>
-    </row>
-    <row r="673" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL673" s="5"/>
-    </row>
-    <row r="680" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV680"/>
-    </row>
-    <row r="681" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL681" s="5"/>
-    </row>
-    <row r="684" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV684"/>
+    <row r="674" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV674"/>
+    </row>
+    <row r="675" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV675"/>
+      <c r="CL675" s="5"/>
+    </row>
+    <row r="676" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV676"/>
+      <c r="CL676" s="5"/>
+    </row>
+    <row r="677" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV677"/>
+      <c r="CL677" s="5"/>
+    </row>
+    <row r="678" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL678" s="5"/>
     </row>
     <row r="685" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV685"/>
-      <c r="CL685" s="5"/>
     </row>
     <row r="686" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV686"/>
       <c r="CL686" s="5"/>
     </row>
-    <row r="687" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV687"/>
-      <c r="CL687" s="5"/>
-    </row>
-    <row r="688" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL688" s="5"/>
+    <row r="689" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV689"/>
     </row>
     <row r="690" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV690"/>
+      <c r="CL690" s="5"/>
     </row>
     <row r="691" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV691"/>
       <c r="CL691" s="5"/>
     </row>
     <row r="692" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV692"/>
       <c r="CL692" s="5"/>
     </row>
     <row r="693" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL693">
-        <v>0.15</v>
-      </c>
+      <c r="CL693" s="5"/>
     </row>
     <row r="695" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL695">
-        <v>0.2</v>
-      </c>
+      <c r="BV695"/>
     </row>
     <row r="696" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL696">
-        <v>0.1</v>
-      </c>
+      <c r="BV696"/>
+      <c r="CL696" s="5"/>
+    </row>
+    <row r="697" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL697" s="5"/>
     </row>
     <row r="698" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL698">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="700" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL700">
         <v>0.2</v>
       </c>
     </row>
-    <row r="705" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL705">
+    <row r="701" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL701">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="703" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL703">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="710" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL710">
         <v>1</v>
       </c>
     </row>
-    <row r="707" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL707">
+    <row r="712" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL712">
         <v>0.4</v>
       </c>
     </row>
-    <row r="708" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL708">
+    <row r="713" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL713">
         <v>0.6</v>
       </c>
     </row>
-    <row r="711" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL711">
+    <row r="716" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL716">
         <v>0.5</v>
       </c>
     </row>
-    <row r="712" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL712">
+    <row r="717" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL717">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="713" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL713">
+    <row r="718" spans="90:90" x14ac:dyDescent="0.25">
+      <c r="CL718">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="716" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV716"/>
-    </row>
-    <row r="717" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV717"/>
-      <c r="CL717" s="5"/>
-    </row>
-    <row r="718" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV718"/>
-      <c r="CL718" s="5"/>
-    </row>
-    <row r="719" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV719"/>
-      <c r="CL719" s="5"/>
-    </row>
-    <row r="720" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV720"/>
-      <c r="CL720" s="5"/>
     </row>
     <row r="721" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV721"/>
-      <c r="CL721" s="5"/>
     </row>
     <row r="722" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV722"/>
@@ -10355,36 +10871,36 @@
       <c r="CL724" s="5"/>
     </row>
     <row r="725" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV725"/>
       <c r="CL725" s="5"/>
     </row>
     <row r="726" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV726"/>
+      <c r="CL726" s="5"/>
     </row>
     <row r="727" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV727"/>
       <c r="CL727" s="5"/>
     </row>
-    <row r="736" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV736"/>
-    </row>
-    <row r="737" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV737"/>
-      <c r="CL737" s="5"/>
-    </row>
-    <row r="738" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV738"/>
-      <c r="CL738" s="5"/>
-    </row>
-    <row r="739" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV739"/>
-      <c r="CL739" s="5"/>
-    </row>
-    <row r="740" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV740"/>
-      <c r="CL740" s="5"/>
+    <row r="728" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV728"/>
+      <c r="CL728" s="5"/>
+    </row>
+    <row r="729" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV729"/>
+      <c r="CL729" s="5"/>
+    </row>
+    <row r="730" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL730" s="5"/>
+    </row>
+    <row r="731" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV731"/>
+    </row>
+    <row r="732" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL732" s="5"/>
     </row>
     <row r="741" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV741"/>
-      <c r="CL741" s="5"/>
     </row>
     <row r="742" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV742"/>
@@ -10395,44 +10911,46 @@
       <c r="CL743" s="5"/>
     </row>
     <row r="744" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV744"/>
       <c r="CL744" s="5"/>
     </row>
     <row r="745" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV745"/>
+      <c r="CL745" s="5"/>
     </row>
     <row r="746" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV746"/>
       <c r="CL746" s="5"/>
     </row>
+    <row r="747" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV747"/>
+      <c r="CL747" s="5"/>
+    </row>
+    <row r="748" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV748"/>
+      <c r="CL748" s="5"/>
+    </row>
+    <row r="749" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL749" s="5"/>
+    </row>
+    <row r="750" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV750"/>
+    </row>
     <row r="751" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV751"/>
-    </row>
-    <row r="752" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV752"/>
-      <c r="CL752" s="5"/>
-    </row>
-    <row r="753" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL753" s="5"/>
-    </row>
-    <row r="754" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV754"/>
-    </row>
-    <row r="755" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV755"/>
-      <c r="CL755" s="5"/>
+      <c r="CL751" s="5"/>
     </row>
     <row r="756" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL756" s="5"/>
+      <c r="BV756"/>
     </row>
     <row r="757" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV757"/>
+      <c r="CL757" s="5"/>
     </row>
     <row r="758" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV758"/>
       <c r="CL758" s="5"/>
     </row>
     <row r="759" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV759"/>
-      <c r="CL759" s="5"/>
     </row>
     <row r="760" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV760"/>
@@ -10441,130 +10959,130 @@
     <row r="761" spans="74:90" x14ac:dyDescent="0.25">
       <c r="CL761" s="5"/>
     </row>
+    <row r="762" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV762"/>
+    </row>
+    <row r="763" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV763"/>
+      <c r="CL763" s="5"/>
+    </row>
+    <row r="764" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV764"/>
+      <c r="CL764" s="5"/>
+    </row>
     <row r="765" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV765"/>
+      <c r="CL765" s="5"/>
     </row>
     <row r="766" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV766"/>
       <c r="CL766" s="5"/>
     </row>
-    <row r="767" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV767"/>
-      <c r="CL767" s="5"/>
-    </row>
-    <row r="768" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="CL768" s="5"/>
-    </row>
-    <row r="769" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV769"/>
-    </row>
     <row r="770" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="CL770" s="5"/>
+      <c r="BV770"/>
     </row>
     <row r="771" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU771" s="15"/>
-      <c r="BV771" s="16"/>
+      <c r="BV771"/>
+      <c r="CL771" s="5"/>
     </row>
     <row r="772" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H772" s="15"/>
-      <c r="CL772" s="15"/>
-    </row>
-    <row r="789" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV789"/>
-    </row>
-    <row r="790" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV790"/>
-      <c r="CL790" s="5"/>
-    </row>
-    <row r="791" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV791"/>
-      <c r="CL791" s="5"/>
-    </row>
-    <row r="792" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BV792"/>
-      <c r="CL792" s="5"/>
-    </row>
-    <row r="793" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="CL793" s="5"/>
-    </row>
-    <row r="794" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV772"/>
+      <c r="CL772" s="5"/>
+    </row>
+    <row r="773" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL773" s="5"/>
+    </row>
+    <row r="774" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV774"/>
+    </row>
+    <row r="775" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="CL775" s="5"/>
+    </row>
+    <row r="776" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU776" s="15"/>
+      <c r="BV776" s="16"/>
+    </row>
+    <row r="777" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H777" s="15"/>
+      <c r="CL777" s="15"/>
+    </row>
+    <row r="794" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV794"/>
     </row>
-    <row r="795" spans="8:90" x14ac:dyDescent="0.25">
+    <row r="795" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV795"/>
       <c r="CL795" s="5"/>
     </row>
-    <row r="796" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="BU796" s="15"/>
-      <c r="BV796" s="16"/>
+    <row r="796" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV796"/>
       <c r="CL796" s="5"/>
     </row>
-    <row r="797" spans="8:90" x14ac:dyDescent="0.25">
-      <c r="H797" s="15"/>
-      <c r="CL797" s="15"/>
-    </row>
-    <row r="800" spans="8:90" x14ac:dyDescent="0.25">
+    <row r="797" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV797"/>
+      <c r="CL797" s="5"/>
+    </row>
+    <row r="798" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL798" s="5"/>
+    </row>
+    <row r="799" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV799"/>
+    </row>
+    <row r="800" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV800"/>
-    </row>
-    <row r="801" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV801"/>
+      <c r="CL800" s="5"/>
+    </row>
+    <row r="801" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BU801" s="15"/>
+      <c r="BV801" s="16"/>
       <c r="CL801" s="5"/>
     </row>
-    <row r="802" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV802"/>
-      <c r="CL802" s="5"/>
-    </row>
-    <row r="803" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV803"/>
-      <c r="CL803" s="5"/>
-    </row>
-    <row r="804" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV804"/>
-      <c r="CL804" s="5"/>
-    </row>
-    <row r="805" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="802" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="H802" s="15"/>
+      <c r="CL802" s="15"/>
+    </row>
+    <row r="805" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV805"/>
-      <c r="CL805" s="5"/>
-    </row>
-    <row r="806" spans="74:90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="806" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV806"/>
       <c r="CL806" s="5"/>
     </row>
-    <row r="807" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="807" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV807"/>
       <c r="CL807" s="5"/>
     </row>
-    <row r="808" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="808" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV808"/>
       <c r="CL808" s="5"/>
     </row>
-    <row r="810" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="809" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV809"/>
+      <c r="CL809" s="5"/>
+    </row>
+    <row r="810" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV810"/>
-    </row>
-    <row r="811" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL810" s="5"/>
+    </row>
+    <row r="811" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV811"/>
       <c r="CL811" s="5"/>
     </row>
-    <row r="812" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="812" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV812"/>
       <c r="CL812" s="5"/>
     </row>
-    <row r="813" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV813"/>
+    <row r="813" spans="8:90" x14ac:dyDescent="0.25">
       <c r="CL813" s="5"/>
     </row>
-    <row r="814" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV814"/>
-      <c r="CL814" s="5"/>
-    </row>
-    <row r="815" spans="74:90" x14ac:dyDescent="0.25">
+    <row r="815" spans="8:90" x14ac:dyDescent="0.25">
       <c r="BV815"/>
-      <c r="CL815" s="5"/>
-    </row>
-    <row r="816" spans="74:90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="816" spans="8:90" x14ac:dyDescent="0.25">
+      <c r="BV816"/>
       <c r="CL816" s="5"/>
     </row>
     <row r="817" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV817"/>
+      <c r="CL817" s="5"/>
     </row>
     <row r="818" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV818"/>
@@ -10579,12 +11097,10 @@
       <c r="CL820" s="5"/>
     </row>
     <row r="821" spans="74:90" x14ac:dyDescent="0.25">
-      <c r="BV821"/>
       <c r="CL821" s="5"/>
     </row>
     <row r="822" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV822"/>
-      <c r="CL822" s="5"/>
     </row>
     <row r="823" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV823"/>
@@ -10683,10 +11199,12 @@
       <c r="CL846" s="5"/>
     </row>
     <row r="847" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV847"/>
       <c r="CL847" s="5"/>
     </row>
     <row r="848" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV848"/>
+      <c r="CL848" s="5"/>
     </row>
     <row r="849" spans="74:90" x14ac:dyDescent="0.25">
       <c r="BV849"/>
@@ -10697,7 +11215,25 @@
       <c r="CL850" s="5"/>
     </row>
     <row r="851" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV851"/>
       <c r="CL851" s="5"/>
+    </row>
+    <row r="852" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL852" s="5"/>
+    </row>
+    <row r="853" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV853"/>
+    </row>
+    <row r="854" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV854"/>
+      <c r="CL854" s="5"/>
+    </row>
+    <row r="855" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="BV855"/>
+      <c r="CL855" s="5"/>
+    </row>
+    <row r="856" spans="74:90" x14ac:dyDescent="0.25">
+      <c r="CL856" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
@@ -10709,7 +11245,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.08203125" customWidth="1"/>
@@ -10872,7 +11408,7 @@
         <v>464</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -10885,7 +11421,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>466</v>
@@ -10894,93 +11430,132 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="C10" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="Q9" s="2"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="K10"/>
-      <c r="P10"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="K13"/>
-      <c r="P13"/>
-    </row>
-    <row r="14" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="Q10" s="2"/>
+    </row>
+    <row r="12" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="K12"/>
+      <c r="P12"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K16"/>
+      <c r="P16"/>
+    </row>
+    <row r="17" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1</v>
+      </c>
+      <c r="K17"/>
+      <c r="P17"/>
+      <c r="Q17" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-      <c r="K14"/>
-      <c r="P14"/>
-      <c r="Q14" s="3" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="J16"/>
-      <c r="P16"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="J20"/>
-      <c r="P20"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="J19"/>
+      <c r="P19"/>
+      <c r="Q19" s="3" t="s">
+        <v>574</v>
+      </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="Q22" s="2"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J23"/>
+      <c r="P23"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="Q25" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
@@ -10991,7 +11566,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -11037,16 +11612,42 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>492</v>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -11058,16 +11659,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -11093,10 +11699,13 @@
         <v>388</v>
       </c>
       <c r="I2" t="s">
+        <v>317</v>
+      </c>
+      <c r="J2" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -11121,48 +11730,49 @@
       <c r="H3" t="s">
         <v>117</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
+        <v>357</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I6" s="2" t="s">
-        <v>553</v>
-      </c>
+      <c r="J5" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J6" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
